--- a/ACCOUNT_RECEIPT/tests/DatasheetKDMC 12.xlsx
+++ b/ACCOUNT_RECEIPT/tests/DatasheetKDMC 12.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="19290" windowHeight="4485"/>
   </bookViews>
   <sheets>
     <sheet name="Done" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>Receipt Date</t>
   </si>
@@ -106,27 +106,6 @@
   <si>
     <t>708989</t>
   </si>
-  <si>
-    <t>Deposits Payables Receipt</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>EMD for E-tendering as per Tender No_2023_KDMC_959513_1As per Bank Ref No_CPADGEJIP9-2Mayur M K S S</t>
-  </si>
-  <si>
-    <t>Cheque</t>
-  </si>
-  <si>
-    <t>708990</t>
-  </si>
-  <si>
-    <t>Pay Order</t>
-  </si>
-  <si>
-    <t>708991</t>
-  </si>
 </sst>
 </file>
 
@@ -138,7 +117,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,12 +145,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1D1C14"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -745,64 +718,64 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -811,10 +784,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,10 +796,10 @@
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -835,10 +808,10 @@
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -847,10 +820,10 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -859,10 +832,10 @@
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -871,11 +844,11 @@
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -922,7 +895,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -932,38 +904,38 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1336,7 +1308,7 @@
       <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
@@ -1376,16 +1348,16 @@
       <c r="H2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M2" s="16" t="s">
@@ -1394,7 +1366,7 @@
       <c r="N2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1402,8 +1374,8 @@
       <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>26</v>
+      <c r="B3" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>17</v>
@@ -1414,30 +1386,30 @@
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="G3" s="16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="24" t="s">
-        <v>29</v>
+      <c r="K3" s="23" t="s">
+        <v>23</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="O3" s="22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1462,25 +1434,25 @@
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>31</v>
+      <c r="K4" s="23" t="s">
+        <v>23</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1491,15 +1463,15 @@
       <c r="D5" s="14"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="19"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="23"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="22"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="27"/>
+      <c r="L5" s="26"/>
       <c r="M5" s="16"/>
       <c r="N5" s="11"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" ht="15.75" spans="1:15">
       <c r="A6" s="11"/>
@@ -1508,15 +1480,15 @@
       <c r="D6" s="14"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="19"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="17"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="23"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="22"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="16"/>
       <c r="N6" s="11"/>
-      <c r="O6" s="23"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" ht="15.75" spans="1:15">
       <c r="A7" s="11"/>
@@ -1525,15 +1497,15 @@
       <c r="D7" s="14"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="19"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="23"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="22"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="27"/>
+      <c r="L7" s="26"/>
       <c r="M7" s="16"/>
       <c r="N7" s="11"/>
-      <c r="O7" s="23"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" ht="15.75" spans="1:15">
       <c r="A8" s="11"/>
@@ -1542,32 +1514,32 @@
       <c r="D8" s="14"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="19"/>
+      <c r="G8" s="18"/>
       <c r="H8" s="17"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="23"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="22"/>
       <c r="K8" s="13"/>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="16"/>
       <c r="N8" s="11"/>
-      <c r="O8" s="23"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="9" ht="15.75" spans="1:15">
       <c r="A9" s="11"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
-      <c r="D9" s="20"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="19"/>
+      <c r="G9" s="18"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="23"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="13"/>
-      <c r="L9" s="27"/>
+      <c r="L9" s="26"/>
       <c r="M9" s="16"/>
       <c r="N9" s="11"/>
-      <c r="O9" s="23"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" ht="15.75" spans="1:15">
       <c r="A10" s="11"/>
@@ -1576,15 +1548,15 @@
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="19"/>
+      <c r="G10" s="18"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="23"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="16"/>
       <c r="N10" s="11"/>
-      <c r="O10" s="23"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11" ht="15.75" spans="1:15">
       <c r="A11" s="11"/>
@@ -1593,15 +1565,15 @@
       <c r="D11" s="14"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="19"/>
+      <c r="G11" s="18"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="23"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="22"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="27"/>
+      <c r="L11" s="26"/>
       <c r="M11" s="16"/>
       <c r="N11" s="11"/>
-      <c r="O11" s="23"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="11"/>
@@ -1610,15 +1582,15 @@
       <c r="D12" s="14"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="19"/>
+      <c r="G12" s="18"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="23"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="22"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="28"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="16"/>
       <c r="N12" s="11"/>
-      <c r="O12" s="23"/>
+      <c r="O12" s="22"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="11"/>
@@ -1627,15 +1599,15 @@
       <c r="D13" s="14"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="19"/>
+      <c r="G13" s="18"/>
       <c r="H13" s="17"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="23"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="22"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="28"/>
+      <c r="L13" s="27"/>
       <c r="M13" s="16"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="23"/>
+      <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="11"/>
@@ -1644,15 +1616,15 @@
       <c r="D14" s="14"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="19"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="23"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="22"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="28"/>
+      <c r="L14" s="27"/>
       <c r="M14" s="16"/>
       <c r="N14" s="11"/>
-      <c r="O14" s="23"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="11"/>
@@ -1661,15 +1633,15 @@
       <c r="D15" s="14"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="19"/>
+      <c r="G15" s="18"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="23"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="13"/>
-      <c r="L15" s="28"/>
+      <c r="L15" s="27"/>
       <c r="M15" s="16"/>
       <c r="N15" s="11"/>
-      <c r="O15" s="23"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="11"/>
@@ -1678,15 +1650,15 @@
       <c r="D16" s="14"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="19"/>
+      <c r="G16" s="18"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="23"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="22"/>
       <c r="K16" s="13"/>
-      <c r="L16" s="28"/>
+      <c r="L16" s="27"/>
       <c r="M16" s="16"/>
       <c r="N16" s="11"/>
-      <c r="O16" s="23"/>
+      <c r="O16" s="22"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="11"/>
@@ -1695,15 +1667,15 @@
       <c r="D17" s="14"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="19"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="17"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="23"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="22"/>
       <c r="K17" s="13"/>
-      <c r="L17" s="28"/>
+      <c r="L17" s="27"/>
       <c r="M17" s="16"/>
       <c r="N17" s="11"/>
-      <c r="O17" s="23"/>
+      <c r="O17" s="22"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="11"/>
@@ -1712,15 +1684,15 @@
       <c r="D18" s="14"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="19"/>
+      <c r="G18" s="18"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="23"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="22"/>
       <c r="K18" s="13"/>
-      <c r="L18" s="28"/>
+      <c r="L18" s="27"/>
       <c r="M18" s="16"/>
       <c r="N18" s="11"/>
-      <c r="O18" s="23"/>
+      <c r="O18" s="22"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="11"/>
@@ -1729,15 +1701,15 @@
       <c r="D19" s="14"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="19"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="23"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="22"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="28"/>
+      <c r="L19" s="27"/>
       <c r="M19" s="16"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="23"/>
+      <c r="O19" s="22"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="11"/>
@@ -1746,15 +1718,15 @@
       <c r="D20" s="14"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="19"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="17"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="23"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="22"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="28"/>
+      <c r="L20" s="27"/>
       <c r="M20" s="16"/>
       <c r="N20" s="11"/>
-      <c r="O20" s="23"/>
+      <c r="O20" s="22"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="11"/>
@@ -1763,15 +1735,15 @@
       <c r="D21" s="14"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="19"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="17"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="23"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="22"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="28"/>
+      <c r="L21" s="27"/>
       <c r="M21" s="16"/>
       <c r="N21" s="11"/>
-      <c r="O21" s="23"/>
+      <c r="O21" s="22"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="11"/>
@@ -1780,15 +1752,15 @@
       <c r="D22" s="14"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="19"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="17"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="23"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="22"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="28"/>
+      <c r="L22" s="27"/>
       <c r="M22" s="16"/>
       <c r="N22" s="11"/>
-      <c r="O22" s="23"/>
+      <c r="O22" s="22"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="11"/>
@@ -1797,15 +1769,15 @@
       <c r="D23" s="14"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="19"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="17"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="23"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="22"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="28"/>
+      <c r="L23" s="27"/>
       <c r="M23" s="16"/>
       <c r="N23" s="11"/>
-      <c r="O23" s="23"/>
+      <c r="O23" s="22"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="11"/>
@@ -1814,15 +1786,15 @@
       <c r="D24" s="14"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="19"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="17"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="23"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="22"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="28"/>
+      <c r="L24" s="27"/>
       <c r="M24" s="16"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="23"/>
+      <c r="O24" s="22"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="11"/>
@@ -1831,15 +1803,15 @@
       <c r="D25" s="14"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
-      <c r="G25" s="19"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="23"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="22"/>
       <c r="K25" s="13"/>
-      <c r="L25" s="28"/>
+      <c r="L25" s="27"/>
       <c r="M25" s="16"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="23"/>
+      <c r="O25" s="22"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="11"/>
@@ -1848,15 +1820,15 @@
       <c r="D26" s="14"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="19"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="17"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="23"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="22"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="28"/>
+      <c r="L26" s="27"/>
       <c r="M26" s="16"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="23"/>
+      <c r="O26" s="22"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="11"/>
@@ -1865,15 +1837,15 @@
       <c r="D27" s="14"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
-      <c r="G27" s="19"/>
+      <c r="G27" s="18"/>
       <c r="H27" s="17"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="23"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="22"/>
       <c r="K27" s="13"/>
-      <c r="L27" s="28"/>
+      <c r="L27" s="27"/>
       <c r="M27" s="16"/>
       <c r="N27" s="11"/>
-      <c r="O27" s="23"/>
+      <c r="O27" s="22"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="11"/>
@@ -1882,15 +1854,15 @@
       <c r="D28" s="14"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
-      <c r="G28" s="19"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="17"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="23"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="22"/>
       <c r="K28" s="13"/>
-      <c r="L28" s="28"/>
+      <c r="L28" s="27"/>
       <c r="M28" s="16"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="23"/>
+      <c r="O28" s="22"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="11"/>
@@ -1899,15 +1871,15 @@
       <c r="D29" s="14"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="19"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="17"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="23"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="13"/>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="16"/>
       <c r="N29" s="11"/>
-      <c r="O29" s="23"/>
+      <c r="O29" s="22"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="11"/>
@@ -1916,15 +1888,15 @@
       <c r="D30" s="14"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="19"/>
+      <c r="G30" s="18"/>
       <c r="H30" s="17"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="23"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="22"/>
       <c r="K30" s="13"/>
-      <c r="L30" s="28"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="16"/>
       <c r="N30" s="11"/>
-      <c r="O30" s="23"/>
+      <c r="O30" s="22"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="11"/>
@@ -1933,15 +1905,15 @@
       <c r="D31" s="14"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="19"/>
+      <c r="G31" s="18"/>
       <c r="H31" s="17"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="23"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="22"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="16"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="23"/>
+      <c r="O31" s="22"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="11"/>
@@ -1950,15 +1922,15 @@
       <c r="D32" s="14"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="19"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="17"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="23"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="22"/>
       <c r="K32" s="13"/>
-      <c r="L32" s="28"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="16"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="23"/>
+      <c r="O32" s="22"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="11"/>
@@ -1967,15 +1939,15 @@
       <c r="D33" s="14"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="19"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="17"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="23"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="22"/>
       <c r="K33" s="13"/>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="16"/>
       <c r="N33" s="11"/>
-      <c r="O33" s="23"/>
+      <c r="O33" s="22"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="11"/>
@@ -1984,15 +1956,15 @@
       <c r="D34" s="14"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
-      <c r="G34" s="19"/>
+      <c r="G34" s="18"/>
       <c r="H34" s="17"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="23"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="22"/>
       <c r="K34" s="13"/>
-      <c r="L34" s="28"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="16"/>
       <c r="N34" s="11"/>
-      <c r="O34" s="23"/>
+      <c r="O34" s="22"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="11"/>
@@ -2001,15 +1973,15 @@
       <c r="D35" s="14"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
-      <c r="G35" s="19"/>
+      <c r="G35" s="18"/>
       <c r="H35" s="17"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="23"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="22"/>
       <c r="K35" s="13"/>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="16"/>
       <c r="N35" s="11"/>
-      <c r="O35" s="23"/>
+      <c r="O35" s="22"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="11"/>
@@ -2018,15 +1990,15 @@
       <c r="D36" s="14"/>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
-      <c r="G36" s="19"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="17"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="23"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="22"/>
       <c r="K36" s="13"/>
-      <c r="L36" s="28"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="16"/>
       <c r="N36" s="11"/>
-      <c r="O36" s="23"/>
+      <c r="O36" s="22"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="11"/>
@@ -2035,15 +2007,15 @@
       <c r="D37" s="14"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
-      <c r="G37" s="19"/>
+      <c r="G37" s="18"/>
       <c r="H37" s="17"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="23"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="22"/>
       <c r="K37" s="13"/>
-      <c r="L37" s="28"/>
+      <c r="L37" s="27"/>
       <c r="M37" s="16"/>
       <c r="N37" s="11"/>
-      <c r="O37" s="23"/>
+      <c r="O37" s="22"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="11"/>
@@ -2052,15 +2024,15 @@
       <c r="D38" s="14"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
-      <c r="G38" s="19"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="17"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="23"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="22"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="28"/>
+      <c r="L38" s="27"/>
       <c r="M38" s="16"/>
       <c r="N38" s="11"/>
-      <c r="O38" s="23"/>
+      <c r="O38" s="22"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="11"/>
@@ -2069,15 +2041,15 @@
       <c r="D39" s="14"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
-      <c r="G39" s="19"/>
+      <c r="G39" s="18"/>
       <c r="H39" s="17"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="23"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="22"/>
       <c r="K39" s="13"/>
-      <c r="L39" s="28"/>
+      <c r="L39" s="27"/>
       <c r="M39" s="16"/>
       <c r="N39" s="11"/>
-      <c r="O39" s="23"/>
+      <c r="O39" s="22"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="11"/>
@@ -2086,15 +2058,15 @@
       <c r="D40" s="14"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="19"/>
+      <c r="G40" s="18"/>
       <c r="H40" s="17"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="23"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="22"/>
       <c r="K40" s="13"/>
-      <c r="L40" s="28"/>
+      <c r="L40" s="27"/>
       <c r="M40" s="16"/>
       <c r="N40" s="11"/>
-      <c r="O40" s="23"/>
+      <c r="O40" s="22"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="11"/>
@@ -2103,15 +2075,15 @@
       <c r="D41" s="14"/>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
-      <c r="G41" s="19"/>
+      <c r="G41" s="18"/>
       <c r="H41" s="17"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="23"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="22"/>
       <c r="K41" s="13"/>
-      <c r="L41" s="28"/>
+      <c r="L41" s="27"/>
       <c r="M41" s="16"/>
       <c r="N41" s="11"/>
-      <c r="O41" s="23"/>
+      <c r="O41" s="22"/>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="11"/>
@@ -2120,15 +2092,15 @@
       <c r="D42" s="14"/>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
-      <c r="G42" s="19"/>
+      <c r="G42" s="18"/>
       <c r="H42" s="17"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="23"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="22"/>
       <c r="K42" s="13"/>
-      <c r="L42" s="28"/>
+      <c r="L42" s="27"/>
       <c r="M42" s="16"/>
       <c r="N42" s="11"/>
-      <c r="O42" s="23"/>
+      <c r="O42" s="22"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="11"/>
@@ -2137,15 +2109,15 @@
       <c r="D43" s="14"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="19"/>
+      <c r="G43" s="18"/>
       <c r="H43" s="17"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="23"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="22"/>
       <c r="K43" s="13"/>
-      <c r="L43" s="28"/>
+      <c r="L43" s="27"/>
       <c r="M43" s="16"/>
       <c r="N43" s="11"/>
-      <c r="O43" s="23"/>
+      <c r="O43" s="22"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="11"/>
@@ -2154,15 +2126,15 @@
       <c r="D44" s="14"/>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="19"/>
+      <c r="G44" s="18"/>
       <c r="H44" s="17"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="23"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="22"/>
       <c r="K44" s="13"/>
-      <c r="L44" s="28"/>
+      <c r="L44" s="27"/>
       <c r="M44" s="16"/>
       <c r="N44" s="11"/>
-      <c r="O44" s="23"/>
+      <c r="O44" s="22"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="11"/>
@@ -2171,15 +2143,15 @@
       <c r="D45" s="14"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="19"/>
+      <c r="G45" s="18"/>
       <c r="H45" s="17"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="23"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="13"/>
-      <c r="L45" s="28"/>
+      <c r="L45" s="27"/>
       <c r="M45" s="16"/>
       <c r="N45" s="11"/>
-      <c r="O45" s="23"/>
+      <c r="O45" s="22"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="11"/>
@@ -2188,15 +2160,15 @@
       <c r="D46" s="14"/>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="19"/>
+      <c r="G46" s="18"/>
       <c r="H46" s="17"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="23"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="22"/>
       <c r="K46" s="13"/>
-      <c r="L46" s="28"/>
+      <c r="L46" s="27"/>
       <c r="M46" s="16"/>
       <c r="N46" s="11"/>
-      <c r="O46" s="23"/>
+      <c r="O46" s="22"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="11"/>
@@ -2205,15 +2177,15 @@
       <c r="D47" s="14"/>
       <c r="E47" s="13"/>
       <c r="F47" s="13"/>
-      <c r="G47" s="19"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="17"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="23"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="22"/>
       <c r="K47" s="13"/>
-      <c r="L47" s="28"/>
+      <c r="L47" s="27"/>
       <c r="M47" s="16"/>
       <c r="N47" s="11"/>
-      <c r="O47" s="23"/>
+      <c r="O47" s="22"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="11"/>
@@ -2222,15 +2194,15 @@
       <c r="D48" s="14"/>
       <c r="E48" s="13"/>
       <c r="F48" s="13"/>
-      <c r="G48" s="19"/>
+      <c r="G48" s="18"/>
       <c r="H48" s="17"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="23"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="22"/>
       <c r="K48" s="13"/>
-      <c r="L48" s="28"/>
+      <c r="L48" s="27"/>
       <c r="M48" s="16"/>
       <c r="N48" s="11"/>
-      <c r="O48" s="23"/>
+      <c r="O48" s="22"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="11"/>
@@ -2239,15 +2211,15 @@
       <c r="D49" s="14"/>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
-      <c r="G49" s="19"/>
+      <c r="G49" s="18"/>
       <c r="H49" s="17"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="23"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="22"/>
       <c r="K49" s="13"/>
-      <c r="L49" s="28"/>
+      <c r="L49" s="27"/>
       <c r="M49" s="16"/>
       <c r="N49" s="11"/>
-      <c r="O49" s="23"/>
+      <c r="O49" s="22"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="11"/>
@@ -2256,15 +2228,15 @@
       <c r="D50" s="14"/>
       <c r="E50" s="13"/>
       <c r="F50" s="13"/>
-      <c r="G50" s="19"/>
+      <c r="G50" s="18"/>
       <c r="H50" s="17"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="23"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="22"/>
       <c r="K50" s="13"/>
-      <c r="L50" s="28"/>
+      <c r="L50" s="27"/>
       <c r="M50" s="16"/>
       <c r="N50" s="11"/>
-      <c r="O50" s="23"/>
+      <c r="O50" s="22"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="11"/>
@@ -2273,15 +2245,15 @@
       <c r="D51" s="14"/>
       <c r="E51" s="13"/>
       <c r="F51" s="13"/>
-      <c r="G51" s="19"/>
+      <c r="G51" s="18"/>
       <c r="H51" s="17"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="23"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="22"/>
       <c r="K51" s="13"/>
-      <c r="L51" s="28"/>
+      <c r="L51" s="27"/>
       <c r="M51" s="16"/>
       <c r="N51" s="11"/>
-      <c r="O51" s="23"/>
+      <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="11"/>
@@ -2290,15 +2262,15 @@
       <c r="D52" s="14"/>
       <c r="E52" s="13"/>
       <c r="F52" s="13"/>
-      <c r="G52" s="19"/>
+      <c r="G52" s="18"/>
       <c r="H52" s="17"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="23"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="22"/>
       <c r="K52" s="13"/>
-      <c r="L52" s="28"/>
+      <c r="L52" s="27"/>
       <c r="M52" s="16"/>
       <c r="N52" s="11"/>
-      <c r="O52" s="23"/>
+      <c r="O52" s="22"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="11"/>
@@ -2307,15 +2279,15 @@
       <c r="D53" s="14"/>
       <c r="E53" s="13"/>
       <c r="F53" s="13"/>
-      <c r="G53" s="19"/>
+      <c r="G53" s="18"/>
       <c r="H53" s="17"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="23"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="22"/>
       <c r="K53" s="13"/>
-      <c r="L53" s="28"/>
+      <c r="L53" s="27"/>
       <c r="M53" s="16"/>
       <c r="N53" s="11"/>
-      <c r="O53" s="23"/>
+      <c r="O53" s="22"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="11"/>
@@ -2324,15 +2296,15 @@
       <c r="D54" s="14"/>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
-      <c r="G54" s="19"/>
+      <c r="G54" s="18"/>
       <c r="H54" s="17"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="23"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="22"/>
       <c r="K54" s="13"/>
-      <c r="L54" s="28"/>
+      <c r="L54" s="27"/>
       <c r="M54" s="16"/>
       <c r="N54" s="11"/>
-      <c r="O54" s="23"/>
+      <c r="O54" s="22"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="11"/>
@@ -2341,15 +2313,15 @@
       <c r="D55" s="14"/>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="19"/>
+      <c r="G55" s="18"/>
       <c r="H55" s="17"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="23"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="22"/>
       <c r="K55" s="13"/>
-      <c r="L55" s="28"/>
+      <c r="L55" s="27"/>
       <c r="M55" s="16"/>
       <c r="N55" s="11"/>
-      <c r="O55" s="23"/>
+      <c r="O55" s="22"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="11"/>
@@ -2358,15 +2330,15 @@
       <c r="D56" s="14"/>
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
-      <c r="G56" s="19"/>
+      <c r="G56" s="18"/>
       <c r="H56" s="17"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="23"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="22"/>
       <c r="K56" s="13"/>
-      <c r="L56" s="28"/>
+      <c r="L56" s="27"/>
       <c r="M56" s="16"/>
       <c r="N56" s="11"/>
-      <c r="O56" s="23"/>
+      <c r="O56" s="22"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="11"/>
@@ -2375,15 +2347,15 @@
       <c r="D57" s="14"/>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="19"/>
+      <c r="G57" s="18"/>
       <c r="H57" s="17"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="23"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="22"/>
       <c r="K57" s="13"/>
-      <c r="L57" s="28"/>
+      <c r="L57" s="27"/>
       <c r="M57" s="16"/>
       <c r="N57" s="11"/>
-      <c r="O57" s="23"/>
+      <c r="O57" s="22"/>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="11"/>
@@ -2392,15 +2364,15 @@
       <c r="D58" s="14"/>
       <c r="E58" s="13"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="19"/>
+      <c r="G58" s="18"/>
       <c r="H58" s="17"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="23"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="22"/>
       <c r="K58" s="13"/>
-      <c r="L58" s="28"/>
+      <c r="L58" s="27"/>
       <c r="M58" s="16"/>
       <c r="N58" s="11"/>
-      <c r="O58" s="23"/>
+      <c r="O58" s="22"/>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="11"/>
@@ -2409,15 +2381,15 @@
       <c r="D59" s="14"/>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="19"/>
+      <c r="G59" s="18"/>
       <c r="H59" s="17"/>
-      <c r="I59" s="26"/>
-      <c r="J59" s="23"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="22"/>
       <c r="K59" s="13"/>
-      <c r="L59" s="28"/>
+      <c r="L59" s="27"/>
       <c r="M59" s="16"/>
       <c r="N59" s="11"/>
-      <c r="O59" s="23"/>
+      <c r="O59" s="22"/>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="11"/>
@@ -2426,15 +2398,15 @@
       <c r="D60" s="14"/>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
-      <c r="G60" s="19"/>
+      <c r="G60" s="18"/>
       <c r="H60" s="17"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="23"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="22"/>
       <c r="K60" s="13"/>
-      <c r="L60" s="28"/>
+      <c r="L60" s="27"/>
       <c r="M60" s="16"/>
       <c r="N60" s="11"/>
-      <c r="O60" s="23"/>
+      <c r="O60" s="22"/>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="11"/>
@@ -2443,15 +2415,15 @@
       <c r="D61" s="14"/>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="19"/>
+      <c r="G61" s="18"/>
       <c r="H61" s="17"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="23"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="22"/>
       <c r="K61" s="13"/>
-      <c r="L61" s="28"/>
+      <c r="L61" s="27"/>
       <c r="M61" s="16"/>
       <c r="N61" s="11"/>
-      <c r="O61" s="23"/>
+      <c r="O61" s="22"/>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="11"/>
@@ -2460,15 +2432,15 @@
       <c r="D62" s="14"/>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
-      <c r="G62" s="19"/>
+      <c r="G62" s="18"/>
       <c r="H62" s="17"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="23"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="22"/>
       <c r="K62" s="13"/>
-      <c r="L62" s="28"/>
+      <c r="L62" s="27"/>
       <c r="M62" s="16"/>
       <c r="N62" s="11"/>
-      <c r="O62" s="23"/>
+      <c r="O62" s="22"/>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="11"/>
@@ -2477,15 +2449,15 @@
       <c r="D63" s="14"/>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
-      <c r="G63" s="19"/>
+      <c r="G63" s="18"/>
       <c r="H63" s="17"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="23"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="22"/>
       <c r="K63" s="13"/>
-      <c r="L63" s="28"/>
+      <c r="L63" s="27"/>
       <c r="M63" s="16"/>
       <c r="N63" s="11"/>
-      <c r="O63" s="23"/>
+      <c r="O63" s="22"/>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" s="11"/>
@@ -2494,15 +2466,15 @@
       <c r="D64" s="14"/>
       <c r="E64" s="13"/>
       <c r="F64" s="13"/>
-      <c r="G64" s="19"/>
+      <c r="G64" s="18"/>
       <c r="H64" s="17"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="23"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="22"/>
       <c r="K64" s="13"/>
-      <c r="L64" s="28"/>
+      <c r="L64" s="27"/>
       <c r="M64" s="16"/>
       <c r="N64" s="11"/>
-      <c r="O64" s="23"/>
+      <c r="O64" s="22"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="11"/>
@@ -2511,15 +2483,15 @@
       <c r="D65" s="14"/>
       <c r="E65" s="13"/>
       <c r="F65" s="13"/>
-      <c r="G65" s="19"/>
+      <c r="G65" s="18"/>
       <c r="H65" s="17"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="23"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="22"/>
       <c r="K65" s="13"/>
-      <c r="L65" s="28"/>
+      <c r="L65" s="27"/>
       <c r="M65" s="16"/>
       <c r="N65" s="11"/>
-      <c r="O65" s="23"/>
+      <c r="O65" s="22"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="11"/>
@@ -2528,15 +2500,15 @@
       <c r="D66" s="14"/>
       <c r="E66" s="13"/>
       <c r="F66" s="13"/>
-      <c r="G66" s="19"/>
+      <c r="G66" s="18"/>
       <c r="H66" s="17"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="23"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="22"/>
       <c r="K66" s="13"/>
-      <c r="L66" s="28"/>
+      <c r="L66" s="27"/>
       <c r="M66" s="16"/>
       <c r="N66" s="11"/>
-      <c r="O66" s="23"/>
+      <c r="O66" s="22"/>
     </row>
     <row r="67" ht="15.75" spans="1:15">
       <c r="A67" s="11"/>
@@ -2547,13 +2519,13 @@
       <c r="F67" s="15"/>
       <c r="G67" s="16"/>
       <c r="H67" s="17"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="23"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="22"/>
       <c r="K67" s="15"/>
-      <c r="L67" s="28"/>
+      <c r="L67" s="27"/>
       <c r="M67" s="16"/>
       <c r="N67" s="11"/>
-      <c r="O67" s="23"/>
+      <c r="O67" s="22"/>
     </row>
     <row r="68" ht="15.75" spans="1:15">
       <c r="A68" s="11"/>
@@ -2564,13 +2536,13 @@
       <c r="F68" s="15"/>
       <c r="G68" s="16"/>
       <c r="H68" s="17"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="23"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="22"/>
       <c r="K68" s="15"/>
-      <c r="L68" s="28"/>
+      <c r="L68" s="27"/>
       <c r="M68" s="16"/>
       <c r="N68" s="11"/>
-      <c r="O68" s="23"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" ht="15.75" spans="1:15">
       <c r="A69" s="11"/>
@@ -2581,13 +2553,13 @@
       <c r="F69" s="15"/>
       <c r="G69" s="16"/>
       <c r="H69" s="17"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="23"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="22"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="28"/>
+      <c r="L69" s="27"/>
       <c r="M69" s="16"/>
       <c r="N69" s="11"/>
-      <c r="O69" s="23"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" ht="15.75" spans="1:15">
       <c r="A70" s="11"/>
@@ -2598,13 +2570,13 @@
       <c r="F70" s="15"/>
       <c r="G70" s="16"/>
       <c r="H70" s="17"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="23"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="22"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="28"/>
+      <c r="L70" s="27"/>
       <c r="M70" s="16"/>
       <c r="N70" s="11"/>
-      <c r="O70" s="23"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" ht="15.75" spans="1:15">
       <c r="A71" s="11"/>
@@ -2615,13 +2587,13 @@
       <c r="F71" s="15"/>
       <c r="G71" s="16"/>
       <c r="H71" s="17"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="23"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="22"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="28"/>
+      <c r="L71" s="27"/>
       <c r="M71" s="16"/>
       <c r="N71" s="11"/>
-      <c r="O71" s="23"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" ht="15.75" spans="1:15">
       <c r="A72" s="11"/>
@@ -2632,13 +2604,13 @@
       <c r="F72" s="15"/>
       <c r="G72" s="16"/>
       <c r="H72" s="17"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="23"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="22"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="28"/>
+      <c r="L72" s="27"/>
       <c r="M72" s="16"/>
       <c r="N72" s="11"/>
-      <c r="O72" s="23"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" ht="15.75" spans="1:15">
       <c r="A73" s="11"/>
@@ -2649,13 +2621,13 @@
       <c r="F73" s="15"/>
       <c r="G73" s="16"/>
       <c r="H73" s="17"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="23"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="22"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="28"/>
+      <c r="L73" s="27"/>
       <c r="M73" s="16"/>
       <c r="N73" s="11"/>
-      <c r="O73" s="23"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" ht="15.75" spans="1:15">
       <c r="A74" s="11"/>
@@ -2666,13 +2638,13 @@
       <c r="F74" s="15"/>
       <c r="G74" s="16"/>
       <c r="H74" s="17"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="23"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="22"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="28"/>
+      <c r="L74" s="27"/>
       <c r="M74" s="16"/>
       <c r="N74" s="11"/>
-      <c r="O74" s="23"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="75" ht="15.75" spans="1:15">
       <c r="A75" s="11"/>
@@ -2683,13 +2655,13 @@
       <c r="F75" s="15"/>
       <c r="G75" s="16"/>
       <c r="H75" s="17"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="23"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="22"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="28"/>
+      <c r="L75" s="27"/>
       <c r="M75" s="16"/>
       <c r="N75" s="11"/>
-      <c r="O75" s="23"/>
+      <c r="O75" s="22"/>
     </row>
     <row r="76" ht="15.75" spans="1:15">
       <c r="A76" s="11"/>
@@ -2700,30 +2672,30 @@
       <c r="F76" s="15"/>
       <c r="G76" s="16"/>
       <c r="H76" s="17"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="23"/>
+      <c r="I76" s="21"/>
+      <c r="J76" s="22"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="28"/>
+      <c r="L76" s="27"/>
       <c r="M76" s="16"/>
       <c r="N76" s="11"/>
-      <c r="O76" s="23"/>
+      <c r="O76" s="22"/>
     </row>
     <row r="77" ht="15.75" spans="1:15">
       <c r="A77" s="11"/>
       <c r="B77" s="15"/>
       <c r="C77" s="13"/>
-      <c r="D77" s="29"/>
+      <c r="D77" s="28"/>
       <c r="E77" s="15"/>
       <c r="F77" s="15"/>
       <c r="G77" s="16"/>
       <c r="H77" s="17"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="23"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="22"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="28"/>
+      <c r="L77" s="27"/>
       <c r="M77" s="16"/>
       <c r="N77" s="11"/>
-      <c r="O77" s="23"/>
+      <c r="O77" s="22"/>
     </row>
     <row r="78" ht="15.75" spans="1:15">
       <c r="A78" s="11"/>
@@ -2734,13 +2706,13 @@
       <c r="F78" s="15"/>
       <c r="G78" s="16"/>
       <c r="H78" s="17"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="23"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="22"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="28"/>
+      <c r="L78" s="27"/>
       <c r="M78" s="16"/>
       <c r="N78" s="11"/>
-      <c r="O78" s="23"/>
+      <c r="O78" s="22"/>
     </row>
     <row r="79" ht="15.75" spans="1:15">
       <c r="A79" s="11"/>
@@ -2751,13 +2723,13 @@
       <c r="F79" s="15"/>
       <c r="G79" s="16"/>
       <c r="H79" s="17"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="23"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="22"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="28"/>
+      <c r="L79" s="27"/>
       <c r="M79" s="16"/>
       <c r="N79" s="11"/>
-      <c r="O79" s="23"/>
+      <c r="O79" s="22"/>
     </row>
     <row r="80" ht="15.75" spans="1:15">
       <c r="A80" s="11"/>
@@ -2768,13 +2740,13 @@
       <c r="F80" s="15"/>
       <c r="G80" s="16"/>
       <c r="H80" s="17"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="23"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="22"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="28"/>
+      <c r="L80" s="27"/>
       <c r="M80" s="16"/>
       <c r="N80" s="11"/>
-      <c r="O80" s="23"/>
+      <c r="O80" s="22"/>
     </row>
     <row r="81" ht="15.75" spans="1:15">
       <c r="A81" s="11"/>
@@ -2785,13 +2757,13 @@
       <c r="F81" s="15"/>
       <c r="G81" s="16"/>
       <c r="H81" s="17"/>
-      <c r="I81" s="22"/>
-      <c r="J81" s="23"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="22"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="28"/>
+      <c r="L81" s="27"/>
       <c r="M81" s="16"/>
       <c r="N81" s="11"/>
-      <c r="O81" s="23"/>
+      <c r="O81" s="22"/>
     </row>
     <row r="82" ht="15.75" spans="1:15">
       <c r="A82" s="11"/>
@@ -2802,13 +2774,13 @@
       <c r="F82" s="15"/>
       <c r="G82" s="16"/>
       <c r="H82" s="17"/>
-      <c r="I82" s="22"/>
-      <c r="J82" s="23"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="22"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="28"/>
+      <c r="L82" s="27"/>
       <c r="M82" s="16"/>
       <c r="N82" s="11"/>
-      <c r="O82" s="23"/>
+      <c r="O82" s="22"/>
     </row>
     <row r="83" ht="15.75" spans="1:15">
       <c r="A83" s="11"/>
@@ -2819,13 +2791,13 @@
       <c r="F83" s="15"/>
       <c r="G83" s="16"/>
       <c r="H83" s="17"/>
-      <c r="I83" s="22"/>
-      <c r="J83" s="23"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="22"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="28"/>
+      <c r="L83" s="27"/>
       <c r="M83" s="16"/>
       <c r="N83" s="11"/>
-      <c r="O83" s="23"/>
+      <c r="O83" s="22"/>
     </row>
     <row r="84" ht="15.75" spans="1:15">
       <c r="A84" s="11"/>
@@ -2836,13 +2808,13 @@
       <c r="F84" s="15"/>
       <c r="G84" s="16"/>
       <c r="H84" s="17"/>
-      <c r="I84" s="22"/>
-      <c r="J84" s="23"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="22"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="28"/>
+      <c r="L84" s="27"/>
       <c r="M84" s="16"/>
       <c r="N84" s="11"/>
-      <c r="O84" s="23"/>
+      <c r="O84" s="22"/>
     </row>
     <row r="85" ht="15.75" spans="1:15">
       <c r="A85" s="11"/>
@@ -2853,13 +2825,13 @@
       <c r="F85" s="15"/>
       <c r="G85" s="16"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="22"/>
-      <c r="J85" s="23"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="22"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="28"/>
+      <c r="L85" s="27"/>
       <c r="M85" s="16"/>
       <c r="N85" s="11"/>
-      <c r="O85" s="23"/>
+      <c r="O85" s="22"/>
     </row>
     <row r="86" ht="15.75" spans="1:15">
       <c r="A86" s="11"/>
@@ -2870,13 +2842,13 @@
       <c r="F86" s="15"/>
       <c r="G86" s="16"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="22"/>
-      <c r="J86" s="23"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="22"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="28"/>
+      <c r="L86" s="27"/>
       <c r="M86" s="16"/>
       <c r="N86" s="11"/>
-      <c r="O86" s="23"/>
+      <c r="O86" s="22"/>
     </row>
     <row r="87" ht="15.75" spans="1:15">
       <c r="A87" s="11"/>
@@ -2887,13 +2859,13 @@
       <c r="F87" s="15"/>
       <c r="G87" s="16"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="23"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="22"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="28"/>
+      <c r="L87" s="27"/>
       <c r="M87" s="16"/>
       <c r="N87" s="11"/>
-      <c r="O87" s="23"/>
+      <c r="O87" s="22"/>
     </row>
     <row r="88" ht="15.75" spans="1:15">
       <c r="A88" s="11"/>
@@ -2904,13 +2876,13 @@
       <c r="F88" s="15"/>
       <c r="G88" s="16"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="22"/>
-      <c r="J88" s="23"/>
+      <c r="I88" s="21"/>
+      <c r="J88" s="22"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="28"/>
+      <c r="L88" s="27"/>
       <c r="M88" s="16"/>
       <c r="N88" s="11"/>
-      <c r="O88" s="23"/>
+      <c r="O88" s="22"/>
     </row>
     <row r="89" ht="15.75" spans="1:15">
       <c r="A89" s="11"/>
@@ -2921,13 +2893,13 @@
       <c r="F89" s="15"/>
       <c r="G89" s="16"/>
       <c r="H89" s="17"/>
-      <c r="I89" s="22"/>
-      <c r="J89" s="23"/>
+      <c r="I89" s="21"/>
+      <c r="J89" s="22"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="28"/>
+      <c r="L89" s="27"/>
       <c r="M89" s="16"/>
       <c r="N89" s="11"/>
-      <c r="O89" s="23"/>
+      <c r="O89" s="22"/>
     </row>
     <row r="90" ht="15.75" spans="1:15">
       <c r="A90" s="11"/>
@@ -2938,13 +2910,13 @@
       <c r="F90" s="15"/>
       <c r="G90" s="16"/>
       <c r="H90" s="17"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="23"/>
+      <c r="I90" s="21"/>
+      <c r="J90" s="22"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="28"/>
+      <c r="L90" s="27"/>
       <c r="M90" s="16"/>
       <c r="N90" s="11"/>
-      <c r="O90" s="23"/>
+      <c r="O90" s="22"/>
     </row>
     <row r="91" ht="15.75" spans="1:15">
       <c r="A91" s="11"/>
@@ -2955,13 +2927,13 @@
       <c r="F91" s="15"/>
       <c r="G91" s="16"/>
       <c r="H91" s="17"/>
-      <c r="I91" s="22"/>
-      <c r="J91" s="23"/>
+      <c r="I91" s="21"/>
+      <c r="J91" s="22"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="28"/>
+      <c r="L91" s="27"/>
       <c r="M91" s="16"/>
       <c r="N91" s="11"/>
-      <c r="O91" s="23"/>
+      <c r="O91" s="22"/>
     </row>
     <row r="92" ht="15.75" spans="1:15">
       <c r="A92" s="11"/>
@@ -2972,13 +2944,13 @@
       <c r="F92" s="15"/>
       <c r="G92" s="16"/>
       <c r="H92" s="17"/>
-      <c r="I92" s="22"/>
-      <c r="J92" s="23"/>
+      <c r="I92" s="21"/>
+      <c r="J92" s="22"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="28"/>
+      <c r="L92" s="27"/>
       <c r="M92" s="16"/>
       <c r="N92" s="11"/>
-      <c r="O92" s="23"/>
+      <c r="O92" s="22"/>
     </row>
     <row r="93" ht="15.75" spans="1:15">
       <c r="A93" s="11"/>
@@ -2989,13 +2961,13 @@
       <c r="F93" s="15"/>
       <c r="G93" s="16"/>
       <c r="H93" s="17"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="23"/>
+      <c r="I93" s="21"/>
+      <c r="J93" s="22"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="28"/>
+      <c r="L93" s="27"/>
       <c r="M93" s="16"/>
       <c r="N93" s="11"/>
-      <c r="O93" s="23"/>
+      <c r="O93" s="22"/>
     </row>
     <row r="94" ht="15.75" spans="1:15">
       <c r="A94" s="11"/>
@@ -3006,13 +2978,13 @@
       <c r="F94" s="15"/>
       <c r="G94" s="16"/>
       <c r="H94" s="17"/>
-      <c r="I94" s="22"/>
-      <c r="J94" s="23"/>
+      <c r="I94" s="21"/>
+      <c r="J94" s="22"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="28"/>
+      <c r="L94" s="27"/>
       <c r="M94" s="16"/>
       <c r="N94" s="11"/>
-      <c r="O94" s="23"/>
+      <c r="O94" s="22"/>
     </row>
     <row r="95" ht="15.75" spans="1:15">
       <c r="A95" s="11"/>
@@ -3023,13 +2995,13 @@
       <c r="F95" s="15"/>
       <c r="G95" s="16"/>
       <c r="H95" s="17"/>
-      <c r="I95" s="22"/>
-      <c r="J95" s="23"/>
+      <c r="I95" s="21"/>
+      <c r="J95" s="22"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="28"/>
+      <c r="L95" s="27"/>
       <c r="M95" s="16"/>
       <c r="N95" s="11"/>
-      <c r="O95" s="23"/>
+      <c r="O95" s="22"/>
     </row>
     <row r="96" ht="15.75" spans="1:15">
       <c r="A96" s="11"/>
@@ -3040,13 +3012,13 @@
       <c r="F96" s="15"/>
       <c r="G96" s="16"/>
       <c r="H96" s="17"/>
-      <c r="I96" s="22"/>
-      <c r="J96" s="23"/>
+      <c r="I96" s="21"/>
+      <c r="J96" s="22"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="28"/>
+      <c r="L96" s="27"/>
       <c r="M96" s="16"/>
       <c r="N96" s="11"/>
-      <c r="O96" s="23"/>
+      <c r="O96" s="22"/>
     </row>
     <row r="97" ht="15.75" spans="1:15">
       <c r="A97" s="11"/>
@@ -3057,13 +3029,13 @@
       <c r="F97" s="15"/>
       <c r="G97" s="16"/>
       <c r="H97" s="17"/>
-      <c r="I97" s="22"/>
-      <c r="J97" s="23"/>
+      <c r="I97" s="21"/>
+      <c r="J97" s="22"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="28"/>
+      <c r="L97" s="27"/>
       <c r="M97" s="16"/>
       <c r="N97" s="11"/>
-      <c r="O97" s="23"/>
+      <c r="O97" s="22"/>
     </row>
     <row r="98" ht="15.75" spans="1:15">
       <c r="A98" s="11"/>
@@ -3074,30 +3046,30 @@
       <c r="F98" s="15"/>
       <c r="G98" s="16"/>
       <c r="H98" s="17"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="23"/>
+      <c r="I98" s="21"/>
+      <c r="J98" s="22"/>
       <c r="K98" s="15"/>
-      <c r="L98" s="28"/>
+      <c r="L98" s="27"/>
       <c r="M98" s="16"/>
       <c r="N98" s="11"/>
-      <c r="O98" s="23"/>
+      <c r="O98" s="22"/>
     </row>
     <row r="99" ht="15.75" spans="1:15">
       <c r="A99" s="11"/>
       <c r="B99" s="15"/>
       <c r="C99" s="13"/>
-      <c r="D99" s="30"/>
+      <c r="D99" s="29"/>
       <c r="E99" s="15"/>
       <c r="F99" s="15"/>
       <c r="G99" s="16"/>
       <c r="H99" s="17"/>
-      <c r="I99" s="22"/>
-      <c r="J99" s="23"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="22"/>
       <c r="K99" s="15"/>
-      <c r="L99" s="28"/>
+      <c r="L99" s="27"/>
       <c r="M99" s="16"/>
       <c r="N99" s="11"/>
-      <c r="O99" s="23"/>
+      <c r="O99" s="22"/>
     </row>
     <row r="100" ht="15.75" spans="1:15">
       <c r="A100" s="11"/>
@@ -3108,13 +3080,13 @@
       <c r="F100" s="15"/>
       <c r="G100" s="16"/>
       <c r="H100" s="17"/>
-      <c r="I100" s="22"/>
-      <c r="J100" s="23"/>
+      <c r="I100" s="21"/>
+      <c r="J100" s="22"/>
       <c r="K100" s="15"/>
-      <c r="L100" s="28"/>
+      <c r="L100" s="27"/>
       <c r="M100" s="16"/>
       <c r="N100" s="11"/>
-      <c r="O100" s="23"/>
+      <c r="O100" s="22"/>
     </row>
     <row r="101" ht="15.75" spans="1:15">
       <c r="A101" s="11"/>
@@ -3125,13 +3097,13 @@
       <c r="F101" s="15"/>
       <c r="G101" s="16"/>
       <c r="H101" s="17"/>
-      <c r="I101" s="22"/>
-      <c r="J101" s="23"/>
+      <c r="I101" s="21"/>
+      <c r="J101" s="22"/>
       <c r="K101" s="15"/>
-      <c r="L101" s="28"/>
+      <c r="L101" s="27"/>
       <c r="M101" s="16"/>
       <c r="N101" s="11"/>
-      <c r="O101" s="23"/>
+      <c r="O101" s="22"/>
     </row>
     <row r="102" ht="15.75" spans="1:15">
       <c r="A102" s="11"/>
@@ -3142,13 +3114,13 @@
       <c r="F102" s="15"/>
       <c r="G102" s="16"/>
       <c r="H102" s="17"/>
-      <c r="I102" s="22"/>
-      <c r="J102" s="23"/>
+      <c r="I102" s="21"/>
+      <c r="J102" s="22"/>
       <c r="K102" s="15"/>
-      <c r="L102" s="28"/>
+      <c r="L102" s="27"/>
       <c r="M102" s="16"/>
       <c r="N102" s="11"/>
-      <c r="O102" s="23"/>
+      <c r="O102" s="22"/>
     </row>
     <row r="103" ht="15.75" spans="1:15">
       <c r="A103" s="11"/>
@@ -3159,13 +3131,13 @@
       <c r="F103" s="15"/>
       <c r="G103" s="16"/>
       <c r="H103" s="17"/>
-      <c r="I103" s="22"/>
-      <c r="J103" s="23"/>
+      <c r="I103" s="21"/>
+      <c r="J103" s="22"/>
       <c r="K103" s="15"/>
-      <c r="L103" s="28"/>
+      <c r="L103" s="27"/>
       <c r="M103" s="16"/>
       <c r="N103" s="11"/>
-      <c r="O103" s="23"/>
+      <c r="O103" s="22"/>
     </row>
     <row r="104" ht="15.75" spans="1:15">
       <c r="A104" s="11"/>
@@ -3176,13 +3148,13 @@
       <c r="F104" s="15"/>
       <c r="G104" s="16"/>
       <c r="H104" s="17"/>
-      <c r="I104" s="22"/>
-      <c r="J104" s="23"/>
+      <c r="I104" s="21"/>
+      <c r="J104" s="22"/>
       <c r="K104" s="15"/>
-      <c r="L104" s="28"/>
+      <c r="L104" s="27"/>
       <c r="M104" s="16"/>
       <c r="N104" s="11"/>
-      <c r="O104" s="23"/>
+      <c r="O104" s="22"/>
     </row>
     <row r="105" ht="15.75" spans="1:15">
       <c r="A105" s="11"/>
@@ -3193,13 +3165,13 @@
       <c r="F105" s="15"/>
       <c r="G105" s="16"/>
       <c r="H105" s="17"/>
-      <c r="I105" s="22"/>
-      <c r="J105" s="23"/>
+      <c r="I105" s="21"/>
+      <c r="J105" s="22"/>
       <c r="K105" s="15"/>
-      <c r="L105" s="28"/>
+      <c r="L105" s="27"/>
       <c r="M105" s="16"/>
       <c r="N105" s="11"/>
-      <c r="O105" s="23"/>
+      <c r="O105" s="22"/>
     </row>
     <row r="106" ht="15.75" spans="1:15">
       <c r="A106" s="11"/>
@@ -3210,13 +3182,13 @@
       <c r="F106" s="15"/>
       <c r="G106" s="16"/>
       <c r="H106" s="17"/>
-      <c r="I106" s="22"/>
-      <c r="J106" s="23"/>
+      <c r="I106" s="21"/>
+      <c r="J106" s="22"/>
       <c r="K106" s="15"/>
-      <c r="L106" s="28"/>
+      <c r="L106" s="27"/>
       <c r="M106" s="16"/>
       <c r="N106" s="11"/>
-      <c r="O106" s="23"/>
+      <c r="O106" s="22"/>
     </row>
     <row r="107" ht="15.75" spans="1:15">
       <c r="A107" s="11"/>
@@ -3227,13 +3199,13 @@
       <c r="F107" s="15"/>
       <c r="G107" s="16"/>
       <c r="H107" s="17"/>
-      <c r="I107" s="22"/>
-      <c r="J107" s="23"/>
+      <c r="I107" s="21"/>
+      <c r="J107" s="22"/>
       <c r="K107" s="15"/>
-      <c r="L107" s="28"/>
+      <c r="L107" s="27"/>
       <c r="M107" s="16"/>
       <c r="N107" s="11"/>
-      <c r="O107" s="23"/>
+      <c r="O107" s="22"/>
     </row>
     <row r="108" ht="15.75" spans="1:15">
       <c r="A108" s="11"/>
@@ -3244,13 +3216,13 @@
       <c r="F108" s="15"/>
       <c r="G108" s="16"/>
       <c r="H108" s="17"/>
-      <c r="I108" s="22"/>
-      <c r="J108" s="23"/>
+      <c r="I108" s="21"/>
+      <c r="J108" s="22"/>
       <c r="K108" s="15"/>
-      <c r="L108" s="28"/>
+      <c r="L108" s="27"/>
       <c r="M108" s="16"/>
       <c r="N108" s="11"/>
-      <c r="O108" s="23"/>
+      <c r="O108" s="22"/>
     </row>
     <row r="109" ht="15.75" spans="1:15">
       <c r="A109" s="11"/>
@@ -3261,13 +3233,13 @@
       <c r="F109" s="15"/>
       <c r="G109" s="16"/>
       <c r="H109" s="17"/>
-      <c r="I109" s="22"/>
-      <c r="J109" s="23"/>
+      <c r="I109" s="21"/>
+      <c r="J109" s="22"/>
       <c r="K109" s="15"/>
-      <c r="L109" s="28"/>
+      <c r="L109" s="27"/>
       <c r="M109" s="16"/>
       <c r="N109" s="11"/>
-      <c r="O109" s="23"/>
+      <c r="O109" s="22"/>
     </row>
     <row r="110" ht="15.75" spans="1:15">
       <c r="A110" s="11"/>
@@ -3278,30 +3250,30 @@
       <c r="F110" s="15"/>
       <c r="G110" s="16"/>
       <c r="H110" s="17"/>
-      <c r="I110" s="22"/>
-      <c r="J110" s="23"/>
+      <c r="I110" s="21"/>
+      <c r="J110" s="22"/>
       <c r="K110" s="15"/>
-      <c r="L110" s="28"/>
+      <c r="L110" s="27"/>
       <c r="M110" s="16"/>
       <c r="N110" s="11"/>
-      <c r="O110" s="23"/>
+      <c r="O110" s="22"/>
     </row>
     <row r="111" ht="15.75" spans="1:15">
       <c r="A111" s="11"/>
       <c r="B111" s="15"/>
       <c r="C111" s="13"/>
-      <c r="D111" s="31"/>
+      <c r="D111" s="30"/>
       <c r="E111" s="15"/>
       <c r="F111" s="15"/>
       <c r="G111" s="16"/>
       <c r="H111" s="17"/>
-      <c r="I111" s="22"/>
-      <c r="J111" s="23"/>
+      <c r="I111" s="21"/>
+      <c r="J111" s="22"/>
       <c r="K111" s="15"/>
-      <c r="L111" s="28"/>
+      <c r="L111" s="27"/>
       <c r="M111" s="16"/>
       <c r="N111" s="11"/>
-      <c r="O111" s="23"/>
+      <c r="O111" s="22"/>
     </row>
     <row r="112" ht="15.75" spans="1:15">
       <c r="A112" s="11"/>
@@ -3312,13 +3284,13 @@
       <c r="F112" s="15"/>
       <c r="G112" s="16"/>
       <c r="H112" s="17"/>
-      <c r="I112" s="22"/>
-      <c r="J112" s="23"/>
+      <c r="I112" s="21"/>
+      <c r="J112" s="22"/>
       <c r="K112" s="15"/>
-      <c r="L112" s="28"/>
+      <c r="L112" s="27"/>
       <c r="M112" s="16"/>
       <c r="N112" s="11"/>
-      <c r="O112" s="23"/>
+      <c r="O112" s="22"/>
     </row>
     <row r="113" ht="15.75" spans="1:15">
       <c r="A113" s="11"/>
@@ -3329,13 +3301,13 @@
       <c r="F113" s="15"/>
       <c r="G113" s="16"/>
       <c r="H113" s="17"/>
-      <c r="I113" s="22"/>
-      <c r="J113" s="23"/>
+      <c r="I113" s="21"/>
+      <c r="J113" s="22"/>
       <c r="K113" s="15"/>
-      <c r="L113" s="28"/>
+      <c r="L113" s="27"/>
       <c r="M113" s="16"/>
       <c r="N113" s="11"/>
-      <c r="O113" s="23"/>
+      <c r="O113" s="22"/>
     </row>
     <row r="114" ht="15.75" spans="1:15">
       <c r="A114" s="11"/>
@@ -3346,13 +3318,13 @@
       <c r="F114" s="15"/>
       <c r="G114" s="16"/>
       <c r="H114" s="17"/>
-      <c r="I114" s="22"/>
-      <c r="J114" s="23"/>
+      <c r="I114" s="21"/>
+      <c r="J114" s="22"/>
       <c r="K114" s="15"/>
-      <c r="L114" s="28"/>
+      <c r="L114" s="27"/>
       <c r="M114" s="16"/>
       <c r="N114" s="11"/>
-      <c r="O114" s="23"/>
+      <c r="O114" s="22"/>
     </row>
     <row r="115" ht="15.75" spans="1:15">
       <c r="A115" s="11"/>
@@ -3363,13 +3335,13 @@
       <c r="F115" s="15"/>
       <c r="G115" s="16"/>
       <c r="H115" s="17"/>
-      <c r="I115" s="22"/>
-      <c r="J115" s="23"/>
+      <c r="I115" s="21"/>
+      <c r="J115" s="22"/>
       <c r="K115" s="15"/>
-      <c r="L115" s="28"/>
+      <c r="L115" s="27"/>
       <c r="M115" s="16"/>
       <c r="N115" s="11"/>
-      <c r="O115" s="23"/>
+      <c r="O115" s="22"/>
     </row>
     <row r="116" ht="15.75" spans="1:15">
       <c r="A116" s="11"/>
@@ -3380,13 +3352,13 @@
       <c r="F116" s="15"/>
       <c r="G116" s="16"/>
       <c r="H116" s="17"/>
-      <c r="I116" s="22"/>
-      <c r="J116" s="23"/>
+      <c r="I116" s="21"/>
+      <c r="J116" s="22"/>
       <c r="K116" s="15"/>
-      <c r="L116" s="28"/>
+      <c r="L116" s="27"/>
       <c r="M116" s="16"/>
       <c r="N116" s="11"/>
-      <c r="O116" s="23"/>
+      <c r="O116" s="22"/>
     </row>
     <row r="117" ht="15.75" spans="1:15">
       <c r="A117" s="11"/>
@@ -3397,13 +3369,13 @@
       <c r="F117" s="15"/>
       <c r="G117" s="16"/>
       <c r="H117" s="17"/>
-      <c r="I117" s="22"/>
-      <c r="J117" s="23"/>
+      <c r="I117" s="21"/>
+      <c r="J117" s="22"/>
       <c r="K117" s="15"/>
-      <c r="L117" s="28"/>
+      <c r="L117" s="27"/>
       <c r="M117" s="16"/>
       <c r="N117" s="11"/>
-      <c r="O117" s="23"/>
+      <c r="O117" s="22"/>
     </row>
     <row r="118" ht="15.75" spans="1:15">
       <c r="A118" s="11"/>
@@ -3414,13 +3386,13 @@
       <c r="F118" s="15"/>
       <c r="G118" s="16"/>
       <c r="H118" s="17"/>
-      <c r="I118" s="22"/>
-      <c r="J118" s="23"/>
+      <c r="I118" s="21"/>
+      <c r="J118" s="22"/>
       <c r="K118" s="15"/>
-      <c r="L118" s="28"/>
+      <c r="L118" s="27"/>
       <c r="M118" s="16"/>
       <c r="N118" s="11"/>
-      <c r="O118" s="23"/>
+      <c r="O118" s="22"/>
     </row>
     <row r="119" ht="15.75" spans="1:15">
       <c r="A119" s="11"/>
@@ -3431,13 +3403,13 @@
       <c r="F119" s="15"/>
       <c r="G119" s="16"/>
       <c r="H119" s="17"/>
-      <c r="I119" s="22"/>
-      <c r="J119" s="23"/>
+      <c r="I119" s="21"/>
+      <c r="J119" s="22"/>
       <c r="K119" s="15"/>
-      <c r="L119" s="28"/>
+      <c r="L119" s="27"/>
       <c r="M119" s="16"/>
       <c r="N119" s="11"/>
-      <c r="O119" s="23"/>
+      <c r="O119" s="22"/>
     </row>
     <row r="120" ht="15.75" spans="1:15">
       <c r="A120" s="11"/>
@@ -3448,13 +3420,13 @@
       <c r="F120" s="15"/>
       <c r="G120" s="16"/>
       <c r="H120" s="17"/>
-      <c r="I120" s="22"/>
-      <c r="J120" s="23"/>
+      <c r="I120" s="21"/>
+      <c r="J120" s="22"/>
       <c r="K120" s="15"/>
-      <c r="L120" s="28"/>
+      <c r="L120" s="27"/>
       <c r="M120" s="16"/>
       <c r="N120" s="11"/>
-      <c r="O120" s="23"/>
+      <c r="O120" s="22"/>
     </row>
     <row r="121" ht="15.75" spans="1:15">
       <c r="A121" s="11"/>
@@ -3465,13 +3437,13 @@
       <c r="F121" s="15"/>
       <c r="G121" s="16"/>
       <c r="H121" s="17"/>
-      <c r="I121" s="22"/>
-      <c r="J121" s="23"/>
+      <c r="I121" s="21"/>
+      <c r="J121" s="22"/>
       <c r="K121" s="15"/>
-      <c r="L121" s="28"/>
+      <c r="L121" s="27"/>
       <c r="M121" s="16"/>
       <c r="N121" s="11"/>
-      <c r="O121" s="23"/>
+      <c r="O121" s="22"/>
     </row>
     <row r="122" ht="15.75" spans="1:15">
       <c r="A122" s="11"/>
@@ -3482,13 +3454,13 @@
       <c r="F122" s="15"/>
       <c r="G122" s="16"/>
       <c r="H122" s="17"/>
-      <c r="I122" s="22"/>
-      <c r="J122" s="23"/>
+      <c r="I122" s="21"/>
+      <c r="J122" s="22"/>
       <c r="K122" s="15"/>
-      <c r="L122" s="28"/>
+      <c r="L122" s="27"/>
       <c r="M122" s="16"/>
       <c r="N122" s="11"/>
-      <c r="O122" s="23"/>
+      <c r="O122" s="22"/>
     </row>
     <row r="123" ht="15.75" spans="1:15">
       <c r="A123" s="11"/>
@@ -3499,13 +3471,13 @@
       <c r="F123" s="15"/>
       <c r="G123" s="16"/>
       <c r="H123" s="17"/>
-      <c r="I123" s="22"/>
-      <c r="J123" s="23"/>
+      <c r="I123" s="21"/>
+      <c r="J123" s="22"/>
       <c r="K123" s="15"/>
-      <c r="L123" s="28"/>
+      <c r="L123" s="27"/>
       <c r="M123" s="16"/>
       <c r="N123" s="11"/>
-      <c r="O123" s="23"/>
+      <c r="O123" s="22"/>
     </row>
     <row r="124" ht="15.75" spans="1:15">
       <c r="A124" s="11"/>
@@ -3516,13 +3488,13 @@
       <c r="F124" s="15"/>
       <c r="G124" s="16"/>
       <c r="H124" s="17"/>
-      <c r="I124" s="22"/>
-      <c r="J124" s="23"/>
+      <c r="I124" s="21"/>
+      <c r="J124" s="22"/>
       <c r="K124" s="15"/>
-      <c r="L124" s="28"/>
+      <c r="L124" s="27"/>
       <c r="M124" s="16"/>
       <c r="N124" s="11"/>
-      <c r="O124" s="23"/>
+      <c r="O124" s="22"/>
     </row>
     <row r="125" ht="15.75" spans="1:15">
       <c r="A125" s="11"/>
@@ -3533,13 +3505,13 @@
       <c r="F125" s="15"/>
       <c r="G125" s="16"/>
       <c r="H125" s="17"/>
-      <c r="I125" s="22"/>
-      <c r="J125" s="23"/>
+      <c r="I125" s="21"/>
+      <c r="J125" s="22"/>
       <c r="K125" s="15"/>
-      <c r="L125" s="28"/>
+      <c r="L125" s="27"/>
       <c r="M125" s="16"/>
       <c r="N125" s="11"/>
-      <c r="O125" s="23"/>
+      <c r="O125" s="22"/>
     </row>
     <row r="126" ht="15.75" spans="1:15">
       <c r="A126" s="11"/>
@@ -3550,13 +3522,13 @@
       <c r="F126" s="15"/>
       <c r="G126" s="16"/>
       <c r="H126" s="17"/>
-      <c r="I126" s="22"/>
-      <c r="J126" s="23"/>
+      <c r="I126" s="21"/>
+      <c r="J126" s="22"/>
       <c r="K126" s="15"/>
-      <c r="L126" s="28"/>
+      <c r="L126" s="27"/>
       <c r="M126" s="16"/>
       <c r="N126" s="11"/>
-      <c r="O126" s="23"/>
+      <c r="O126" s="22"/>
     </row>
     <row r="127" ht="15.75" spans="1:15">
       <c r="A127" s="11"/>
@@ -3567,13 +3539,13 @@
       <c r="F127" s="15"/>
       <c r="G127" s="16"/>
       <c r="H127" s="17"/>
-      <c r="I127" s="22"/>
-      <c r="J127" s="23"/>
+      <c r="I127" s="21"/>
+      <c r="J127" s="22"/>
       <c r="K127" s="15"/>
-      <c r="L127" s="28"/>
+      <c r="L127" s="27"/>
       <c r="M127" s="16"/>
       <c r="N127" s="11"/>
-      <c r="O127" s="23"/>
+      <c r="O127" s="22"/>
     </row>
     <row r="128" ht="15.75" spans="1:15">
       <c r="A128" s="11"/>
@@ -3584,13 +3556,13 @@
       <c r="F128" s="15"/>
       <c r="G128" s="16"/>
       <c r="H128" s="17"/>
-      <c r="I128" s="22"/>
-      <c r="J128" s="23"/>
+      <c r="I128" s="21"/>
+      <c r="J128" s="22"/>
       <c r="K128" s="15"/>
-      <c r="L128" s="28"/>
+      <c r="L128" s="27"/>
       <c r="M128" s="16"/>
       <c r="N128" s="11"/>
-      <c r="O128" s="23"/>
+      <c r="O128" s="22"/>
     </row>
     <row r="129" ht="15.75" spans="1:15">
       <c r="A129" s="11"/>
@@ -3601,13 +3573,13 @@
       <c r="F129" s="15"/>
       <c r="G129" s="16"/>
       <c r="H129" s="17"/>
-      <c r="I129" s="22"/>
-      <c r="J129" s="23"/>
+      <c r="I129" s="21"/>
+      <c r="J129" s="22"/>
       <c r="K129" s="15"/>
-      <c r="L129" s="28"/>
+      <c r="L129" s="27"/>
       <c r="M129" s="16"/>
       <c r="N129" s="11"/>
-      <c r="O129" s="23"/>
+      <c r="O129" s="22"/>
     </row>
     <row r="130" ht="15.75" spans="1:15">
       <c r="A130" s="11"/>
@@ -3618,13 +3590,13 @@
       <c r="F130" s="15"/>
       <c r="G130" s="16"/>
       <c r="H130" s="17"/>
-      <c r="I130" s="22"/>
-      <c r="J130" s="23"/>
+      <c r="I130" s="21"/>
+      <c r="J130" s="22"/>
       <c r="K130" s="15"/>
-      <c r="L130" s="28"/>
+      <c r="L130" s="27"/>
       <c r="M130" s="16"/>
       <c r="N130" s="11"/>
-      <c r="O130" s="23"/>
+      <c r="O130" s="22"/>
     </row>
     <row r="131" ht="15.75" spans="1:15">
       <c r="A131" s="11"/>
@@ -3635,13 +3607,13 @@
       <c r="F131" s="15"/>
       <c r="G131" s="16"/>
       <c r="H131" s="17"/>
-      <c r="I131" s="22"/>
-      <c r="J131" s="23"/>
+      <c r="I131" s="21"/>
+      <c r="J131" s="22"/>
       <c r="K131" s="15"/>
-      <c r="L131" s="28"/>
+      <c r="L131" s="27"/>
       <c r="M131" s="16"/>
       <c r="N131" s="11"/>
-      <c r="O131" s="23"/>
+      <c r="O131" s="22"/>
     </row>
     <row r="132" ht="15.75" spans="1:15">
       <c r="A132" s="11"/>
@@ -3652,13 +3624,13 @@
       <c r="F132" s="15"/>
       <c r="G132" s="16"/>
       <c r="H132" s="17"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="23"/>
+      <c r="I132" s="21"/>
+      <c r="J132" s="22"/>
       <c r="K132" s="15"/>
-      <c r="L132" s="28"/>
+      <c r="L132" s="27"/>
       <c r="M132" s="16"/>
       <c r="N132" s="11"/>
-      <c r="O132" s="23"/>
+      <c r="O132" s="22"/>
     </row>
     <row r="133" ht="15.75" spans="1:15">
       <c r="A133" s="11"/>
@@ -3669,13 +3641,13 @@
       <c r="F133" s="15"/>
       <c r="G133" s="16"/>
       <c r="H133" s="17"/>
-      <c r="I133" s="22"/>
-      <c r="J133" s="23"/>
+      <c r="I133" s="21"/>
+      <c r="J133" s="22"/>
       <c r="K133" s="15"/>
-      <c r="L133" s="28"/>
+      <c r="L133" s="27"/>
       <c r="M133" s="16"/>
       <c r="N133" s="11"/>
-      <c r="O133" s="23"/>
+      <c r="O133" s="22"/>
     </row>
     <row r="134" ht="15.75" spans="1:15">
       <c r="A134" s="11"/>
@@ -3686,13 +3658,13 @@
       <c r="F134" s="15"/>
       <c r="G134" s="16"/>
       <c r="H134" s="17"/>
-      <c r="I134" s="22"/>
-      <c r="J134" s="23"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="22"/>
       <c r="K134" s="15"/>
-      <c r="L134" s="28"/>
+      <c r="L134" s="27"/>
       <c r="M134" s="16"/>
       <c r="N134" s="11"/>
-      <c r="O134" s="23"/>
+      <c r="O134" s="22"/>
     </row>
     <row r="135" ht="15.75" spans="1:14">
       <c r="A135" s="11"/>
@@ -3703,10 +3675,10 @@
       <c r="F135" s="15"/>
       <c r="G135" s="16"/>
       <c r="H135" s="17"/>
-      <c r="I135" s="22"/>
-      <c r="J135" s="23"/>
+      <c r="I135" s="21"/>
+      <c r="J135" s="22"/>
       <c r="K135" s="15"/>
-      <c r="L135" s="28"/>
+      <c r="L135" s="27"/>
       <c r="M135" s="16"/>
       <c r="N135" s="11"/>
     </row>
@@ -3719,9 +3691,9 @@
       <c r="F136" s="15"/>
       <c r="G136" s="16"/>
       <c r="H136" s="17"/>
-      <c r="I136" s="22"/>
+      <c r="I136" s="21"/>
       <c r="K136" s="15"/>
-      <c r="L136" s="28"/>
+      <c r="L136" s="27"/>
       <c r="M136" s="16"/>
       <c r="N136" s="11"/>
     </row>
@@ -3734,9 +3706,9 @@
       <c r="F137" s="15"/>
       <c r="G137" s="16"/>
       <c r="H137" s="17"/>
-      <c r="I137" s="22"/>
+      <c r="I137" s="21"/>
       <c r="K137" s="15"/>
-      <c r="L137" s="28"/>
+      <c r="L137" s="27"/>
       <c r="M137" s="16"/>
       <c r="N137" s="11"/>
     </row>
@@ -3749,9 +3721,9 @@
       <c r="F138" s="15"/>
       <c r="G138" s="16"/>
       <c r="H138" s="17"/>
-      <c r="I138" s="22"/>
+      <c r="I138" s="21"/>
       <c r="K138" s="15"/>
-      <c r="L138" s="28"/>
+      <c r="L138" s="27"/>
       <c r="M138" s="16"/>
       <c r="N138" s="11"/>
     </row>
@@ -3764,9 +3736,9 @@
       <c r="F139" s="15"/>
       <c r="G139" s="16"/>
       <c r="H139" s="17"/>
-      <c r="I139" s="22"/>
+      <c r="I139" s="21"/>
       <c r="K139" s="15"/>
-      <c r="L139" s="28"/>
+      <c r="L139" s="27"/>
       <c r="M139" s="16"/>
       <c r="N139" s="11"/>
     </row>
@@ -3779,9 +3751,9 @@
       <c r="F140" s="15"/>
       <c r="G140" s="16"/>
       <c r="H140" s="17"/>
-      <c r="I140" s="22"/>
+      <c r="I140" s="21"/>
       <c r="K140" s="15"/>
-      <c r="L140" s="28"/>
+      <c r="L140" s="27"/>
       <c r="M140" s="16"/>
       <c r="N140" s="11"/>
     </row>
@@ -3794,9 +3766,9 @@
       <c r="F141" s="15"/>
       <c r="G141" s="16"/>
       <c r="H141" s="17"/>
-      <c r="I141" s="22"/>
+      <c r="I141" s="21"/>
       <c r="K141" s="15"/>
-      <c r="L141" s="28"/>
+      <c r="L141" s="27"/>
       <c r="M141" s="16"/>
       <c r="N141" s="11"/>
     </row>
@@ -3809,9 +3781,9 @@
       <c r="F142" s="15"/>
       <c r="G142" s="16"/>
       <c r="H142" s="17"/>
-      <c r="I142" s="22"/>
+      <c r="I142" s="21"/>
       <c r="K142" s="15"/>
-      <c r="L142" s="28"/>
+      <c r="L142" s="27"/>
       <c r="M142" s="16"/>
       <c r="N142" s="11"/>
     </row>
@@ -3824,9 +3796,9 @@
       <c r="F143" s="15"/>
       <c r="G143" s="16"/>
       <c r="H143" s="17"/>
-      <c r="I143" s="22"/>
+      <c r="I143" s="21"/>
       <c r="K143" s="15"/>
-      <c r="L143" s="28"/>
+      <c r="L143" s="27"/>
       <c r="M143" s="16"/>
       <c r="N143" s="11"/>
     </row>
@@ -3839,9 +3811,9 @@
       <c r="F144" s="15"/>
       <c r="G144" s="16"/>
       <c r="H144" s="17"/>
-      <c r="I144" s="22"/>
+      <c r="I144" s="21"/>
       <c r="K144" s="15"/>
-      <c r="L144" s="28"/>
+      <c r="L144" s="27"/>
       <c r="M144" s="16"/>
       <c r="N144" s="11"/>
     </row>
@@ -3854,9 +3826,9 @@
       <c r="F145" s="15"/>
       <c r="G145" s="16"/>
       <c r="H145" s="17"/>
-      <c r="I145" s="22"/>
+      <c r="I145" s="21"/>
       <c r="K145" s="15"/>
-      <c r="L145" s="28"/>
+      <c r="L145" s="27"/>
       <c r="M145" s="16"/>
       <c r="N145" s="11"/>
     </row>
@@ -3869,9 +3841,9 @@
       <c r="F146" s="15"/>
       <c r="G146" s="16"/>
       <c r="H146" s="17"/>
-      <c r="I146" s="22"/>
+      <c r="I146" s="21"/>
       <c r="K146" s="15"/>
-      <c r="L146" s="28"/>
+      <c r="L146" s="27"/>
       <c r="M146" s="16"/>
       <c r="N146" s="11"/>
     </row>
@@ -3884,9 +3856,9 @@
       <c r="F147" s="15"/>
       <c r="G147" s="16"/>
       <c r="H147" s="17"/>
-      <c r="I147" s="22"/>
+      <c r="I147" s="21"/>
       <c r="K147" s="15"/>
-      <c r="L147" s="28"/>
+      <c r="L147" s="27"/>
       <c r="M147" s="16"/>
       <c r="N147" s="11"/>
     </row>
@@ -3899,9 +3871,9 @@
       <c r="F148" s="15"/>
       <c r="G148" s="16"/>
       <c r="H148" s="17"/>
-      <c r="I148" s="22"/>
+      <c r="I148" s="21"/>
       <c r="K148" s="15"/>
-      <c r="L148" s="28"/>
+      <c r="L148" s="27"/>
       <c r="M148" s="16"/>
       <c r="N148" s="11"/>
     </row>
@@ -3914,9 +3886,9 @@
       <c r="F149" s="15"/>
       <c r="G149" s="16"/>
       <c r="H149" s="17"/>
-      <c r="I149" s="22"/>
+      <c r="I149" s="21"/>
       <c r="K149" s="15"/>
-      <c r="L149" s="28"/>
+      <c r="L149" s="27"/>
       <c r="M149" s="16"/>
       <c r="N149" s="11"/>
     </row>
@@ -3929,9 +3901,9 @@
       <c r="F150" s="15"/>
       <c r="G150" s="16"/>
       <c r="H150" s="17"/>
-      <c r="I150" s="22"/>
+      <c r="I150" s="21"/>
       <c r="K150" s="15"/>
-      <c r="L150" s="28"/>
+      <c r="L150" s="27"/>
       <c r="M150" s="16"/>
       <c r="N150" s="11"/>
     </row>
@@ -3944,9 +3916,9 @@
       <c r="F151" s="15"/>
       <c r="G151" s="16"/>
       <c r="H151" s="17"/>
-      <c r="I151" s="22"/>
+      <c r="I151" s="21"/>
       <c r="K151" s="15"/>
-      <c r="L151" s="28"/>
+      <c r="L151" s="27"/>
       <c r="M151" s="16"/>
       <c r="N151" s="11"/>
     </row>
@@ -3959,9 +3931,9 @@
       <c r="F152" s="15"/>
       <c r="G152" s="16"/>
       <c r="H152" s="17"/>
-      <c r="I152" s="22"/>
+      <c r="I152" s="21"/>
       <c r="K152" s="15"/>
-      <c r="L152" s="28"/>
+      <c r="L152" s="27"/>
       <c r="M152" s="16"/>
       <c r="N152" s="11"/>
     </row>
@@ -3974,9 +3946,9 @@
       <c r="F153" s="15"/>
       <c r="G153" s="16"/>
       <c r="H153" s="17"/>
-      <c r="I153" s="22"/>
+      <c r="I153" s="21"/>
       <c r="K153" s="15"/>
-      <c r="L153" s="28"/>
+      <c r="L153" s="27"/>
       <c r="M153" s="16"/>
       <c r="N153" s="11"/>
     </row>
@@ -3989,9 +3961,9 @@
       <c r="F154" s="15"/>
       <c r="G154" s="16"/>
       <c r="H154" s="17"/>
-      <c r="I154" s="22"/>
+      <c r="I154" s="21"/>
       <c r="K154" s="15"/>
-      <c r="L154" s="28"/>
+      <c r="L154" s="27"/>
       <c r="M154" s="16"/>
       <c r="N154" s="11"/>
     </row>
@@ -4004,9 +3976,9 @@
       <c r="F155" s="15"/>
       <c r="G155" s="16"/>
       <c r="H155" s="17"/>
-      <c r="I155" s="22"/>
+      <c r="I155" s="21"/>
       <c r="K155" s="15"/>
-      <c r="L155" s="28"/>
+      <c r="L155" s="27"/>
       <c r="M155" s="16"/>
       <c r="N155" s="11"/>
     </row>
@@ -4019,9 +3991,9 @@
       <c r="F156" s="15"/>
       <c r="G156" s="16"/>
       <c r="H156" s="17"/>
-      <c r="I156" s="22"/>
+      <c r="I156" s="21"/>
       <c r="K156" s="15"/>
-      <c r="L156" s="28"/>
+      <c r="L156" s="27"/>
       <c r="M156" s="16"/>
       <c r="N156" s="11"/>
     </row>
@@ -4029,3423 +4001,3423 @@
       <c r="A157" s="11"/>
       <c r="B157" s="15"/>
       <c r="C157" s="13"/>
-      <c r="D157" s="32"/>
+      <c r="D157" s="31"/>
       <c r="E157" s="15"/>
       <c r="F157" s="15"/>
       <c r="G157" s="16"/>
       <c r="H157"/>
-      <c r="I157" s="22"/>
+      <c r="I157" s="21"/>
       <c r="K157" s="15"/>
-      <c r="L157" s="28"/>
+      <c r="L157" s="27"/>
       <c r="M157" s="16"/>
     </row>
     <row r="158" ht="15.75" spans="1:13">
       <c r="A158" s="11"/>
       <c r="B158" s="15"/>
       <c r="C158" s="13"/>
-      <c r="D158" s="32"/>
+      <c r="D158" s="31"/>
       <c r="E158" s="15"/>
       <c r="F158" s="15"/>
       <c r="G158" s="16"/>
       <c r="H158"/>
-      <c r="I158" s="22"/>
+      <c r="I158" s="21"/>
       <c r="K158" s="15"/>
-      <c r="L158" s="28"/>
+      <c r="L158" s="27"/>
       <c r="M158" s="16"/>
     </row>
     <row r="159" ht="15.75" spans="1:13">
       <c r="A159" s="11"/>
       <c r="B159" s="15"/>
       <c r="C159" s="13"/>
-      <c r="D159" s="32"/>
+      <c r="D159" s="31"/>
       <c r="E159" s="15"/>
       <c r="F159" s="15"/>
       <c r="G159" s="16"/>
       <c r="H159"/>
-      <c r="I159" s="22"/>
+      <c r="I159" s="21"/>
       <c r="K159" s="15"/>
-      <c r="L159" s="28"/>
+      <c r="L159" s="27"/>
       <c r="M159" s="16"/>
     </row>
     <row r="160" ht="15.75" spans="1:13">
       <c r="A160" s="11"/>
       <c r="B160" s="15"/>
       <c r="C160" s="13"/>
-      <c r="D160" s="32"/>
+      <c r="D160" s="31"/>
       <c r="E160" s="15"/>
       <c r="F160" s="15"/>
       <c r="G160" s="16"/>
       <c r="H160"/>
-      <c r="I160" s="22"/>
+      <c r="I160" s="21"/>
       <c r="K160" s="15"/>
-      <c r="L160" s="28"/>
+      <c r="L160" s="27"/>
       <c r="M160" s="16"/>
     </row>
     <row r="161" ht="15.75" spans="1:13">
       <c r="A161" s="11"/>
       <c r="B161" s="15"/>
       <c r="C161" s="13"/>
-      <c r="D161" s="32"/>
+      <c r="D161" s="31"/>
       <c r="E161" s="15"/>
       <c r="F161" s="15"/>
       <c r="G161" s="16"/>
       <c r="H161"/>
-      <c r="I161" s="22"/>
+      <c r="I161" s="21"/>
       <c r="K161" s="15"/>
-      <c r="L161" s="28"/>
+      <c r="L161" s="27"/>
       <c r="M161" s="16"/>
     </row>
     <row r="162" ht="15.75" spans="1:13">
       <c r="A162" s="11"/>
       <c r="B162" s="15"/>
       <c r="C162" s="13"/>
-      <c r="D162" s="32"/>
+      <c r="D162" s="31"/>
       <c r="E162" s="15"/>
       <c r="F162" s="15"/>
       <c r="G162" s="16"/>
       <c r="H162"/>
-      <c r="I162" s="22"/>
+      <c r="I162" s="21"/>
       <c r="K162" s="15"/>
-      <c r="L162" s="28"/>
+      <c r="L162" s="27"/>
       <c r="M162" s="16"/>
     </row>
     <row r="163" ht="15.75" spans="1:13">
       <c r="A163" s="11"/>
       <c r="B163" s="15"/>
       <c r="C163" s="13"/>
-      <c r="D163" s="32"/>
+      <c r="D163" s="31"/>
       <c r="E163" s="15"/>
       <c r="F163" s="15"/>
       <c r="G163" s="16"/>
       <c r="H163"/>
-      <c r="I163" s="22"/>
+      <c r="I163" s="21"/>
       <c r="K163" s="15"/>
-      <c r="L163" s="28"/>
+      <c r="L163" s="27"/>
       <c r="M163" s="16"/>
     </row>
     <row r="164" ht="15.75" spans="1:13">
       <c r="A164" s="11"/>
       <c r="B164" s="15"/>
       <c r="C164" s="13"/>
-      <c r="D164" s="32"/>
+      <c r="D164" s="31"/>
       <c r="E164" s="15"/>
       <c r="F164" s="15"/>
       <c r="G164" s="16"/>
       <c r="H164"/>
-      <c r="I164" s="22"/>
+      <c r="I164" s="21"/>
       <c r="K164" s="15"/>
-      <c r="L164" s="28"/>
+      <c r="L164" s="27"/>
       <c r="M164" s="16"/>
     </row>
     <row r="165" ht="15.75" spans="1:13">
       <c r="A165" s="11"/>
       <c r="B165" s="15"/>
       <c r="C165" s="13"/>
-      <c r="D165" s="33"/>
+      <c r="D165" s="32"/>
       <c r="E165" s="15"/>
       <c r="F165" s="15"/>
       <c r="G165" s="16"/>
       <c r="H165"/>
-      <c r="I165" s="22"/>
+      <c r="I165" s="21"/>
       <c r="K165" s="15"/>
-      <c r="L165" s="28"/>
+      <c r="L165" s="27"/>
       <c r="M165" s="16"/>
     </row>
     <row r="166" ht="15.75" spans="1:13">
       <c r="A166" s="11"/>
       <c r="B166" s="15"/>
       <c r="C166" s="13"/>
-      <c r="D166" s="32"/>
+      <c r="D166" s="31"/>
       <c r="E166" s="15"/>
       <c r="F166" s="15"/>
       <c r="G166" s="16"/>
       <c r="H166"/>
-      <c r="I166" s="22"/>
+      <c r="I166" s="21"/>
       <c r="K166" s="15"/>
-      <c r="L166" s="28"/>
+      <c r="L166" s="27"/>
       <c r="M166" s="16"/>
     </row>
     <row r="167" ht="15.75" spans="1:13">
       <c r="A167" s="11"/>
       <c r="B167" s="15"/>
       <c r="C167" s="13"/>
-      <c r="D167" s="32"/>
+      <c r="D167" s="31"/>
       <c r="E167" s="15"/>
       <c r="F167" s="15"/>
       <c r="G167" s="16"/>
       <c r="H167"/>
-      <c r="I167" s="22"/>
+      <c r="I167" s="21"/>
       <c r="K167" s="15"/>
-      <c r="L167" s="28"/>
+      <c r="L167" s="27"/>
       <c r="M167" s="16"/>
     </row>
     <row r="168" ht="15.75" spans="1:13">
       <c r="A168" s="11"/>
       <c r="B168" s="15"/>
       <c r="C168" s="13"/>
-      <c r="D168" s="32"/>
+      <c r="D168" s="31"/>
       <c r="E168" s="15"/>
       <c r="F168" s="15"/>
       <c r="G168" s="16"/>
       <c r="H168"/>
-      <c r="I168" s="22"/>
+      <c r="I168" s="21"/>
       <c r="K168" s="15"/>
-      <c r="L168" s="28"/>
+      <c r="L168" s="27"/>
       <c r="M168" s="16"/>
     </row>
     <row r="169" ht="15.75" spans="1:13">
       <c r="A169" s="11"/>
       <c r="B169" s="15"/>
       <c r="C169" s="13"/>
-      <c r="D169" s="33"/>
+      <c r="D169" s="32"/>
       <c r="E169" s="15"/>
       <c r="F169" s="15"/>
       <c r="G169" s="16"/>
       <c r="H169"/>
-      <c r="I169" s="22"/>
+      <c r="I169" s="21"/>
       <c r="K169" s="15"/>
-      <c r="L169" s="28"/>
+      <c r="L169" s="27"/>
       <c r="M169" s="16"/>
     </row>
     <row r="170" ht="15.75" spans="1:13">
       <c r="A170" s="11"/>
       <c r="B170" s="15"/>
       <c r="C170" s="13"/>
-      <c r="D170" s="32"/>
+      <c r="D170" s="31"/>
       <c r="E170" s="15"/>
       <c r="F170" s="15"/>
       <c r="G170" s="16"/>
       <c r="H170"/>
-      <c r="I170" s="22"/>
+      <c r="I170" s="21"/>
       <c r="K170" s="15"/>
-      <c r="L170" s="28"/>
+      <c r="L170" s="27"/>
       <c r="M170" s="16"/>
     </row>
     <row r="171" ht="15.75" spans="1:13">
       <c r="A171" s="11"/>
       <c r="B171" s="15"/>
       <c r="C171" s="13"/>
-      <c r="D171" s="32"/>
+      <c r="D171" s="31"/>
       <c r="E171" s="15"/>
       <c r="F171" s="15"/>
       <c r="G171" s="16"/>
       <c r="H171"/>
-      <c r="I171" s="22"/>
+      <c r="I171" s="21"/>
       <c r="K171" s="15"/>
-      <c r="L171" s="28"/>
+      <c r="L171" s="27"/>
       <c r="M171" s="16"/>
     </row>
     <row r="172" ht="15.75" spans="1:13">
       <c r="A172" s="11"/>
       <c r="B172" s="15"/>
       <c r="C172" s="13"/>
-      <c r="D172" s="32"/>
+      <c r="D172" s="31"/>
       <c r="E172" s="15"/>
       <c r="F172" s="15"/>
       <c r="G172" s="16"/>
       <c r="H172"/>
-      <c r="I172" s="22"/>
+      <c r="I172" s="21"/>
       <c r="K172" s="15"/>
-      <c r="L172" s="28"/>
+      <c r="L172" s="27"/>
       <c r="M172" s="16"/>
     </row>
     <row r="173" ht="15.75" spans="1:13">
       <c r="A173" s="11"/>
       <c r="B173" s="15"/>
       <c r="C173" s="13"/>
-      <c r="D173" s="32"/>
+      <c r="D173" s="31"/>
       <c r="E173" s="15"/>
       <c r="F173" s="15"/>
       <c r="G173" s="16"/>
       <c r="H173"/>
-      <c r="I173" s="22"/>
+      <c r="I173" s="21"/>
       <c r="K173" s="15"/>
-      <c r="L173" s="28"/>
+      <c r="L173" s="27"/>
       <c r="M173" s="16"/>
     </row>
     <row r="174" ht="15.75" spans="1:13">
       <c r="A174" s="11"/>
       <c r="B174" s="15"/>
       <c r="C174" s="13"/>
-      <c r="D174" s="32"/>
+      <c r="D174" s="31"/>
       <c r="E174" s="15"/>
       <c r="F174" s="15"/>
       <c r="G174" s="16"/>
       <c r="H174"/>
-      <c r="I174" s="22"/>
+      <c r="I174" s="21"/>
       <c r="K174" s="15"/>
-      <c r="L174" s="28"/>
+      <c r="L174" s="27"/>
       <c r="M174" s="16"/>
     </row>
     <row r="175" ht="15.75" spans="1:13">
       <c r="A175" s="11"/>
       <c r="B175" s="15"/>
       <c r="C175" s="13"/>
-      <c r="D175" s="32"/>
+      <c r="D175" s="31"/>
       <c r="E175" s="15"/>
       <c r="F175" s="15"/>
       <c r="G175" s="16"/>
       <c r="H175"/>
-      <c r="I175" s="22"/>
+      <c r="I175" s="21"/>
       <c r="K175" s="15"/>
-      <c r="L175" s="28"/>
+      <c r="L175" s="27"/>
       <c r="M175" s="16"/>
     </row>
     <row r="176" ht="15.75" spans="1:13">
       <c r="A176" s="11"/>
       <c r="B176" s="15"/>
       <c r="C176" s="13"/>
-      <c r="D176" s="32"/>
+      <c r="D176" s="31"/>
       <c r="E176" s="15"/>
       <c r="F176" s="15"/>
       <c r="G176" s="16"/>
       <c r="H176"/>
-      <c r="I176" s="22"/>
+      <c r="I176" s="21"/>
       <c r="K176" s="15"/>
-      <c r="L176" s="28"/>
+      <c r="L176" s="27"/>
       <c r="M176" s="16"/>
     </row>
     <row r="177" ht="15.75" spans="1:13">
       <c r="A177" s="11"/>
       <c r="B177" s="15"/>
       <c r="C177" s="13"/>
-      <c r="D177" s="32"/>
+      <c r="D177" s="31"/>
       <c r="E177" s="15"/>
       <c r="F177" s="15"/>
       <c r="G177" s="16"/>
       <c r="H177"/>
-      <c r="I177" s="22"/>
+      <c r="I177" s="21"/>
       <c r="K177" s="15"/>
-      <c r="L177" s="28"/>
+      <c r="L177" s="27"/>
       <c r="M177" s="16"/>
     </row>
     <row r="178" ht="15.75" spans="1:13">
       <c r="A178" s="11"/>
       <c r="B178" s="15"/>
       <c r="C178" s="13"/>
-      <c r="D178" s="32"/>
+      <c r="D178" s="31"/>
       <c r="E178" s="15"/>
       <c r="F178" s="15"/>
       <c r="G178" s="16"/>
       <c r="H178"/>
-      <c r="I178" s="22"/>
+      <c r="I178" s="21"/>
       <c r="K178" s="15"/>
-      <c r="L178" s="28"/>
+      <c r="L178" s="27"/>
       <c r="M178" s="16"/>
     </row>
     <row r="179" ht="15.75" spans="1:13">
       <c r="A179" s="11"/>
       <c r="B179" s="15"/>
       <c r="C179" s="13"/>
-      <c r="D179" s="32"/>
+      <c r="D179" s="31"/>
       <c r="E179" s="15"/>
       <c r="F179" s="15"/>
       <c r="G179" s="16"/>
       <c r="H179"/>
-      <c r="I179" s="22"/>
+      <c r="I179" s="21"/>
       <c r="K179" s="15"/>
-      <c r="L179" s="28"/>
+      <c r="L179" s="27"/>
       <c r="M179" s="16"/>
     </row>
     <row r="180" ht="15.75" spans="1:13">
       <c r="A180" s="11"/>
       <c r="B180" s="15"/>
       <c r="C180" s="13"/>
-      <c r="D180" s="32"/>
+      <c r="D180" s="31"/>
       <c r="E180" s="15"/>
       <c r="F180" s="15"/>
       <c r="G180" s="16"/>
       <c r="H180"/>
-      <c r="I180" s="22"/>
+      <c r="I180" s="21"/>
       <c r="K180" s="15"/>
-      <c r="L180" s="28"/>
+      <c r="L180" s="27"/>
       <c r="M180" s="16"/>
     </row>
     <row r="181" ht="15.75" spans="1:13">
       <c r="A181" s="11"/>
       <c r="B181" s="15"/>
       <c r="C181" s="13"/>
-      <c r="D181" s="32"/>
+      <c r="D181" s="31"/>
       <c r="E181" s="15"/>
       <c r="F181" s="15"/>
       <c r="G181" s="16"/>
       <c r="H181"/>
-      <c r="I181" s="22"/>
+      <c r="I181" s="21"/>
       <c r="K181" s="15"/>
-      <c r="L181" s="28"/>
+      <c r="L181" s="27"/>
       <c r="M181" s="16"/>
     </row>
     <row r="182" ht="15.75" spans="1:13">
       <c r="A182" s="11"/>
       <c r="B182" s="15"/>
       <c r="C182" s="13"/>
-      <c r="D182" s="32"/>
+      <c r="D182" s="31"/>
       <c r="E182" s="15"/>
       <c r="F182" s="15"/>
       <c r="G182" s="16"/>
       <c r="H182"/>
-      <c r="I182" s="22"/>
+      <c r="I182" s="21"/>
       <c r="K182" s="15"/>
-      <c r="L182" s="28"/>
+      <c r="L182" s="27"/>
       <c r="M182" s="16"/>
     </row>
     <row r="183" ht="15.75" spans="1:13">
       <c r="A183" s="11"/>
       <c r="B183" s="15"/>
       <c r="C183" s="13"/>
-      <c r="D183" s="32"/>
+      <c r="D183" s="31"/>
       <c r="E183" s="15"/>
       <c r="F183" s="15"/>
       <c r="G183" s="16"/>
       <c r="H183"/>
-      <c r="I183" s="22"/>
+      <c r="I183" s="21"/>
       <c r="K183" s="15"/>
-      <c r="L183" s="28"/>
+      <c r="L183" s="27"/>
       <c r="M183" s="16"/>
     </row>
     <row r="184" ht="15.75" spans="1:13">
       <c r="A184" s="11"/>
       <c r="B184" s="15"/>
       <c r="C184" s="13"/>
-      <c r="D184" s="32"/>
+      <c r="D184" s="31"/>
       <c r="E184" s="15"/>
       <c r="F184" s="15"/>
       <c r="G184" s="16"/>
       <c r="H184"/>
-      <c r="I184" s="22"/>
+      <c r="I184" s="21"/>
       <c r="K184" s="15"/>
-      <c r="L184" s="28"/>
+      <c r="L184" s="27"/>
       <c r="M184" s="16"/>
     </row>
     <row r="185" ht="15.75" spans="1:13">
       <c r="A185" s="11"/>
       <c r="B185" s="15"/>
       <c r="C185" s="13"/>
-      <c r="D185" s="32"/>
+      <c r="D185" s="31"/>
       <c r="E185" s="15"/>
       <c r="F185" s="15"/>
       <c r="G185" s="16"/>
       <c r="H185"/>
-      <c r="I185" s="22"/>
+      <c r="I185" s="21"/>
       <c r="K185" s="15"/>
-      <c r="L185" s="28"/>
+      <c r="L185" s="27"/>
       <c r="M185" s="16"/>
     </row>
     <row r="186" ht="15.75" spans="1:13">
       <c r="A186" s="11"/>
       <c r="B186" s="15"/>
       <c r="C186" s="13"/>
-      <c r="D186" s="32"/>
+      <c r="D186" s="31"/>
       <c r="E186" s="15"/>
       <c r="F186" s="15"/>
       <c r="G186" s="16"/>
       <c r="H186"/>
-      <c r="I186" s="22"/>
+      <c r="I186" s="21"/>
       <c r="K186" s="15"/>
-      <c r="L186" s="28"/>
+      <c r="L186" s="27"/>
       <c r="M186" s="16"/>
     </row>
     <row r="187" ht="15.75" spans="1:13">
       <c r="A187" s="11"/>
       <c r="B187" s="15"/>
       <c r="C187" s="13"/>
-      <c r="D187" s="32"/>
+      <c r="D187" s="31"/>
       <c r="E187" s="15"/>
       <c r="F187" s="15"/>
       <c r="G187" s="16"/>
       <c r="H187"/>
-      <c r="I187" s="22"/>
+      <c r="I187" s="21"/>
       <c r="K187" s="15"/>
-      <c r="L187" s="28"/>
+      <c r="L187" s="27"/>
       <c r="M187" s="16"/>
     </row>
     <row r="188" ht="15.75" spans="1:13">
       <c r="A188" s="11"/>
       <c r="B188" s="15"/>
       <c r="C188" s="13"/>
-      <c r="D188" s="32"/>
+      <c r="D188" s="31"/>
       <c r="E188" s="15"/>
       <c r="F188" s="15"/>
       <c r="G188" s="16"/>
       <c r="H188"/>
-      <c r="I188" s="22"/>
+      <c r="I188" s="21"/>
       <c r="K188" s="15"/>
-      <c r="L188" s="28"/>
+      <c r="L188" s="27"/>
       <c r="M188" s="16"/>
     </row>
     <row r="189" ht="15.75" spans="1:13">
       <c r="A189" s="11"/>
       <c r="B189" s="15"/>
       <c r="C189" s="13"/>
-      <c r="D189" s="32"/>
+      <c r="D189" s="31"/>
       <c r="E189" s="15"/>
       <c r="F189" s="15"/>
       <c r="G189" s="16"/>
       <c r="H189"/>
-      <c r="I189" s="22"/>
+      <c r="I189" s="21"/>
       <c r="K189" s="15"/>
-      <c r="L189" s="28"/>
+      <c r="L189" s="27"/>
       <c r="M189" s="16"/>
     </row>
     <row r="190" ht="15.75" spans="1:13">
       <c r="A190" s="11"/>
       <c r="B190" s="15"/>
       <c r="C190" s="13"/>
-      <c r="D190" s="32"/>
+      <c r="D190" s="31"/>
       <c r="E190" s="15"/>
       <c r="F190" s="15"/>
       <c r="G190" s="16"/>
       <c r="H190"/>
-      <c r="I190" s="22"/>
+      <c r="I190" s="21"/>
       <c r="K190" s="15"/>
-      <c r="L190" s="28"/>
+      <c r="L190" s="27"/>
       <c r="M190" s="16"/>
     </row>
     <row r="191" ht="15.75" spans="1:13">
       <c r="A191" s="11"/>
       <c r="B191" s="15"/>
       <c r="C191" s="13"/>
-      <c r="D191" s="32"/>
+      <c r="D191" s="31"/>
       <c r="E191" s="15"/>
       <c r="F191" s="15"/>
       <c r="G191" s="16"/>
       <c r="H191"/>
-      <c r="I191" s="22"/>
+      <c r="I191" s="21"/>
       <c r="K191" s="15"/>
-      <c r="L191" s="28"/>
+      <c r="L191" s="27"/>
       <c r="M191" s="16"/>
     </row>
     <row r="192" ht="15.75" spans="1:13">
       <c r="A192" s="11"/>
       <c r="B192" s="15"/>
       <c r="C192" s="13"/>
-      <c r="D192" s="32"/>
+      <c r="D192" s="31"/>
       <c r="E192" s="15"/>
       <c r="F192" s="15"/>
       <c r="G192" s="16"/>
       <c r="H192"/>
-      <c r="I192" s="22"/>
+      <c r="I192" s="21"/>
       <c r="K192" s="15"/>
-      <c r="L192" s="28"/>
+      <c r="L192" s="27"/>
       <c r="M192" s="16"/>
     </row>
     <row r="193" ht="15.75" spans="1:13">
       <c r="A193" s="11"/>
       <c r="B193" s="15"/>
       <c r="C193" s="13"/>
-      <c r="D193" s="32"/>
+      <c r="D193" s="31"/>
       <c r="E193" s="15"/>
       <c r="F193" s="15"/>
       <c r="G193" s="16"/>
       <c r="H193"/>
-      <c r="I193" s="22"/>
+      <c r="I193" s="21"/>
       <c r="K193" s="15"/>
-      <c r="L193" s="28"/>
+      <c r="L193" s="27"/>
       <c r="M193" s="16"/>
     </row>
     <row r="194" ht="15.75" spans="1:13">
       <c r="A194" s="11"/>
       <c r="B194" s="15"/>
       <c r="C194" s="13"/>
-      <c r="D194" s="32"/>
+      <c r="D194" s="31"/>
       <c r="E194" s="15"/>
       <c r="F194" s="15"/>
       <c r="G194" s="16"/>
       <c r="H194"/>
-      <c r="I194" s="22"/>
+      <c r="I194" s="21"/>
       <c r="K194" s="15"/>
-      <c r="L194" s="28"/>
+      <c r="L194" s="27"/>
       <c r="M194" s="16"/>
     </row>
     <row r="195" ht="15.75" spans="1:13">
       <c r="A195" s="11"/>
       <c r="B195" s="15"/>
       <c r="C195" s="13"/>
-      <c r="D195" s="32"/>
+      <c r="D195" s="31"/>
       <c r="E195" s="15"/>
       <c r="F195" s="15"/>
       <c r="G195" s="16"/>
       <c r="H195"/>
-      <c r="I195" s="22"/>
+      <c r="I195" s="21"/>
       <c r="K195" s="15"/>
-      <c r="L195" s="28"/>
+      <c r="L195" s="27"/>
       <c r="M195" s="16"/>
     </row>
     <row r="196" ht="15.75" spans="1:13">
       <c r="A196" s="11"/>
       <c r="B196" s="15"/>
       <c r="C196" s="13"/>
-      <c r="D196" s="32"/>
+      <c r="D196" s="31"/>
       <c r="E196" s="15"/>
       <c r="F196" s="15"/>
       <c r="G196" s="16"/>
       <c r="H196"/>
-      <c r="I196" s="22"/>
+      <c r="I196" s="21"/>
       <c r="K196" s="15"/>
-      <c r="L196" s="28"/>
+      <c r="L196" s="27"/>
       <c r="M196" s="16"/>
     </row>
     <row r="197" ht="15.75" spans="1:13">
       <c r="A197" s="11"/>
       <c r="B197" s="15"/>
       <c r="C197" s="13"/>
-      <c r="D197" s="32"/>
+      <c r="D197" s="31"/>
       <c r="E197" s="15"/>
       <c r="F197" s="15"/>
       <c r="G197" s="16"/>
       <c r="H197"/>
-      <c r="I197" s="22"/>
+      <c r="I197" s="21"/>
       <c r="K197" s="15"/>
-      <c r="L197" s="28"/>
+      <c r="L197" s="27"/>
       <c r="M197" s="16"/>
     </row>
     <row r="198" ht="15.75" spans="1:13">
       <c r="A198" s="11"/>
       <c r="B198" s="15"/>
       <c r="C198" s="13"/>
-      <c r="D198" s="32"/>
+      <c r="D198" s="31"/>
       <c r="E198" s="15"/>
       <c r="F198" s="15"/>
       <c r="G198" s="16"/>
       <c r="H198"/>
-      <c r="I198" s="22"/>
+      <c r="I198" s="21"/>
       <c r="K198" s="15"/>
-      <c r="L198" s="28"/>
+      <c r="L198" s="27"/>
       <c r="M198" s="16"/>
     </row>
     <row r="199" ht="15.75" spans="1:12">
       <c r="A199" s="11"/>
       <c r="B199" s="15"/>
       <c r="C199" s="13"/>
-      <c r="D199" s="32"/>
+      <c r="D199" s="31"/>
       <c r="E199" s="15"/>
       <c r="F199" s="15"/>
       <c r="G199" s="16"/>
       <c r="H199"/>
-      <c r="I199" s="22"/>
+      <c r="I199" s="21"/>
       <c r="K199" s="15"/>
-      <c r="L199" s="28"/>
+      <c r="L199" s="27"/>
     </row>
     <row r="200" ht="15.75" spans="1:12">
       <c r="A200" s="11"/>
       <c r="B200" s="15"/>
       <c r="C200" s="13"/>
-      <c r="D200" s="32"/>
+      <c r="D200" s="31"/>
       <c r="E200" s="15"/>
       <c r="F200" s="15"/>
       <c r="G200" s="16"/>
       <c r="H200"/>
-      <c r="I200" s="22"/>
+      <c r="I200" s="21"/>
       <c r="K200" s="15"/>
-      <c r="L200" s="28"/>
+      <c r="L200" s="27"/>
     </row>
     <row r="201" ht="15.75" spans="1:12">
       <c r="A201" s="11"/>
       <c r="B201" s="15"/>
       <c r="C201" s="13"/>
-      <c r="D201" s="32"/>
+      <c r="D201" s="31"/>
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
       <c r="G201" s="16"/>
       <c r="H201"/>
-      <c r="I201" s="22"/>
+      <c r="I201" s="21"/>
       <c r="K201" s="15"/>
-      <c r="L201" s="28"/>
+      <c r="L201" s="27"/>
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="11"/>
       <c r="B202" s="15"/>
       <c r="C202" s="13"/>
-      <c r="D202" s="32"/>
+      <c r="D202" s="31"/>
       <c r="E202" s="15"/>
       <c r="F202" s="15"/>
       <c r="G202" s="16"/>
       <c r="H202"/>
-      <c r="I202" s="26"/>
+      <c r="I202" s="25"/>
       <c r="K202" s="15"/>
-      <c r="L202" s="28"/>
+      <c r="L202" s="27"/>
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="11"/>
       <c r="B203" s="15"/>
       <c r="C203" s="13"/>
-      <c r="D203" s="32"/>
+      <c r="D203" s="31"/>
       <c r="E203" s="15"/>
       <c r="F203" s="15"/>
       <c r="G203" s="16"/>
       <c r="H203"/>
-      <c r="I203" s="26"/>
+      <c r="I203" s="25"/>
       <c r="K203" s="15"/>
-      <c r="L203" s="28"/>
+      <c r="L203" s="27"/>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="11"/>
       <c r="B204" s="15"/>
       <c r="C204" s="13"/>
-      <c r="D204" s="33"/>
+      <c r="D204" s="32"/>
       <c r="E204" s="15"/>
       <c r="F204" s="15"/>
       <c r="G204" s="16"/>
       <c r="H204"/>
-      <c r="I204" s="26"/>
+      <c r="I204" s="25"/>
       <c r="K204" s="15"/>
-      <c r="L204" s="28"/>
+      <c r="L204" s="27"/>
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="11"/>
       <c r="B205" s="15"/>
       <c r="C205" s="13"/>
-      <c r="D205" s="32"/>
+      <c r="D205" s="31"/>
       <c r="E205" s="15"/>
       <c r="F205" s="15"/>
       <c r="G205" s="16"/>
       <c r="H205"/>
-      <c r="I205" s="26"/>
+      <c r="I205" s="25"/>
       <c r="K205" s="15"/>
-      <c r="L205" s="28"/>
+      <c r="L205" s="27"/>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="11"/>
       <c r="B206" s="15"/>
       <c r="C206" s="13"/>
-      <c r="D206" s="32"/>
+      <c r="D206" s="31"/>
       <c r="E206" s="15"/>
       <c r="F206" s="15"/>
       <c r="G206" s="16"/>
       <c r="H206"/>
-      <c r="I206" s="26"/>
+      <c r="I206" s="25"/>
       <c r="K206" s="15"/>
-      <c r="L206" s="28"/>
+      <c r="L206" s="27"/>
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="11"/>
       <c r="B207" s="15"/>
       <c r="C207" s="13"/>
-      <c r="D207" s="32"/>
+      <c r="D207" s="31"/>
       <c r="E207" s="15"/>
       <c r="F207" s="15"/>
       <c r="G207" s="16"/>
       <c r="H207"/>
-      <c r="I207" s="26"/>
+      <c r="I207" s="25"/>
       <c r="K207" s="15"/>
-      <c r="L207" s="28"/>
+      <c r="L207" s="27"/>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="11"/>
       <c r="B208" s="15"/>
       <c r="C208" s="13"/>
-      <c r="D208" s="32"/>
+      <c r="D208" s="31"/>
       <c r="E208" s="15"/>
       <c r="F208" s="15"/>
       <c r="G208" s="16"/>
       <c r="H208"/>
-      <c r="I208" s="26"/>
+      <c r="I208" s="25"/>
       <c r="K208" s="15"/>
-      <c r="L208" s="28"/>
+      <c r="L208" s="27"/>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="11"/>
       <c r="B209" s="15"/>
       <c r="C209" s="13"/>
-      <c r="D209" s="32"/>
+      <c r="D209" s="31"/>
       <c r="E209" s="15"/>
       <c r="F209" s="15"/>
       <c r="G209" s="16"/>
       <c r="H209"/>
-      <c r="I209" s="26"/>
+      <c r="I209" s="25"/>
       <c r="K209" s="15"/>
-      <c r="L209" s="28"/>
+      <c r="L209" s="27"/>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="11"/>
       <c r="B210" s="15"/>
       <c r="C210" s="13"/>
-      <c r="D210" s="32"/>
+      <c r="D210" s="31"/>
       <c r="E210" s="15"/>
       <c r="F210" s="15"/>
       <c r="G210" s="16"/>
       <c r="H210"/>
-      <c r="I210" s="26"/>
+      <c r="I210" s="25"/>
       <c r="K210" s="15"/>
-      <c r="L210" s="28"/>
+      <c r="L210" s="27"/>
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="11"/>
       <c r="B211" s="15"/>
       <c r="C211" s="13"/>
-      <c r="D211" s="32"/>
+      <c r="D211" s="31"/>
       <c r="E211" s="15"/>
       <c r="F211" s="15"/>
       <c r="G211" s="16"/>
       <c r="H211"/>
-      <c r="I211" s="26"/>
+      <c r="I211" s="25"/>
       <c r="K211" s="15"/>
-      <c r="L211" s="28"/>
+      <c r="L211" s="27"/>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="11"/>
       <c r="B212" s="15"/>
       <c r="C212" s="13"/>
-      <c r="D212" s="32"/>
+      <c r="D212" s="31"/>
       <c r="E212" s="15"/>
       <c r="F212" s="15"/>
       <c r="G212" s="16"/>
       <c r="H212"/>
-      <c r="I212" s="26"/>
+      <c r="I212" s="25"/>
       <c r="K212" s="15"/>
-      <c r="L212" s="28"/>
+      <c r="L212" s="27"/>
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="11"/>
       <c r="B213" s="15"/>
       <c r="C213" s="13"/>
-      <c r="D213" s="32"/>
+      <c r="D213" s="31"/>
       <c r="E213" s="15"/>
       <c r="F213" s="15"/>
       <c r="G213" s="16"/>
       <c r="H213"/>
-      <c r="I213" s="26"/>
+      <c r="I213" s="25"/>
       <c r="K213" s="15"/>
-      <c r="L213" s="28"/>
+      <c r="L213" s="27"/>
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="11"/>
       <c r="B214" s="15"/>
       <c r="C214" s="13"/>
-      <c r="D214" s="32"/>
+      <c r="D214" s="31"/>
       <c r="E214" s="15"/>
       <c r="F214" s="15"/>
       <c r="G214" s="16"/>
       <c r="H214"/>
-      <c r="I214" s="26"/>
+      <c r="I214" s="25"/>
       <c r="K214" s="15"/>
-      <c r="L214" s="28"/>
+      <c r="L214" s="27"/>
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="11"/>
       <c r="B215" s="15"/>
       <c r="C215" s="13"/>
-      <c r="D215" s="32"/>
+      <c r="D215" s="31"/>
       <c r="E215" s="15"/>
       <c r="F215" s="15"/>
       <c r="G215" s="16"/>
       <c r="H215"/>
-      <c r="I215" s="26"/>
+      <c r="I215" s="25"/>
       <c r="K215" s="15"/>
-      <c r="L215" s="28"/>
+      <c r="L215" s="27"/>
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="11"/>
       <c r="B216" s="15"/>
       <c r="C216" s="13"/>
-      <c r="D216" s="32"/>
+      <c r="D216" s="31"/>
       <c r="E216" s="15"/>
       <c r="F216" s="15"/>
       <c r="G216" s="16"/>
       <c r="H216"/>
-      <c r="I216" s="26"/>
+      <c r="I216" s="25"/>
       <c r="K216" s="15"/>
-      <c r="L216" s="28"/>
+      <c r="L216" s="27"/>
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="11"/>
       <c r="B217" s="15"/>
       <c r="C217" s="13"/>
-      <c r="D217" s="32"/>
+      <c r="D217" s="31"/>
       <c r="E217" s="15"/>
       <c r="F217" s="15"/>
       <c r="G217" s="16"/>
       <c r="H217"/>
-      <c r="I217" s="26"/>
+      <c r="I217" s="25"/>
       <c r="K217" s="15"/>
-      <c r="L217" s="28"/>
+      <c r="L217" s="27"/>
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="11"/>
       <c r="B218" s="15"/>
       <c r="C218" s="13"/>
-      <c r="D218" s="32"/>
+      <c r="D218" s="31"/>
       <c r="E218" s="15"/>
       <c r="F218" s="15"/>
       <c r="G218" s="16"/>
       <c r="H218"/>
-      <c r="I218" s="26"/>
+      <c r="I218" s="25"/>
       <c r="K218" s="15"/>
-      <c r="L218" s="28"/>
+      <c r="L218" s="27"/>
     </row>
     <row r="219" spans="1:12">
       <c r="A219" s="11"/>
       <c r="B219" s="15"/>
       <c r="C219" s="13"/>
-      <c r="D219" s="32"/>
+      <c r="D219" s="31"/>
       <c r="E219" s="15"/>
       <c r="F219" s="15"/>
       <c r="G219" s="16"/>
       <c r="H219"/>
-      <c r="I219" s="26"/>
+      <c r="I219" s="25"/>
       <c r="K219" s="15"/>
-      <c r="L219" s="28"/>
+      <c r="L219" s="27"/>
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="11"/>
       <c r="B220" s="15"/>
       <c r="C220" s="13"/>
-      <c r="D220" s="32"/>
+      <c r="D220" s="31"/>
       <c r="E220" s="15"/>
       <c r="F220" s="15"/>
       <c r="G220" s="16"/>
       <c r="H220"/>
-      <c r="I220" s="26"/>
+      <c r="I220" s="25"/>
       <c r="K220" s="15"/>
-      <c r="L220" s="28"/>
+      <c r="L220" s="27"/>
     </row>
     <row r="221" spans="1:12">
       <c r="A221" s="11"/>
       <c r="B221" s="15"/>
       <c r="C221" s="13"/>
-      <c r="D221" s="32"/>
+      <c r="D221" s="31"/>
       <c r="E221" s="15"/>
       <c r="F221" s="15"/>
       <c r="G221" s="16"/>
       <c r="H221"/>
-      <c r="I221" s="26"/>
+      <c r="I221" s="25"/>
       <c r="K221" s="15"/>
-      <c r="L221" s="28"/>
+      <c r="L221" s="27"/>
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="11"/>
       <c r="B222" s="15"/>
       <c r="C222" s="13"/>
-      <c r="D222" s="32"/>
+      <c r="D222" s="31"/>
       <c r="E222" s="15"/>
       <c r="F222" s="15"/>
       <c r="G222" s="16"/>
       <c r="H222"/>
-      <c r="I222" s="26"/>
+      <c r="I222" s="25"/>
       <c r="K222" s="15"/>
-      <c r="L222" s="28"/>
+      <c r="L222" s="27"/>
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="11"/>
       <c r="B223" s="15"/>
       <c r="C223" s="13"/>
-      <c r="D223" s="32"/>
+      <c r="D223" s="31"/>
       <c r="E223" s="15"/>
       <c r="F223" s="15"/>
       <c r="G223" s="16"/>
       <c r="H223"/>
-      <c r="I223" s="26"/>
+      <c r="I223" s="25"/>
       <c r="K223" s="15"/>
-      <c r="L223" s="28"/>
+      <c r="L223" s="27"/>
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="11"/>
       <c r="B224" s="15"/>
       <c r="C224" s="13"/>
-      <c r="D224" s="32"/>
+      <c r="D224" s="31"/>
       <c r="E224" s="15"/>
       <c r="F224" s="15"/>
       <c r="G224" s="16"/>
       <c r="H224"/>
-      <c r="I224" s="26"/>
+      <c r="I224" s="25"/>
       <c r="K224" s="15"/>
-      <c r="L224" s="28"/>
+      <c r="L224" s="27"/>
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="11"/>
       <c r="B225" s="15"/>
       <c r="C225" s="13"/>
-      <c r="D225" s="32"/>
+      <c r="D225" s="31"/>
       <c r="E225" s="15"/>
       <c r="F225" s="15"/>
       <c r="G225" s="16"/>
       <c r="H225"/>
-      <c r="I225" s="26"/>
+      <c r="I225" s="25"/>
       <c r="K225" s="15"/>
-      <c r="L225" s="28"/>
+      <c r="L225" s="27"/>
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="11"/>
       <c r="B226" s="15"/>
       <c r="C226" s="13"/>
-      <c r="D226" s="32"/>
+      <c r="D226" s="31"/>
       <c r="E226" s="15"/>
       <c r="F226" s="15"/>
       <c r="G226" s="16"/>
       <c r="H226"/>
-      <c r="I226" s="26"/>
+      <c r="I226" s="25"/>
       <c r="K226" s="15"/>
-      <c r="L226" s="28"/>
+      <c r="L226" s="27"/>
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="11"/>
       <c r="B227" s="15"/>
       <c r="C227" s="13"/>
-      <c r="D227" s="32"/>
+      <c r="D227" s="31"/>
       <c r="E227" s="15"/>
       <c r="F227" s="15"/>
       <c r="G227" s="16"/>
       <c r="H227"/>
-      <c r="I227" s="26"/>
+      <c r="I227" s="25"/>
       <c r="K227" s="15"/>
-      <c r="L227" s="28"/>
+      <c r="L227" s="27"/>
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="11"/>
       <c r="B228" s="15"/>
       <c r="C228" s="13"/>
-      <c r="D228" s="32"/>
+      <c r="D228" s="31"/>
       <c r="E228" s="15"/>
       <c r="F228" s="15"/>
       <c r="G228" s="16"/>
       <c r="H228"/>
-      <c r="I228" s="26"/>
+      <c r="I228" s="25"/>
       <c r="K228" s="15"/>
-      <c r="L228" s="28"/>
+      <c r="L228" s="27"/>
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="11"/>
       <c r="B229" s="15"/>
       <c r="C229" s="13"/>
-      <c r="D229" s="32"/>
+      <c r="D229" s="31"/>
       <c r="E229" s="15"/>
       <c r="F229" s="15"/>
       <c r="G229" s="16"/>
       <c r="H229"/>
-      <c r="I229" s="26"/>
+      <c r="I229" s="25"/>
       <c r="K229" s="15"/>
-      <c r="L229" s="28"/>
+      <c r="L229" s="27"/>
     </row>
     <row r="230" spans="1:12">
       <c r="A230" s="11"/>
       <c r="B230" s="15"/>
       <c r="C230" s="13"/>
-      <c r="D230" s="32"/>
+      <c r="D230" s="31"/>
       <c r="E230" s="15"/>
       <c r="F230" s="15"/>
       <c r="G230" s="16"/>
       <c r="H230"/>
-      <c r="I230" s="26"/>
+      <c r="I230" s="25"/>
       <c r="K230" s="15"/>
-      <c r="L230" s="28"/>
+      <c r="L230" s="27"/>
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="11"/>
       <c r="B231" s="15"/>
       <c r="C231" s="13"/>
-      <c r="D231" s="32"/>
+      <c r="D231" s="31"/>
       <c r="E231" s="15"/>
       <c r="F231" s="15"/>
       <c r="G231" s="16"/>
       <c r="H231"/>
-      <c r="I231" s="26"/>
+      <c r="I231" s="25"/>
       <c r="K231" s="15"/>
-      <c r="L231" s="28"/>
+      <c r="L231" s="27"/>
     </row>
     <row r="232" spans="1:12">
       <c r="A232" s="11"/>
       <c r="B232" s="15"/>
       <c r="C232" s="13"/>
-      <c r="D232" s="32"/>
+      <c r="D232" s="31"/>
       <c r="E232" s="15"/>
       <c r="F232" s="15"/>
       <c r="G232" s="16"/>
       <c r="H232"/>
-      <c r="I232" s="26"/>
+      <c r="I232" s="25"/>
       <c r="K232" s="15"/>
-      <c r="L232" s="28"/>
+      <c r="L232" s="27"/>
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="11"/>
       <c r="B233" s="15"/>
       <c r="C233" s="13"/>
-      <c r="D233" s="32"/>
+      <c r="D233" s="31"/>
       <c r="E233" s="15"/>
       <c r="F233" s="15"/>
       <c r="G233" s="16"/>
       <c r="H233"/>
-      <c r="I233" s="26"/>
+      <c r="I233" s="25"/>
       <c r="K233" s="15"/>
-      <c r="L233" s="28"/>
+      <c r="L233" s="27"/>
     </row>
     <row r="234" spans="1:12">
       <c r="A234" s="11"/>
       <c r="B234" s="15"/>
       <c r="C234" s="13"/>
-      <c r="D234" s="32"/>
+      <c r="D234" s="31"/>
       <c r="E234" s="15"/>
       <c r="F234" s="15"/>
       <c r="G234" s="16"/>
       <c r="H234"/>
-      <c r="I234" s="26"/>
+      <c r="I234" s="25"/>
       <c r="K234" s="15"/>
-      <c r="L234" s="28"/>
+      <c r="L234" s="27"/>
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="11"/>
       <c r="B235" s="15"/>
       <c r="C235" s="13"/>
-      <c r="D235" s="32"/>
+      <c r="D235" s="31"/>
       <c r="E235" s="15"/>
       <c r="F235" s="15"/>
       <c r="G235" s="16"/>
       <c r="H235"/>
-      <c r="I235" s="26"/>
+      <c r="I235" s="25"/>
       <c r="K235" s="15"/>
-      <c r="L235" s="28"/>
+      <c r="L235" s="27"/>
     </row>
     <row r="236" spans="1:12">
       <c r="A236" s="11"/>
       <c r="B236" s="15"/>
       <c r="C236" s="13"/>
-      <c r="D236" s="32"/>
+      <c r="D236" s="31"/>
       <c r="E236" s="15"/>
       <c r="F236" s="15"/>
       <c r="G236" s="16"/>
       <c r="H236"/>
-      <c r="I236" s="26"/>
+      <c r="I236" s="25"/>
       <c r="K236" s="15"/>
-      <c r="L236" s="28"/>
+      <c r="L236" s="27"/>
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="11"/>
       <c r="B237" s="15"/>
       <c r="C237" s="13"/>
-      <c r="D237" s="32"/>
+      <c r="D237" s="31"/>
       <c r="E237" s="15"/>
       <c r="F237" s="15"/>
       <c r="G237" s="16"/>
       <c r="H237"/>
-      <c r="I237" s="26"/>
+      <c r="I237" s="25"/>
       <c r="K237" s="15"/>
-      <c r="L237" s="28"/>
+      <c r="L237" s="27"/>
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="11"/>
       <c r="B238" s="15"/>
       <c r="C238" s="13"/>
-      <c r="D238" s="32"/>
+      <c r="D238" s="31"/>
       <c r="E238" s="15"/>
       <c r="F238" s="15"/>
       <c r="G238" s="16"/>
       <c r="H238"/>
-      <c r="I238" s="26"/>
+      <c r="I238" s="25"/>
       <c r="K238" s="15"/>
-      <c r="L238" s="28"/>
+      <c r="L238" s="27"/>
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="11"/>
       <c r="B239" s="15"/>
       <c r="C239" s="13"/>
-      <c r="D239" s="32"/>
+      <c r="D239" s="31"/>
       <c r="E239" s="15"/>
       <c r="F239" s="15"/>
       <c r="G239" s="16"/>
       <c r="H239"/>
-      <c r="I239" s="26"/>
+      <c r="I239" s="25"/>
       <c r="K239" s="15"/>
-      <c r="L239" s="28"/>
+      <c r="L239" s="27"/>
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="11"/>
       <c r="B240" s="15"/>
       <c r="C240" s="13"/>
-      <c r="D240" s="32"/>
+      <c r="D240" s="31"/>
       <c r="E240" s="15"/>
       <c r="F240" s="15"/>
       <c r="G240" s="16"/>
       <c r="H240"/>
-      <c r="I240" s="26"/>
+      <c r="I240" s="25"/>
       <c r="K240" s="15"/>
-      <c r="L240" s="28"/>
+      <c r="L240" s="27"/>
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="11"/>
       <c r="B241" s="15"/>
       <c r="C241" s="13"/>
-      <c r="D241" s="32"/>
+      <c r="D241" s="31"/>
       <c r="E241" s="15"/>
       <c r="F241" s="15"/>
       <c r="G241" s="16"/>
       <c r="H241"/>
-      <c r="I241" s="26"/>
+      <c r="I241" s="25"/>
       <c r="K241" s="15"/>
-      <c r="L241" s="28"/>
+      <c r="L241" s="27"/>
     </row>
     <row r="242" spans="1:12">
       <c r="A242" s="11"/>
       <c r="B242" s="15"/>
       <c r="C242" s="13"/>
-      <c r="D242" s="32"/>
+      <c r="D242" s="31"/>
       <c r="E242" s="15"/>
       <c r="F242" s="15"/>
       <c r="G242" s="16"/>
       <c r="H242"/>
-      <c r="I242" s="26"/>
+      <c r="I242" s="25"/>
       <c r="K242" s="15"/>
-      <c r="L242" s="28"/>
+      <c r="L242" s="27"/>
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="11"/>
       <c r="B243" s="15"/>
       <c r="C243" s="13"/>
-      <c r="D243" s="32"/>
+      <c r="D243" s="31"/>
       <c r="E243" s="15"/>
       <c r="F243" s="15"/>
       <c r="G243" s="16"/>
       <c r="H243"/>
-      <c r="I243" s="26"/>
+      <c r="I243" s="25"/>
       <c r="K243" s="15"/>
-      <c r="L243" s="28"/>
+      <c r="L243" s="27"/>
     </row>
     <row r="244" spans="1:12">
       <c r="A244" s="11"/>
       <c r="B244" s="15"/>
       <c r="C244" s="13"/>
-      <c r="D244" s="32"/>
+      <c r="D244" s="31"/>
       <c r="E244" s="15"/>
       <c r="F244" s="15"/>
       <c r="G244" s="16"/>
       <c r="H244"/>
-      <c r="I244" s="26"/>
+      <c r="I244" s="25"/>
       <c r="K244" s="15"/>
-      <c r="L244" s="28"/>
+      <c r="L244" s="27"/>
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="11"/>
       <c r="B245" s="15"/>
       <c r="C245" s="13"/>
-      <c r="D245" s="32"/>
+      <c r="D245" s="31"/>
       <c r="E245" s="15"/>
       <c r="F245" s="15"/>
       <c r="G245" s="16"/>
       <c r="H245"/>
-      <c r="I245" s="26"/>
+      <c r="I245" s="25"/>
       <c r="K245" s="15"/>
-      <c r="L245" s="28"/>
+      <c r="L245" s="27"/>
     </row>
     <row r="246" spans="1:12">
       <c r="A246" s="11"/>
       <c r="B246" s="15"/>
       <c r="C246" s="13"/>
-      <c r="D246" s="32"/>
+      <c r="D246" s="31"/>
       <c r="E246" s="15"/>
       <c r="F246" s="15"/>
       <c r="G246" s="16"/>
       <c r="H246"/>
-      <c r="I246" s="26"/>
+      <c r="I246" s="25"/>
       <c r="K246" s="15"/>
-      <c r="L246" s="28"/>
+      <c r="L246" s="27"/>
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="11"/>
       <c r="B247" s="15"/>
       <c r="C247" s="13"/>
-      <c r="D247" s="32"/>
+      <c r="D247" s="31"/>
       <c r="E247" s="15"/>
       <c r="F247" s="15"/>
       <c r="G247" s="16"/>
       <c r="H247"/>
-      <c r="I247" s="26"/>
+      <c r="I247" s="25"/>
       <c r="K247" s="15"/>
-      <c r="L247" s="28"/>
+      <c r="L247" s="27"/>
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="11"/>
       <c r="B248" s="15"/>
       <c r="C248" s="13"/>
-      <c r="D248" s="32"/>
+      <c r="D248" s="31"/>
       <c r="E248" s="15"/>
       <c r="F248" s="15"/>
       <c r="G248" s="16"/>
       <c r="H248"/>
-      <c r="I248" s="26"/>
+      <c r="I248" s="25"/>
       <c r="K248" s="15"/>
-      <c r="L248" s="28"/>
+      <c r="L248" s="27"/>
     </row>
     <row r="249" spans="1:12">
       <c r="A249" s="11"/>
       <c r="B249" s="15"/>
       <c r="C249" s="13"/>
-      <c r="D249" s="32"/>
+      <c r="D249" s="31"/>
       <c r="E249" s="15"/>
       <c r="F249" s="15"/>
       <c r="G249" s="16"/>
       <c r="H249"/>
-      <c r="I249" s="26"/>
+      <c r="I249" s="25"/>
       <c r="K249" s="15"/>
-      <c r="L249" s="28"/>
+      <c r="L249" s="27"/>
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="11"/>
       <c r="B250" s="15"/>
       <c r="C250" s="13"/>
-      <c r="D250" s="32"/>
+      <c r="D250" s="31"/>
       <c r="E250" s="15"/>
       <c r="F250" s="15"/>
       <c r="G250" s="16"/>
       <c r="H250"/>
-      <c r="I250" s="26"/>
+      <c r="I250" s="25"/>
       <c r="K250" s="15"/>
-      <c r="L250" s="28"/>
+      <c r="L250" s="27"/>
     </row>
     <row r="251" spans="1:12">
       <c r="A251" s="11"/>
       <c r="B251" s="15"/>
       <c r="C251" s="13"/>
-      <c r="D251" s="32"/>
+      <c r="D251" s="31"/>
       <c r="E251" s="15"/>
       <c r="F251" s="15"/>
       <c r="G251" s="16"/>
       <c r="H251"/>
-      <c r="I251" s="26"/>
+      <c r="I251" s="25"/>
       <c r="K251" s="15"/>
-      <c r="L251" s="28"/>
+      <c r="L251" s="27"/>
     </row>
     <row r="252" spans="1:12">
       <c r="A252" s="11"/>
       <c r="B252" s="15"/>
       <c r="C252" s="13"/>
-      <c r="D252" s="32"/>
+      <c r="D252" s="31"/>
       <c r="E252" s="15"/>
       <c r="F252" s="15"/>
       <c r="G252" s="16"/>
       <c r="H252"/>
-      <c r="I252" s="26"/>
+      <c r="I252" s="25"/>
       <c r="K252" s="15"/>
-      <c r="L252" s="28"/>
+      <c r="L252" s="27"/>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="11"/>
       <c r="B253" s="15"/>
       <c r="C253" s="13"/>
-      <c r="D253" s="32"/>
+      <c r="D253" s="31"/>
       <c r="E253" s="15"/>
       <c r="F253" s="15"/>
       <c r="G253" s="16"/>
       <c r="H253"/>
-      <c r="I253" s="26"/>
+      <c r="I253" s="25"/>
       <c r="K253" s="15"/>
-      <c r="L253" s="28"/>
+      <c r="L253" s="27"/>
     </row>
     <row r="254" spans="1:12">
       <c r="A254" s="11"/>
       <c r="B254" s="15"/>
       <c r="C254" s="13"/>
-      <c r="D254" s="32"/>
+      <c r="D254" s="31"/>
       <c r="E254" s="15"/>
       <c r="F254" s="15"/>
       <c r="G254" s="16"/>
       <c r="H254"/>
-      <c r="I254" s="26"/>
+      <c r="I254" s="25"/>
       <c r="K254" s="15"/>
-      <c r="L254" s="28"/>
+      <c r="L254" s="27"/>
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="11"/>
       <c r="B255" s="15"/>
       <c r="C255" s="13"/>
-      <c r="D255" s="32"/>
+      <c r="D255" s="31"/>
       <c r="E255" s="15"/>
       <c r="F255" s="15"/>
       <c r="G255" s="16"/>
       <c r="H255"/>
-      <c r="I255" s="26"/>
+      <c r="I255" s="25"/>
       <c r="K255" s="15"/>
-      <c r="L255" s="28"/>
+      <c r="L255" s="27"/>
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="11"/>
       <c r="B256" s="15"/>
       <c r="C256" s="13"/>
-      <c r="D256" s="32"/>
+      <c r="D256" s="31"/>
       <c r="E256" s="15"/>
       <c r="F256" s="15"/>
       <c r="G256" s="16"/>
       <c r="H256"/>
-      <c r="I256" s="26"/>
+      <c r="I256" s="25"/>
       <c r="K256" s="15"/>
-      <c r="L256" s="28"/>
+      <c r="L256" s="27"/>
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="11"/>
       <c r="B257" s="15"/>
       <c r="C257" s="13"/>
-      <c r="D257" s="32"/>
+      <c r="D257" s="31"/>
       <c r="E257" s="15"/>
       <c r="F257" s="15"/>
       <c r="G257" s="16"/>
       <c r="H257"/>
-      <c r="I257" s="26"/>
+      <c r="I257" s="25"/>
       <c r="K257" s="15"/>
-      <c r="L257" s="28"/>
+      <c r="L257" s="27"/>
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="11"/>
       <c r="B258" s="15"/>
       <c r="C258" s="13"/>
-      <c r="D258" s="32"/>
+      <c r="D258" s="31"/>
       <c r="E258" s="15"/>
       <c r="F258" s="15"/>
       <c r="G258" s="16"/>
       <c r="H258"/>
-      <c r="I258" s="26"/>
+      <c r="I258" s="25"/>
       <c r="K258" s="15"/>
-      <c r="L258" s="28"/>
+      <c r="L258" s="27"/>
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="11"/>
       <c r="B259" s="15"/>
       <c r="C259" s="13"/>
-      <c r="D259" s="32"/>
+      <c r="D259" s="31"/>
       <c r="E259" s="15"/>
       <c r="F259" s="15"/>
       <c r="G259" s="16"/>
       <c r="H259"/>
-      <c r="I259" s="26"/>
+      <c r="I259" s="25"/>
       <c r="K259" s="15"/>
-      <c r="L259" s="28"/>
+      <c r="L259" s="27"/>
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="11"/>
       <c r="B260" s="15"/>
       <c r="C260" s="13"/>
-      <c r="D260" s="32"/>
+      <c r="D260" s="31"/>
       <c r="E260" s="15"/>
       <c r="F260" s="15"/>
       <c r="G260" s="16"/>
       <c r="H260"/>
-      <c r="I260" s="26"/>
+      <c r="I260" s="25"/>
       <c r="K260" s="15"/>
-      <c r="L260" s="28"/>
+      <c r="L260" s="27"/>
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="11"/>
       <c r="B261" s="15"/>
       <c r="C261" s="13"/>
-      <c r="D261" s="32"/>
+      <c r="D261" s="31"/>
       <c r="E261" s="15"/>
       <c r="F261" s="15"/>
       <c r="G261" s="16"/>
       <c r="H261"/>
-      <c r="I261" s="26"/>
+      <c r="I261" s="25"/>
       <c r="K261" s="15"/>
-      <c r="L261" s="28"/>
+      <c r="L261" s="27"/>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="11"/>
       <c r="B262" s="15"/>
       <c r="C262" s="13"/>
-      <c r="D262" s="32"/>
+      <c r="D262" s="31"/>
       <c r="E262" s="15"/>
       <c r="F262" s="15"/>
       <c r="G262" s="16"/>
       <c r="H262"/>
-      <c r="I262" s="26"/>
+      <c r="I262" s="25"/>
       <c r="K262" s="15"/>
-      <c r="L262" s="28"/>
+      <c r="L262" s="27"/>
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="11"/>
       <c r="B263" s="15"/>
       <c r="C263" s="13"/>
-      <c r="D263" s="32"/>
+      <c r="D263" s="31"/>
       <c r="E263" s="15"/>
       <c r="F263" s="15"/>
       <c r="G263" s="16"/>
       <c r="H263"/>
-      <c r="I263" s="26"/>
+      <c r="I263" s="25"/>
       <c r="K263" s="15"/>
-      <c r="L263" s="28"/>
+      <c r="L263" s="27"/>
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="11"/>
       <c r="B264" s="15"/>
       <c r="C264" s="13"/>
-      <c r="D264" s="32"/>
+      <c r="D264" s="31"/>
       <c r="E264" s="15"/>
       <c r="F264" s="15"/>
       <c r="G264" s="16"/>
       <c r="H264"/>
-      <c r="I264" s="26"/>
+      <c r="I264" s="25"/>
       <c r="K264" s="15"/>
-      <c r="L264" s="28"/>
+      <c r="L264" s="27"/>
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="11"/>
       <c r="B265" s="15"/>
       <c r="C265" s="13"/>
-      <c r="D265" s="32"/>
+      <c r="D265" s="31"/>
       <c r="E265" s="15"/>
       <c r="F265" s="15"/>
       <c r="G265" s="16"/>
       <c r="H265"/>
-      <c r="I265" s="26"/>
+      <c r="I265" s="25"/>
       <c r="K265" s="15"/>
-      <c r="L265" s="28"/>
+      <c r="L265" s="27"/>
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="11"/>
       <c r="B266" s="15"/>
       <c r="C266" s="13"/>
-      <c r="D266" s="32"/>
+      <c r="D266" s="31"/>
       <c r="E266" s="15"/>
       <c r="F266" s="15"/>
       <c r="G266" s="16"/>
       <c r="H266"/>
-      <c r="I266" s="26"/>
+      <c r="I266" s="25"/>
       <c r="K266" s="15"/>
-      <c r="L266" s="28"/>
+      <c r="L266" s="27"/>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="11"/>
       <c r="B267" s="15"/>
       <c r="C267" s="13"/>
-      <c r="D267" s="32"/>
+      <c r="D267" s="31"/>
       <c r="E267" s="15"/>
       <c r="F267" s="15"/>
       <c r="G267" s="16"/>
       <c r="H267"/>
-      <c r="I267" s="26"/>
+      <c r="I267" s="25"/>
       <c r="K267" s="15"/>
-      <c r="L267" s="28"/>
+      <c r="L267" s="27"/>
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="11"/>
       <c r="B268" s="15"/>
       <c r="C268" s="13"/>
-      <c r="D268" s="32"/>
+      <c r="D268" s="31"/>
       <c r="E268" s="15"/>
       <c r="F268" s="15"/>
       <c r="G268" s="16"/>
       <c r="H268"/>
-      <c r="I268" s="26"/>
+      <c r="I268" s="25"/>
       <c r="K268" s="15"/>
-      <c r="L268" s="28"/>
+      <c r="L268" s="27"/>
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="11"/>
       <c r="B269" s="15"/>
       <c r="C269" s="13"/>
-      <c r="D269" s="32"/>
+      <c r="D269" s="31"/>
       <c r="E269" s="15"/>
       <c r="F269" s="15"/>
       <c r="G269" s="16"/>
       <c r="H269"/>
-      <c r="I269" s="26"/>
+      <c r="I269" s="25"/>
       <c r="K269" s="15"/>
-      <c r="L269" s="28"/>
+      <c r="L269" s="27"/>
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="11"/>
       <c r="B270" s="15"/>
       <c r="C270" s="13"/>
-      <c r="D270" s="32"/>
+      <c r="D270" s="31"/>
       <c r="E270" s="15"/>
       <c r="F270" s="15"/>
       <c r="G270" s="16"/>
       <c r="H270"/>
-      <c r="I270" s="26"/>
+      <c r="I270" s="25"/>
       <c r="K270" s="15"/>
-      <c r="L270" s="28"/>
+      <c r="L270" s="27"/>
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="11"/>
       <c r="B271" s="15"/>
       <c r="C271" s="13"/>
-      <c r="D271" s="32"/>
+      <c r="D271" s="31"/>
       <c r="E271" s="15"/>
       <c r="F271" s="15"/>
       <c r="G271" s="16"/>
       <c r="H271"/>
-      <c r="I271" s="26"/>
+      <c r="I271" s="25"/>
       <c r="K271" s="15"/>
-      <c r="L271" s="28"/>
+      <c r="L271" s="27"/>
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="11"/>
       <c r="B272" s="15"/>
       <c r="C272" s="13"/>
-      <c r="D272" s="32"/>
+      <c r="D272" s="31"/>
       <c r="E272" s="15"/>
       <c r="F272" s="15"/>
       <c r="G272" s="16"/>
       <c r="H272"/>
-      <c r="I272" s="26"/>
+      <c r="I272" s="25"/>
       <c r="K272" s="15"/>
-      <c r="L272" s="28"/>
+      <c r="L272" s="27"/>
     </row>
     <row r="273" spans="1:12">
       <c r="A273" s="11"/>
       <c r="B273" s="15"/>
       <c r="C273" s="13"/>
-      <c r="D273" s="32"/>
+      <c r="D273" s="31"/>
       <c r="E273" s="15"/>
       <c r="F273" s="15"/>
       <c r="G273" s="16"/>
       <c r="H273"/>
-      <c r="I273" s="26"/>
+      <c r="I273" s="25"/>
       <c r="K273" s="15"/>
-      <c r="L273" s="28"/>
+      <c r="L273" s="27"/>
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="11"/>
       <c r="B274" s="15"/>
       <c r="C274" s="13"/>
-      <c r="D274" s="32"/>
+      <c r="D274" s="31"/>
       <c r="E274" s="15"/>
       <c r="F274" s="15"/>
       <c r="G274" s="16"/>
       <c r="H274"/>
-      <c r="I274" s="26"/>
+      <c r="I274" s="25"/>
       <c r="K274" s="15"/>
-      <c r="L274" s="28"/>
+      <c r="L274" s="27"/>
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="11"/>
       <c r="B275" s="15"/>
       <c r="C275" s="13"/>
-      <c r="D275" s="32"/>
+      <c r="D275" s="31"/>
       <c r="E275" s="15"/>
       <c r="F275" s="15"/>
       <c r="G275" s="16"/>
       <c r="H275"/>
-      <c r="I275" s="26"/>
+      <c r="I275" s="25"/>
       <c r="K275" s="15"/>
-      <c r="L275" s="28"/>
+      <c r="L275" s="27"/>
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="11"/>
       <c r="B276" s="15"/>
       <c r="C276" s="13"/>
-      <c r="D276" s="32"/>
+      <c r="D276" s="31"/>
       <c r="E276" s="15"/>
       <c r="F276" s="15"/>
       <c r="G276" s="16"/>
       <c r="H276"/>
-      <c r="I276" s="26"/>
+      <c r="I276" s="25"/>
       <c r="K276" s="15"/>
-      <c r="L276" s="28"/>
+      <c r="L276" s="27"/>
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="11"/>
       <c r="B277" s="15"/>
       <c r="C277" s="13"/>
-      <c r="D277" s="32"/>
+      <c r="D277" s="31"/>
       <c r="E277" s="15"/>
       <c r="F277" s="15"/>
       <c r="G277" s="16"/>
       <c r="H277"/>
-      <c r="I277" s="26"/>
+      <c r="I277" s="25"/>
       <c r="K277" s="15"/>
-      <c r="L277" s="28"/>
+      <c r="L277" s="27"/>
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="11"/>
       <c r="B278" s="15"/>
       <c r="C278" s="13"/>
-      <c r="D278" s="32"/>
+      <c r="D278" s="31"/>
       <c r="E278" s="15"/>
       <c r="F278" s="15"/>
       <c r="G278" s="16"/>
       <c r="H278"/>
-      <c r="I278" s="26"/>
+      <c r="I278" s="25"/>
       <c r="K278" s="15"/>
-      <c r="L278" s="28"/>
+      <c r="L278" s="27"/>
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="11"/>
       <c r="B279" s="15"/>
       <c r="C279" s="13"/>
-      <c r="D279" s="32"/>
+      <c r="D279" s="31"/>
       <c r="E279" s="15"/>
       <c r="F279" s="15"/>
       <c r="G279" s="16"/>
       <c r="H279"/>
-      <c r="I279" s="26"/>
+      <c r="I279" s="25"/>
       <c r="K279" s="15"/>
-      <c r="L279" s="28"/>
+      <c r="L279" s="27"/>
     </row>
     <row r="280" spans="1:12">
       <c r="A280" s="11"/>
       <c r="B280" s="15"/>
       <c r="C280" s="13"/>
-      <c r="D280" s="32"/>
+      <c r="D280" s="31"/>
       <c r="E280" s="15"/>
       <c r="F280" s="15"/>
       <c r="G280" s="16"/>
       <c r="H280"/>
-      <c r="I280" s="26"/>
+      <c r="I280" s="25"/>
       <c r="K280" s="15"/>
-      <c r="L280" s="28"/>
+      <c r="L280" s="27"/>
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="11"/>
       <c r="B281" s="15"/>
       <c r="C281" s="13"/>
-      <c r="D281" s="32"/>
+      <c r="D281" s="31"/>
       <c r="E281" s="15"/>
       <c r="F281" s="15"/>
       <c r="G281" s="16"/>
       <c r="H281"/>
-      <c r="I281" s="26"/>
+      <c r="I281" s="25"/>
       <c r="K281" s="15"/>
-      <c r="L281" s="28"/>
+      <c r="L281" s="27"/>
     </row>
     <row r="282" spans="1:12">
       <c r="A282" s="11"/>
       <c r="B282" s="15"/>
       <c r="C282" s="13"/>
-      <c r="D282" s="32"/>
+      <c r="D282" s="31"/>
       <c r="E282" s="15"/>
       <c r="F282" s="15"/>
       <c r="G282" s="16"/>
       <c r="H282"/>
-      <c r="I282" s="26"/>
+      <c r="I282" s="25"/>
       <c r="K282" s="15"/>
-      <c r="L282" s="28"/>
+      <c r="L282" s="27"/>
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="11"/>
       <c r="B283" s="15"/>
       <c r="C283" s="13"/>
-      <c r="D283" s="32"/>
+      <c r="D283" s="31"/>
       <c r="E283" s="15"/>
       <c r="F283" s="15"/>
       <c r="G283" s="16"/>
       <c r="H283"/>
-      <c r="I283" s="26"/>
+      <c r="I283" s="25"/>
       <c r="K283" s="15"/>
-      <c r="L283" s="28"/>
+      <c r="L283" s="27"/>
     </row>
     <row r="284" spans="1:12">
       <c r="A284" s="11"/>
       <c r="B284" s="15"/>
       <c r="C284" s="13"/>
-      <c r="D284" s="32"/>
+      <c r="D284" s="31"/>
       <c r="E284" s="15"/>
       <c r="F284" s="15"/>
       <c r="G284" s="16"/>
       <c r="H284"/>
-      <c r="I284" s="26"/>
+      <c r="I284" s="25"/>
       <c r="K284" s="15"/>
-      <c r="L284" s="28"/>
+      <c r="L284" s="27"/>
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="11"/>
       <c r="B285" s="15"/>
       <c r="C285" s="13"/>
-      <c r="D285" s="32"/>
+      <c r="D285" s="31"/>
       <c r="E285" s="15"/>
       <c r="F285" s="15"/>
       <c r="G285" s="16"/>
       <c r="H285"/>
-      <c r="I285" s="26"/>
+      <c r="I285" s="25"/>
       <c r="K285" s="15"/>
-      <c r="L285" s="28"/>
+      <c r="L285" s="27"/>
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="11"/>
       <c r="B286" s="15"/>
       <c r="C286" s="13"/>
-      <c r="D286" s="32"/>
+      <c r="D286" s="31"/>
       <c r="E286" s="15"/>
       <c r="F286" s="15"/>
       <c r="G286" s="16"/>
       <c r="H286"/>
-      <c r="I286" s="26"/>
+      <c r="I286" s="25"/>
       <c r="K286" s="15"/>
-      <c r="L286" s="28"/>
+      <c r="L286" s="27"/>
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="11"/>
       <c r="B287" s="15"/>
       <c r="C287" s="13"/>
-      <c r="D287" s="32"/>
+      <c r="D287" s="31"/>
       <c r="E287" s="15"/>
       <c r="F287" s="15"/>
       <c r="G287" s="16"/>
       <c r="H287"/>
-      <c r="I287" s="26"/>
+      <c r="I287" s="25"/>
       <c r="K287" s="15"/>
-      <c r="L287" s="28"/>
+      <c r="L287" s="27"/>
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="11"/>
       <c r="B288" s="15"/>
       <c r="C288" s="13"/>
-      <c r="D288" s="32"/>
+      <c r="D288" s="31"/>
       <c r="E288" s="15"/>
       <c r="F288" s="15"/>
       <c r="G288" s="16"/>
       <c r="H288"/>
-      <c r="I288" s="26"/>
+      <c r="I288" s="25"/>
       <c r="K288" s="15"/>
-      <c r="L288" s="28"/>
+      <c r="L288" s="27"/>
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="11"/>
       <c r="B289" s="15"/>
       <c r="C289" s="13"/>
-      <c r="D289" s="32"/>
+      <c r="D289" s="31"/>
       <c r="E289" s="15"/>
       <c r="F289" s="15"/>
       <c r="G289" s="16"/>
       <c r="H289"/>
-      <c r="I289" s="26"/>
+      <c r="I289" s="25"/>
       <c r="K289" s="15"/>
-      <c r="L289" s="28"/>
+      <c r="L289" s="27"/>
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="11"/>
       <c r="B290" s="15"/>
       <c r="C290" s="13"/>
-      <c r="D290" s="32"/>
+      <c r="D290" s="31"/>
       <c r="E290" s="15"/>
       <c r="F290" s="15"/>
       <c r="G290" s="16"/>
       <c r="H290"/>
-      <c r="I290" s="26"/>
+      <c r="I290" s="25"/>
       <c r="K290" s="15"/>
-      <c r="L290" s="28"/>
+      <c r="L290" s="27"/>
     </row>
     <row r="291" spans="1:12">
       <c r="A291" s="11"/>
       <c r="B291" s="15"/>
       <c r="C291" s="13"/>
-      <c r="D291" s="32"/>
+      <c r="D291" s="31"/>
       <c r="E291" s="15"/>
       <c r="F291" s="15"/>
       <c r="G291" s="16"/>
       <c r="H291"/>
-      <c r="I291" s="26"/>
+      <c r="I291" s="25"/>
       <c r="K291" s="15"/>
-      <c r="L291" s="28"/>
+      <c r="L291" s="27"/>
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="11"/>
       <c r="B292" s="15"/>
       <c r="C292" s="13"/>
-      <c r="D292" s="32"/>
+      <c r="D292" s="31"/>
       <c r="E292" s="15"/>
       <c r="F292" s="15"/>
       <c r="G292" s="16"/>
       <c r="H292"/>
-      <c r="I292" s="26"/>
+      <c r="I292" s="25"/>
       <c r="K292" s="15"/>
-      <c r="L292" s="28"/>
+      <c r="L292" s="27"/>
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="11"/>
       <c r="B293" s="15"/>
       <c r="C293" s="13"/>
-      <c r="D293" s="32"/>
+      <c r="D293" s="31"/>
       <c r="E293" s="15"/>
       <c r="F293" s="15"/>
       <c r="G293" s="16"/>
       <c r="H293"/>
-      <c r="I293" s="26"/>
+      <c r="I293" s="25"/>
       <c r="K293" s="15"/>
-      <c r="L293" s="28"/>
+      <c r="L293" s="27"/>
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="11"/>
       <c r="B294" s="15"/>
       <c r="C294" s="13"/>
-      <c r="D294" s="32"/>
+      <c r="D294" s="31"/>
       <c r="E294" s="15"/>
       <c r="F294" s="15"/>
       <c r="G294" s="16"/>
       <c r="H294"/>
-      <c r="I294" s="26"/>
+      <c r="I294" s="25"/>
       <c r="K294" s="15"/>
-      <c r="L294" s="28"/>
+      <c r="L294" s="27"/>
     </row>
     <row r="295" spans="1:12">
       <c r="A295" s="11"/>
       <c r="B295" s="15"/>
       <c r="C295" s="13"/>
-      <c r="D295" s="32"/>
+      <c r="D295" s="31"/>
       <c r="E295" s="15"/>
       <c r="F295" s="15"/>
       <c r="G295" s="16"/>
       <c r="H295"/>
-      <c r="I295" s="26"/>
+      <c r="I295" s="25"/>
       <c r="K295" s="15"/>
-      <c r="L295" s="28"/>
+      <c r="L295" s="27"/>
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="11"/>
       <c r="B296" s="15"/>
       <c r="C296" s="13"/>
-      <c r="D296" s="32"/>
+      <c r="D296" s="31"/>
       <c r="E296" s="15"/>
       <c r="F296" s="15"/>
       <c r="G296" s="16"/>
       <c r="H296"/>
-      <c r="I296" s="26"/>
+      <c r="I296" s="25"/>
       <c r="K296" s="15"/>
-      <c r="L296" s="28"/>
+      <c r="L296" s="27"/>
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="11"/>
       <c r="B297" s="15"/>
       <c r="C297" s="13"/>
-      <c r="D297" s="32"/>
+      <c r="D297" s="31"/>
       <c r="E297" s="15"/>
       <c r="F297" s="15"/>
       <c r="G297" s="16"/>
       <c r="H297"/>
-      <c r="I297" s="26"/>
+      <c r="I297" s="25"/>
       <c r="K297" s="15"/>
-      <c r="L297" s="28"/>
+      <c r="L297" s="27"/>
     </row>
     <row r="298" spans="1:12">
       <c r="A298" s="11"/>
       <c r="B298" s="15"/>
       <c r="C298" s="13"/>
-      <c r="D298" s="32"/>
+      <c r="D298" s="31"/>
       <c r="E298" s="15"/>
       <c r="F298" s="15"/>
       <c r="G298" s="16"/>
       <c r="H298"/>
-      <c r="I298" s="26"/>
+      <c r="I298" s="25"/>
       <c r="K298" s="15"/>
-      <c r="L298" s="28"/>
+      <c r="L298" s="27"/>
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="11"/>
       <c r="B299" s="15"/>
       <c r="C299" s="13"/>
-      <c r="D299" s="32"/>
+      <c r="D299" s="31"/>
       <c r="E299" s="15"/>
       <c r="F299" s="15"/>
       <c r="G299" s="16"/>
       <c r="H299"/>
-      <c r="I299" s="26"/>
+      <c r="I299" s="25"/>
       <c r="K299" s="15"/>
-      <c r="L299" s="28"/>
+      <c r="L299" s="27"/>
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="11"/>
       <c r="B300" s="15"/>
       <c r="C300" s="13"/>
-      <c r="D300" s="32"/>
+      <c r="D300" s="31"/>
       <c r="E300" s="15"/>
       <c r="F300" s="15"/>
       <c r="G300" s="16"/>
       <c r="H300"/>
-      <c r="I300" s="26"/>
+      <c r="I300" s="25"/>
       <c r="K300" s="15"/>
-      <c r="L300" s="28"/>
+      <c r="L300" s="27"/>
     </row>
     <row r="301" spans="1:12">
       <c r="A301" s="11"/>
       <c r="B301" s="15"/>
       <c r="C301" s="13"/>
-      <c r="D301" s="32"/>
+      <c r="D301" s="31"/>
       <c r="E301" s="15"/>
       <c r="F301" s="15"/>
       <c r="G301" s="16"/>
       <c r="H301"/>
-      <c r="I301" s="26"/>
+      <c r="I301" s="25"/>
       <c r="K301" s="15"/>
-      <c r="L301" s="28"/>
+      <c r="L301" s="27"/>
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="11"/>
       <c r="B302" s="15"/>
       <c r="C302" s="13"/>
-      <c r="D302" s="32"/>
+      <c r="D302" s="31"/>
       <c r="E302" s="15"/>
       <c r="F302" s="15"/>
       <c r="G302" s="16"/>
       <c r="H302"/>
-      <c r="I302" s="26"/>
+      <c r="I302" s="25"/>
       <c r="K302" s="15"/>
-      <c r="L302" s="28"/>
+      <c r="L302" s="27"/>
     </row>
     <row r="303" spans="1:12">
       <c r="A303" s="11"/>
       <c r="B303" s="15"/>
       <c r="C303" s="13"/>
-      <c r="D303" s="32"/>
+      <c r="D303" s="31"/>
       <c r="E303" s="15"/>
       <c r="F303" s="15"/>
       <c r="G303" s="16"/>
       <c r="H303"/>
-      <c r="I303" s="26"/>
+      <c r="I303" s="25"/>
       <c r="K303" s="15"/>
-      <c r="L303" s="28"/>
+      <c r="L303" s="27"/>
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="11"/>
       <c r="B304" s="15"/>
       <c r="C304" s="13"/>
-      <c r="D304" s="32"/>
+      <c r="D304" s="31"/>
       <c r="E304" s="15"/>
       <c r="F304" s="15"/>
       <c r="G304" s="16"/>
       <c r="H304"/>
-      <c r="I304" s="26"/>
+      <c r="I304" s="25"/>
       <c r="K304" s="15"/>
-      <c r="L304" s="28"/>
+      <c r="L304" s="27"/>
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="11"/>
       <c r="B305" s="15"/>
       <c r="C305" s="13"/>
-      <c r="D305" s="32"/>
+      <c r="D305" s="31"/>
       <c r="E305" s="15"/>
       <c r="F305" s="15"/>
       <c r="G305" s="16"/>
       <c r="H305"/>
-      <c r="I305" s="26"/>
+      <c r="I305" s="25"/>
       <c r="K305" s="15"/>
-      <c r="L305" s="28"/>
+      <c r="L305" s="27"/>
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="11"/>
       <c r="B306" s="15"/>
       <c r="C306" s="13"/>
-      <c r="D306" s="32"/>
+      <c r="D306" s="31"/>
       <c r="E306" s="15"/>
       <c r="F306" s="15"/>
       <c r="G306" s="16"/>
       <c r="H306"/>
-      <c r="I306" s="26"/>
+      <c r="I306" s="25"/>
       <c r="K306" s="15"/>
-      <c r="L306" s="28"/>
+      <c r="L306" s="27"/>
     </row>
     <row r="307" spans="1:12">
       <c r="A307" s="11"/>
       <c r="B307" s="15"/>
       <c r="C307" s="13"/>
-      <c r="D307" s="32"/>
+      <c r="D307" s="31"/>
       <c r="E307" s="15"/>
       <c r="F307" s="15"/>
       <c r="G307" s="16"/>
       <c r="H307"/>
-      <c r="I307" s="26"/>
+      <c r="I307" s="25"/>
       <c r="K307" s="15"/>
-      <c r="L307" s="28"/>
+      <c r="L307" s="27"/>
     </row>
     <row r="308" spans="1:12">
       <c r="A308" s="11"/>
       <c r="B308" s="15"/>
       <c r="C308" s="13"/>
-      <c r="D308" s="32"/>
+      <c r="D308" s="31"/>
       <c r="E308" s="15"/>
       <c r="F308" s="15"/>
       <c r="G308" s="16"/>
       <c r="H308"/>
-      <c r="I308" s="26"/>
+      <c r="I308" s="25"/>
       <c r="K308" s="15"/>
-      <c r="L308" s="28"/>
+      <c r="L308" s="27"/>
     </row>
     <row r="309" spans="1:12">
       <c r="A309" s="11"/>
       <c r="B309" s="15"/>
       <c r="C309" s="13"/>
-      <c r="D309" s="32"/>
+      <c r="D309" s="31"/>
       <c r="E309" s="15"/>
       <c r="F309" s="15"/>
       <c r="G309" s="16"/>
       <c r="H309"/>
-      <c r="I309" s="26"/>
+      <c r="I309" s="25"/>
       <c r="K309" s="15"/>
-      <c r="L309" s="28"/>
+      <c r="L309" s="27"/>
     </row>
     <row r="310" spans="1:12">
       <c r="A310" s="11"/>
       <c r="B310" s="15"/>
       <c r="C310" s="13"/>
-      <c r="D310" s="32"/>
+      <c r="D310" s="31"/>
       <c r="E310" s="15"/>
       <c r="F310" s="15"/>
       <c r="G310" s="16"/>
       <c r="H310"/>
-      <c r="I310" s="26"/>
+      <c r="I310" s="25"/>
       <c r="K310" s="15"/>
-      <c r="L310" s="28"/>
+      <c r="L310" s="27"/>
     </row>
     <row r="311" spans="1:12">
       <c r="A311" s="11"/>
       <c r="B311" s="15"/>
       <c r="C311" s="13"/>
-      <c r="D311" s="32"/>
+      <c r="D311" s="31"/>
       <c r="E311" s="15"/>
       <c r="F311" s="15"/>
       <c r="G311" s="16"/>
       <c r="H311"/>
-      <c r="I311" s="26"/>
+      <c r="I311" s="25"/>
       <c r="K311" s="15"/>
-      <c r="L311" s="28"/>
+      <c r="L311" s="27"/>
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="11"/>
       <c r="B312" s="15"/>
       <c r="C312" s="13"/>
-      <c r="D312" s="32"/>
+      <c r="D312" s="31"/>
       <c r="E312" s="15"/>
       <c r="F312" s="15"/>
       <c r="G312" s="16"/>
       <c r="H312"/>
-      <c r="I312" s="26"/>
+      <c r="I312" s="25"/>
       <c r="K312" s="15"/>
-      <c r="L312" s="28"/>
+      <c r="L312" s="27"/>
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="11"/>
       <c r="B313" s="15"/>
       <c r="C313" s="13"/>
-      <c r="D313" s="32"/>
+      <c r="D313" s="31"/>
       <c r="E313" s="15"/>
       <c r="F313" s="15"/>
       <c r="G313" s="16"/>
       <c r="H313"/>
-      <c r="I313" s="26"/>
+      <c r="I313" s="25"/>
       <c r="K313" s="15"/>
-      <c r="L313" s="28"/>
+      <c r="L313" s="27"/>
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="11"/>
       <c r="B314" s="15"/>
       <c r="C314" s="13"/>
-      <c r="D314" s="32"/>
+      <c r="D314" s="31"/>
       <c r="E314" s="15"/>
       <c r="F314" s="15"/>
       <c r="G314" s="16"/>
       <c r="H314"/>
-      <c r="I314" s="26"/>
+      <c r="I314" s="25"/>
       <c r="K314" s="15"/>
-      <c r="L314" s="28"/>
+      <c r="L314" s="27"/>
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="11"/>
       <c r="B315" s="15"/>
       <c r="C315" s="13"/>
-      <c r="D315" s="32"/>
+      <c r="D315" s="31"/>
       <c r="E315" s="15"/>
       <c r="F315" s="15"/>
       <c r="G315" s="16"/>
       <c r="H315"/>
-      <c r="I315" s="26"/>
+      <c r="I315" s="25"/>
       <c r="K315" s="15"/>
-      <c r="L315" s="28"/>
+      <c r="L315" s="27"/>
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="11"/>
       <c r="B316" s="15"/>
       <c r="C316" s="13"/>
-      <c r="D316" s="32"/>
+      <c r="D316" s="31"/>
       <c r="E316" s="15"/>
       <c r="F316" s="15"/>
       <c r="G316" s="16"/>
       <c r="H316"/>
-      <c r="I316" s="26"/>
+      <c r="I316" s="25"/>
       <c r="K316" s="15"/>
-      <c r="L316" s="28"/>
+      <c r="L316" s="27"/>
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="11"/>
       <c r="B317" s="15"/>
       <c r="C317" s="13"/>
-      <c r="D317" s="32"/>
+      <c r="D317" s="31"/>
       <c r="E317" s="15"/>
       <c r="F317" s="15"/>
       <c r="G317" s="16"/>
       <c r="H317"/>
-      <c r="I317" s="26"/>
+      <c r="I317" s="25"/>
       <c r="K317" s="15"/>
-      <c r="L317" s="28"/>
+      <c r="L317" s="27"/>
     </row>
     <row r="318" spans="1:12">
       <c r="A318" s="11"/>
       <c r="B318" s="15"/>
       <c r="C318" s="13"/>
-      <c r="D318" s="32"/>
+      <c r="D318" s="31"/>
       <c r="E318" s="15"/>
       <c r="F318" s="15"/>
       <c r="G318" s="16"/>
       <c r="H318"/>
-      <c r="I318" s="26"/>
+      <c r="I318" s="25"/>
       <c r="K318" s="15"/>
-      <c r="L318" s="28"/>
+      <c r="L318" s="27"/>
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="11"/>
       <c r="B319" s="15"/>
       <c r="C319" s="13"/>
-      <c r="D319" s="32"/>
+      <c r="D319" s="31"/>
       <c r="E319" s="15"/>
       <c r="F319" s="15"/>
       <c r="G319" s="16"/>
       <c r="H319"/>
-      <c r="I319" s="26"/>
+      <c r="I319" s="25"/>
       <c r="K319" s="15"/>
-      <c r="L319" s="28"/>
+      <c r="L319" s="27"/>
     </row>
     <row r="320" spans="1:12">
       <c r="A320" s="11"/>
       <c r="B320" s="15"/>
       <c r="C320" s="13"/>
-      <c r="D320" s="32"/>
+      <c r="D320" s="31"/>
       <c r="E320" s="15"/>
       <c r="F320" s="15"/>
       <c r="G320" s="16"/>
       <c r="H320"/>
-      <c r="I320" s="26"/>
+      <c r="I320" s="25"/>
       <c r="K320" s="15"/>
-      <c r="L320" s="28"/>
+      <c r="L320" s="27"/>
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="11"/>
       <c r="B321" s="15"/>
       <c r="C321" s="13"/>
-      <c r="D321" s="32"/>
+      <c r="D321" s="31"/>
       <c r="E321" s="15"/>
       <c r="F321" s="15"/>
       <c r="G321" s="16"/>
       <c r="H321"/>
-      <c r="I321" s="26"/>
+      <c r="I321" s="25"/>
       <c r="K321" s="15"/>
-      <c r="L321" s="28"/>
+      <c r="L321" s="27"/>
     </row>
     <row r="322" spans="1:12">
       <c r="A322" s="11"/>
       <c r="B322" s="15"/>
       <c r="C322" s="13"/>
-      <c r="D322" s="32"/>
+      <c r="D322" s="31"/>
       <c r="E322" s="15"/>
       <c r="F322" s="15"/>
       <c r="G322" s="16"/>
       <c r="H322"/>
-      <c r="I322" s="26"/>
+      <c r="I322" s="25"/>
       <c r="K322" s="15"/>
-      <c r="L322" s="28"/>
+      <c r="L322" s="27"/>
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="11"/>
       <c r="B323" s="15"/>
       <c r="C323" s="13"/>
-      <c r="D323" s="32"/>
+      <c r="D323" s="31"/>
       <c r="E323" s="15"/>
       <c r="F323" s="15"/>
       <c r="G323" s="16"/>
       <c r="H323"/>
-      <c r="I323" s="26"/>
+      <c r="I323" s="25"/>
       <c r="K323" s="15"/>
-      <c r="L323" s="28"/>
+      <c r="L323" s="27"/>
     </row>
     <row r="324" spans="1:12">
       <c r="A324" s="11"/>
       <c r="B324" s="15"/>
       <c r="C324" s="13"/>
-      <c r="D324" s="32"/>
+      <c r="D324" s="31"/>
       <c r="E324" s="15"/>
       <c r="F324" s="15"/>
       <c r="G324" s="16"/>
       <c r="H324"/>
-      <c r="I324" s="26"/>
+      <c r="I324" s="25"/>
       <c r="K324" s="15"/>
-      <c r="L324" s="28"/>
+      <c r="L324" s="27"/>
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="11"/>
       <c r="B325" s="15"/>
       <c r="C325" s="13"/>
-      <c r="D325" s="32"/>
+      <c r="D325" s="31"/>
       <c r="E325" s="15"/>
       <c r="F325" s="15"/>
       <c r="G325" s="16"/>
       <c r="H325"/>
-      <c r="I325" s="26"/>
+      <c r="I325" s="25"/>
       <c r="K325" s="15"/>
-      <c r="L325" s="28"/>
+      <c r="L325" s="27"/>
     </row>
     <row r="326" spans="1:12">
       <c r="A326" s="11"/>
       <c r="B326" s="15"/>
       <c r="C326" s="13"/>
-      <c r="D326" s="32"/>
-      <c r="E326" s="34"/>
-      <c r="F326" s="34"/>
+      <c r="D326" s="31"/>
+      <c r="E326" s="33"/>
+      <c r="F326" s="33"/>
       <c r="G326" s="16"/>
       <c r="H326"/>
-      <c r="I326" s="26"/>
+      <c r="I326" s="25"/>
       <c r="K326" s="15"/>
-      <c r="L326" s="28"/>
+      <c r="L326" s="27"/>
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="11"/>
       <c r="B327" s="15"/>
       <c r="C327" s="13"/>
-      <c r="D327" s="32"/>
-      <c r="E327" s="34"/>
-      <c r="F327" s="34"/>
+      <c r="D327" s="31"/>
+      <c r="E327" s="33"/>
+      <c r="F327" s="33"/>
       <c r="G327" s="16"/>
       <c r="H327"/>
-      <c r="I327" s="26"/>
+      <c r="I327" s="25"/>
       <c r="K327" s="15"/>
-      <c r="L327" s="28"/>
+      <c r="L327" s="27"/>
     </row>
     <row r="328" spans="1:12">
       <c r="A328" s="11"/>
       <c r="B328" s="15"/>
       <c r="C328" s="13"/>
-      <c r="D328" s="32"/>
-      <c r="E328" s="34"/>
-      <c r="F328" s="34"/>
+      <c r="D328" s="31"/>
+      <c r="E328" s="33"/>
+      <c r="F328" s="33"/>
       <c r="G328" s="16"/>
       <c r="H328"/>
-      <c r="I328" s="26"/>
+      <c r="I328" s="25"/>
       <c r="K328" s="15"/>
-      <c r="L328" s="28"/>
+      <c r="L328" s="27"/>
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="11"/>
       <c r="B329" s="15"/>
       <c r="C329" s="13"/>
-      <c r="D329" s="32"/>
-      <c r="E329" s="34"/>
-      <c r="F329" s="34"/>
+      <c r="D329" s="31"/>
+      <c r="E329" s="33"/>
+      <c r="F329" s="33"/>
       <c r="G329" s="16"/>
       <c r="H329"/>
-      <c r="I329" s="26"/>
+      <c r="I329" s="25"/>
       <c r="K329" s="15"/>
-      <c r="L329" s="28"/>
+      <c r="L329" s="27"/>
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="11"/>
       <c r="B330" s="15"/>
       <c r="C330" s="13"/>
-      <c r="D330" s="32"/>
-      <c r="E330" s="34"/>
-      <c r="F330" s="34"/>
+      <c r="D330" s="31"/>
+      <c r="E330" s="33"/>
+      <c r="F330" s="33"/>
       <c r="G330" s="16"/>
       <c r="H330"/>
-      <c r="I330" s="26"/>
+      <c r="I330" s="25"/>
       <c r="K330" s="15"/>
-      <c r="L330" s="28"/>
+      <c r="L330" s="27"/>
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="11"/>
       <c r="B331" s="15"/>
       <c r="C331" s="13"/>
-      <c r="D331" s="32"/>
-      <c r="E331" s="34"/>
-      <c r="F331" s="34"/>
+      <c r="D331" s="31"/>
+      <c r="E331" s="33"/>
+      <c r="F331" s="33"/>
       <c r="G331" s="16"/>
       <c r="H331"/>
-      <c r="I331" s="26"/>
+      <c r="I331" s="25"/>
       <c r="K331" s="15"/>
-      <c r="L331" s="28"/>
+      <c r="L331" s="27"/>
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="11"/>
       <c r="B332" s="15"/>
       <c r="C332" s="13"/>
-      <c r="D332" s="32"/>
-      <c r="E332" s="34"/>
-      <c r="F332" s="34"/>
+      <c r="D332" s="31"/>
+      <c r="E332" s="33"/>
+      <c r="F332" s="33"/>
       <c r="G332" s="16"/>
       <c r="H332"/>
-      <c r="I332" s="26"/>
+      <c r="I332" s="25"/>
       <c r="K332" s="15"/>
-      <c r="L332" s="28"/>
+      <c r="L332" s="27"/>
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="11"/>
       <c r="B333" s="15"/>
       <c r="C333" s="13"/>
-      <c r="D333" s="32"/>
-      <c r="E333" s="34"/>
-      <c r="F333" s="34"/>
+      <c r="D333" s="31"/>
+      <c r="E333" s="33"/>
+      <c r="F333" s="33"/>
       <c r="G333" s="16"/>
       <c r="H333"/>
-      <c r="I333" s="26"/>
+      <c r="I333" s="25"/>
       <c r="K333" s="15"/>
-      <c r="L333" s="28"/>
+      <c r="L333" s="27"/>
     </row>
     <row r="334" spans="1:12">
       <c r="A334" s="11"/>
       <c r="B334" s="15"/>
       <c r="C334" s="13"/>
-      <c r="D334" s="32"/>
-      <c r="E334" s="34"/>
-      <c r="F334" s="34"/>
+      <c r="D334" s="31"/>
+      <c r="E334" s="33"/>
+      <c r="F334" s="33"/>
       <c r="G334" s="16"/>
       <c r="H334"/>
-      <c r="I334" s="26"/>
+      <c r="I334" s="25"/>
       <c r="K334" s="15"/>
-      <c r="L334" s="28"/>
+      <c r="L334" s="27"/>
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="11"/>
       <c r="B335" s="15"/>
       <c r="C335" s="13"/>
-      <c r="D335" s="32"/>
-      <c r="E335" s="34"/>
-      <c r="F335" s="34"/>
+      <c r="D335" s="31"/>
+      <c r="E335" s="33"/>
+      <c r="F335" s="33"/>
       <c r="G335" s="16"/>
       <c r="H335"/>
-      <c r="I335" s="26"/>
+      <c r="I335" s="25"/>
       <c r="K335" s="15"/>
-      <c r="L335" s="28"/>
+      <c r="L335" s="27"/>
     </row>
     <row r="336" spans="1:12">
       <c r="A336" s="11"/>
       <c r="B336" s="15"/>
       <c r="C336" s="13"/>
-      <c r="D336" s="32"/>
-      <c r="E336" s="34"/>
-      <c r="F336" s="34"/>
+      <c r="D336" s="31"/>
+      <c r="E336" s="33"/>
+      <c r="F336" s="33"/>
       <c r="G336" s="16"/>
       <c r="H336"/>
-      <c r="I336" s="26"/>
+      <c r="I336" s="25"/>
       <c r="K336" s="15"/>
-      <c r="L336" s="28"/>
+      <c r="L336" s="27"/>
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="11"/>
       <c r="B337" s="15"/>
       <c r="C337" s="13"/>
-      <c r="D337" s="32"/>
-      <c r="E337" s="34"/>
-      <c r="F337" s="34"/>
+      <c r="D337" s="31"/>
+      <c r="E337" s="33"/>
+      <c r="F337" s="33"/>
       <c r="G337" s="16"/>
       <c r="H337"/>
-      <c r="I337" s="26"/>
+      <c r="I337" s="25"/>
       <c r="K337" s="15"/>
-      <c r="L337" s="28"/>
+      <c r="L337" s="27"/>
     </row>
     <row r="338" spans="1:12">
       <c r="A338" s="11"/>
       <c r="B338" s="15"/>
       <c r="C338" s="13"/>
-      <c r="D338" s="32"/>
-      <c r="E338" s="34"/>
-      <c r="F338" s="34"/>
+      <c r="D338" s="31"/>
+      <c r="E338" s="33"/>
+      <c r="F338" s="33"/>
       <c r="G338" s="16"/>
       <c r="H338"/>
-      <c r="I338" s="26"/>
+      <c r="I338" s="25"/>
       <c r="K338" s="15"/>
-      <c r="L338" s="28"/>
+      <c r="L338" s="27"/>
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="11"/>
       <c r="B339" s="15"/>
       <c r="C339" s="13"/>
-      <c r="D339" s="32"/>
-      <c r="E339" s="34"/>
-      <c r="F339" s="34"/>
+      <c r="D339" s="31"/>
+      <c r="E339" s="33"/>
+      <c r="F339" s="33"/>
       <c r="G339" s="16"/>
       <c r="H339"/>
-      <c r="I339" s="26"/>
+      <c r="I339" s="25"/>
       <c r="K339" s="15"/>
-      <c r="L339" s="28"/>
+      <c r="L339" s="27"/>
     </row>
     <row r="340" spans="1:12">
       <c r="A340" s="11"/>
       <c r="B340" s="15"/>
       <c r="C340" s="13"/>
-      <c r="D340" s="32"/>
-      <c r="E340" s="34"/>
-      <c r="F340" s="34"/>
+      <c r="D340" s="31"/>
+      <c r="E340" s="33"/>
+      <c r="F340" s="33"/>
       <c r="G340" s="16"/>
       <c r="H340"/>
-      <c r="I340" s="26"/>
+      <c r="I340" s="25"/>
       <c r="K340" s="15"/>
-      <c r="L340" s="28"/>
+      <c r="L340" s="27"/>
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="11"/>
       <c r="B341" s="15"/>
       <c r="C341" s="13"/>
-      <c r="D341" s="32"/>
-      <c r="E341" s="34"/>
-      <c r="F341" s="34"/>
+      <c r="D341" s="31"/>
+      <c r="E341" s="33"/>
+      <c r="F341" s="33"/>
       <c r="G341" s="16"/>
       <c r="H341"/>
-      <c r="I341" s="26"/>
+      <c r="I341" s="25"/>
       <c r="K341" s="15"/>
-      <c r="L341" s="28"/>
+      <c r="L341" s="27"/>
     </row>
     <row r="342" spans="1:12">
       <c r="A342" s="11"/>
       <c r="B342" s="15"/>
       <c r="C342" s="13"/>
-      <c r="D342" s="32"/>
-      <c r="E342" s="34"/>
-      <c r="F342" s="34"/>
+      <c r="D342" s="31"/>
+      <c r="E342" s="33"/>
+      <c r="F342" s="33"/>
       <c r="G342" s="16"/>
       <c r="H342"/>
-      <c r="I342" s="26"/>
+      <c r="I342" s="25"/>
       <c r="K342" s="15"/>
-      <c r="L342" s="28"/>
+      <c r="L342" s="27"/>
     </row>
     <row r="343" spans="1:12">
       <c r="A343" s="11"/>
       <c r="B343" s="15"/>
       <c r="C343" s="13"/>
-      <c r="D343" s="32"/>
-      <c r="E343" s="34"/>
-      <c r="F343" s="34"/>
+      <c r="D343" s="31"/>
+      <c r="E343" s="33"/>
+      <c r="F343" s="33"/>
       <c r="G343" s="16"/>
       <c r="H343"/>
-      <c r="I343" s="26"/>
+      <c r="I343" s="25"/>
       <c r="K343" s="15"/>
-      <c r="L343" s="28"/>
+      <c r="L343" s="27"/>
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="11"/>
       <c r="B344" s="15"/>
       <c r="C344" s="13"/>
-      <c r="D344" s="32"/>
-      <c r="E344" s="34"/>
-      <c r="F344" s="34"/>
+      <c r="D344" s="31"/>
+      <c r="E344" s="33"/>
+      <c r="F344" s="33"/>
       <c r="G344" s="16"/>
       <c r="H344"/>
-      <c r="I344" s="26"/>
+      <c r="I344" s="25"/>
       <c r="K344" s="15"/>
-      <c r="L344" s="28"/>
+      <c r="L344" s="27"/>
     </row>
     <row r="345" spans="1:12">
       <c r="A345" s="11"/>
       <c r="B345" s="15"/>
       <c r="C345" s="13"/>
-      <c r="D345" s="32"/>
-      <c r="E345" s="34"/>
-      <c r="F345" s="34"/>
+      <c r="D345" s="31"/>
+      <c r="E345" s="33"/>
+      <c r="F345" s="33"/>
       <c r="G345" s="16"/>
       <c r="H345"/>
-      <c r="I345" s="26"/>
+      <c r="I345" s="25"/>
       <c r="K345" s="15"/>
-      <c r="L345" s="28"/>
+      <c r="L345" s="27"/>
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="11"/>
       <c r="B346" s="15"/>
       <c r="C346" s="13"/>
-      <c r="D346" s="32"/>
-      <c r="E346" s="34"/>
-      <c r="F346" s="34"/>
+      <c r="D346" s="31"/>
+      <c r="E346" s="33"/>
+      <c r="F346" s="33"/>
       <c r="G346" s="16"/>
       <c r="H346"/>
-      <c r="I346" s="26"/>
+      <c r="I346" s="25"/>
       <c r="K346" s="15"/>
-      <c r="L346" s="28"/>
+      <c r="L346" s="27"/>
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="11"/>
       <c r="B347" s="15"/>
       <c r="C347" s="13"/>
-      <c r="D347" s="32"/>
-      <c r="E347" s="34"/>
-      <c r="F347" s="34"/>
+      <c r="D347" s="31"/>
+      <c r="E347" s="33"/>
+      <c r="F347" s="33"/>
       <c r="G347" s="16"/>
       <c r="H347"/>
-      <c r="I347" s="26"/>
+      <c r="I347" s="25"/>
       <c r="K347" s="15"/>
-      <c r="L347" s="28"/>
+      <c r="L347" s="27"/>
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="11"/>
       <c r="B348" s="15"/>
       <c r="C348" s="13"/>
-      <c r="D348" s="32"/>
-      <c r="E348" s="34"/>
-      <c r="F348" s="34"/>
+      <c r="D348" s="31"/>
+      <c r="E348" s="33"/>
+      <c r="F348" s="33"/>
       <c r="G348" s="16"/>
       <c r="H348"/>
-      <c r="I348" s="26"/>
+      <c r="I348" s="25"/>
       <c r="K348" s="15"/>
-      <c r="L348" s="28"/>
+      <c r="L348" s="27"/>
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="11"/>
       <c r="B349" s="15"/>
       <c r="C349" s="13"/>
-      <c r="D349" s="32"/>
-      <c r="E349" s="34"/>
-      <c r="F349" s="34"/>
+      <c r="D349" s="31"/>
+      <c r="E349" s="33"/>
+      <c r="F349" s="33"/>
       <c r="G349" s="16"/>
       <c r="H349"/>
-      <c r="I349" s="26"/>
+      <c r="I349" s="25"/>
       <c r="K349" s="15"/>
-      <c r="L349" s="28"/>
+      <c r="L349" s="27"/>
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="11"/>
       <c r="B350" s="15"/>
       <c r="C350" s="13"/>
-      <c r="D350" s="32"/>
-      <c r="E350" s="34"/>
-      <c r="F350" s="34"/>
+      <c r="D350" s="31"/>
+      <c r="E350" s="33"/>
+      <c r="F350" s="33"/>
       <c r="G350" s="16"/>
       <c r="H350"/>
-      <c r="I350" s="26"/>
+      <c r="I350" s="25"/>
       <c r="K350" s="15"/>
-      <c r="L350" s="28"/>
+      <c r="L350" s="27"/>
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="11"/>
       <c r="B351" s="15"/>
       <c r="C351" s="13"/>
-      <c r="D351" s="32"/>
-      <c r="E351" s="34"/>
-      <c r="F351" s="34"/>
+      <c r="D351" s="31"/>
+      <c r="E351" s="33"/>
+      <c r="F351" s="33"/>
       <c r="G351" s="16"/>
       <c r="H351"/>
-      <c r="I351" s="26"/>
+      <c r="I351" s="25"/>
       <c r="K351" s="15"/>
-      <c r="L351" s="28"/>
+      <c r="L351" s="27"/>
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="11"/>
       <c r="B352" s="15"/>
       <c r="C352" s="13"/>
-      <c r="D352" s="32"/>
-      <c r="E352" s="34"/>
-      <c r="F352" s="34"/>
+      <c r="D352" s="31"/>
+      <c r="E352" s="33"/>
+      <c r="F352" s="33"/>
       <c r="G352" s="16"/>
       <c r="H352"/>
-      <c r="I352" s="26"/>
+      <c r="I352" s="25"/>
       <c r="K352" s="15"/>
-      <c r="L352" s="28"/>
+      <c r="L352" s="27"/>
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="11"/>
       <c r="B353" s="15"/>
       <c r="C353" s="13"/>
-      <c r="D353" s="32"/>
-      <c r="E353" s="34"/>
-      <c r="F353" s="34"/>
+      <c r="D353" s="31"/>
+      <c r="E353" s="33"/>
+      <c r="F353" s="33"/>
       <c r="G353" s="16"/>
       <c r="H353"/>
-      <c r="I353" s="26"/>
+      <c r="I353" s="25"/>
       <c r="K353" s="15"/>
-      <c r="L353" s="28"/>
+      <c r="L353" s="27"/>
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="11"/>
       <c r="B354" s="15"/>
       <c r="C354" s="13"/>
-      <c r="D354" s="32"/>
-      <c r="E354" s="34"/>
-      <c r="F354" s="34"/>
+      <c r="D354" s="31"/>
+      <c r="E354" s="33"/>
+      <c r="F354" s="33"/>
       <c r="G354" s="16"/>
       <c r="H354"/>
-      <c r="I354" s="26"/>
+      <c r="I354" s="25"/>
       <c r="K354" s="15"/>
-      <c r="L354" s="28"/>
+      <c r="L354" s="27"/>
     </row>
     <row r="355" spans="1:12">
       <c r="A355" s="11"/>
       <c r="B355" s="15"/>
       <c r="C355" s="13"/>
-      <c r="D355" s="32"/>
-      <c r="E355" s="34"/>
-      <c r="F355" s="34"/>
+      <c r="D355" s="31"/>
+      <c r="E355" s="33"/>
+      <c r="F355" s="33"/>
       <c r="G355" s="16"/>
       <c r="H355"/>
-      <c r="I355" s="26"/>
+      <c r="I355" s="25"/>
       <c r="K355" s="15"/>
-      <c r="L355" s="28"/>
+      <c r="L355" s="27"/>
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="11"/>
       <c r="B356" s="15"/>
       <c r="C356" s="13"/>
-      <c r="D356" s="32"/>
-      <c r="E356" s="34"/>
-      <c r="F356" s="34"/>
+      <c r="D356" s="31"/>
+      <c r="E356" s="33"/>
+      <c r="F356" s="33"/>
       <c r="G356" s="16"/>
       <c r="H356"/>
-      <c r="I356" s="26"/>
+      <c r="I356" s="25"/>
       <c r="K356" s="15"/>
-      <c r="L356" s="28"/>
+      <c r="L356" s="27"/>
     </row>
     <row r="357" spans="1:12">
       <c r="A357" s="11"/>
       <c r="B357" s="15"/>
       <c r="C357" s="13"/>
-      <c r="D357" s="32"/>
-      <c r="E357" s="34"/>
-      <c r="F357" s="34"/>
+      <c r="D357" s="31"/>
+      <c r="E357" s="33"/>
+      <c r="F357" s="33"/>
       <c r="G357" s="16"/>
       <c r="H357"/>
-      <c r="I357" s="26"/>
+      <c r="I357" s="25"/>
       <c r="K357" s="15"/>
-      <c r="L357" s="28"/>
+      <c r="L357" s="27"/>
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="11"/>
       <c r="B358" s="15"/>
       <c r="C358" s="13"/>
-      <c r="D358" s="32"/>
-      <c r="E358" s="34"/>
-      <c r="F358" s="34"/>
+      <c r="D358" s="31"/>
+      <c r="E358" s="33"/>
+      <c r="F358" s="33"/>
       <c r="G358" s="16"/>
       <c r="H358"/>
-      <c r="I358" s="26"/>
+      <c r="I358" s="25"/>
       <c r="K358" s="15"/>
-      <c r="L358" s="28"/>
+      <c r="L358" s="27"/>
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="11"/>
       <c r="B359" s="15"/>
       <c r="C359" s="13"/>
-      <c r="D359" s="32"/>
-      <c r="E359" s="34"/>
-      <c r="F359" s="34"/>
+      <c r="D359" s="31"/>
+      <c r="E359" s="33"/>
+      <c r="F359" s="33"/>
       <c r="G359" s="16"/>
       <c r="H359"/>
-      <c r="I359" s="26"/>
+      <c r="I359" s="25"/>
       <c r="K359" s="15"/>
-      <c r="L359" s="28"/>
+      <c r="L359" s="27"/>
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="11"/>
       <c r="B360" s="15"/>
       <c r="C360" s="13"/>
-      <c r="D360" s="32"/>
-      <c r="E360" s="34"/>
-      <c r="F360" s="34"/>
+      <c r="D360" s="31"/>
+      <c r="E360" s="33"/>
+      <c r="F360" s="33"/>
       <c r="G360" s="16"/>
       <c r="H360"/>
-      <c r="I360" s="26"/>
+      <c r="I360" s="25"/>
       <c r="K360" s="15"/>
-      <c r="L360" s="28"/>
+      <c r="L360" s="27"/>
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="11"/>
       <c r="B361" s="15"/>
       <c r="C361" s="13"/>
-      <c r="D361" s="32"/>
-      <c r="E361" s="34"/>
-      <c r="F361" s="34"/>
+      <c r="D361" s="31"/>
+      <c r="E361" s="33"/>
+      <c r="F361" s="33"/>
       <c r="G361" s="16"/>
       <c r="H361"/>
-      <c r="I361" s="26"/>
+      <c r="I361" s="25"/>
       <c r="K361" s="15"/>
-      <c r="L361" s="28"/>
+      <c r="L361" s="27"/>
     </row>
     <row r="362" spans="1:12">
       <c r="A362" s="11"/>
       <c r="B362" s="15"/>
       <c r="C362" s="13"/>
-      <c r="D362" s="32"/>
-      <c r="E362" s="34"/>
-      <c r="F362" s="34"/>
+      <c r="D362" s="31"/>
+      <c r="E362" s="33"/>
+      <c r="F362" s="33"/>
       <c r="G362" s="16"/>
       <c r="H362"/>
-      <c r="I362" s="26"/>
+      <c r="I362" s="25"/>
       <c r="K362" s="15"/>
-      <c r="L362" s="28"/>
+      <c r="L362" s="27"/>
     </row>
     <row r="363" spans="1:12">
       <c r="A363" s="11"/>
       <c r="B363" s="15"/>
       <c r="C363" s="13"/>
-      <c r="D363" s="32"/>
-      <c r="E363" s="34"/>
-      <c r="F363" s="34"/>
+      <c r="D363" s="31"/>
+      <c r="E363" s="33"/>
+      <c r="F363" s="33"/>
       <c r="G363" s="16"/>
       <c r="H363"/>
-      <c r="I363" s="26"/>
+      <c r="I363" s="25"/>
       <c r="K363" s="15"/>
-      <c r="L363" s="28"/>
+      <c r="L363" s="27"/>
     </row>
     <row r="364" spans="1:12">
       <c r="A364" s="11"/>
       <c r="B364" s="15"/>
       <c r="C364" s="13"/>
-      <c r="D364" s="32"/>
-      <c r="E364" s="34"/>
-      <c r="F364" s="34"/>
+      <c r="D364" s="31"/>
+      <c r="E364" s="33"/>
+      <c r="F364" s="33"/>
       <c r="G364" s="16"/>
       <c r="H364"/>
-      <c r="I364" s="26"/>
+      <c r="I364" s="25"/>
       <c r="K364" s="15"/>
-      <c r="L364" s="28"/>
+      <c r="L364" s="27"/>
     </row>
     <row r="365" spans="1:12">
       <c r="A365" s="11"/>
       <c r="B365" s="15"/>
       <c r="C365" s="13"/>
-      <c r="D365" s="32"/>
-      <c r="E365" s="34"/>
-      <c r="F365" s="34"/>
+      <c r="D365" s="31"/>
+      <c r="E365" s="33"/>
+      <c r="F365" s="33"/>
       <c r="G365" s="16"/>
       <c r="H365"/>
-      <c r="I365" s="26"/>
+      <c r="I365" s="25"/>
       <c r="K365" s="15"/>
-      <c r="L365" s="28"/>
+      <c r="L365" s="27"/>
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="11"/>
       <c r="B366" s="15"/>
       <c r="C366" s="13"/>
-      <c r="D366" s="32"/>
-      <c r="E366" s="34"/>
-      <c r="F366" s="34"/>
+      <c r="D366" s="31"/>
+      <c r="E366" s="33"/>
+      <c r="F366" s="33"/>
       <c r="G366" s="16"/>
       <c r="H366"/>
-      <c r="I366" s="26"/>
+      <c r="I366" s="25"/>
       <c r="K366" s="15"/>
-      <c r="L366" s="28"/>
+      <c r="L366" s="27"/>
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="11"/>
       <c r="B367" s="15"/>
       <c r="C367" s="13"/>
-      <c r="D367" s="32"/>
-      <c r="E367" s="34"/>
-      <c r="F367" s="34"/>
+      <c r="D367" s="31"/>
+      <c r="E367" s="33"/>
+      <c r="F367" s="33"/>
       <c r="G367" s="16"/>
       <c r="H367"/>
-      <c r="I367" s="26"/>
+      <c r="I367" s="25"/>
       <c r="K367" s="15"/>
-      <c r="L367" s="28"/>
+      <c r="L367" s="27"/>
     </row>
     <row r="368" spans="1:12">
       <c r="A368" s="11"/>
       <c r="B368" s="15"/>
       <c r="C368" s="13"/>
-      <c r="D368" s="32"/>
-      <c r="E368" s="34"/>
-      <c r="F368" s="34"/>
+      <c r="D368" s="31"/>
+      <c r="E368" s="33"/>
+      <c r="F368" s="33"/>
       <c r="G368" s="16"/>
       <c r="H368"/>
-      <c r="I368" s="26"/>
+      <c r="I368" s="25"/>
       <c r="K368" s="15"/>
-      <c r="L368" s="28"/>
+      <c r="L368" s="27"/>
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="11"/>
       <c r="B369" s="15"/>
       <c r="C369" s="13"/>
-      <c r="D369" s="32"/>
-      <c r="E369" s="34"/>
-      <c r="F369" s="34"/>
+      <c r="D369" s="31"/>
+      <c r="E369" s="33"/>
+      <c r="F369" s="33"/>
       <c r="G369" s="16"/>
       <c r="H369"/>
-      <c r="I369" s="26"/>
+      <c r="I369" s="25"/>
       <c r="K369" s="15"/>
-      <c r="L369" s="28"/>
+      <c r="L369" s="27"/>
     </row>
     <row r="370" spans="1:12">
       <c r="A370" s="11"/>
       <c r="B370" s="15"/>
       <c r="C370" s="13"/>
-      <c r="D370" s="32"/>
-      <c r="E370" s="34"/>
-      <c r="F370" s="34"/>
+      <c r="D370" s="31"/>
+      <c r="E370" s="33"/>
+      <c r="F370" s="33"/>
       <c r="G370" s="16"/>
       <c r="H370"/>
-      <c r="I370" s="26"/>
+      <c r="I370" s="25"/>
       <c r="K370" s="15"/>
-      <c r="L370" s="28"/>
+      <c r="L370" s="27"/>
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="11"/>
       <c r="B371" s="15"/>
       <c r="C371" s="13"/>
-      <c r="D371" s="32"/>
-      <c r="E371" s="34"/>
-      <c r="F371" s="34"/>
+      <c r="D371" s="31"/>
+      <c r="E371" s="33"/>
+      <c r="F371" s="33"/>
       <c r="G371" s="16"/>
       <c r="H371"/>
-      <c r="I371" s="26"/>
+      <c r="I371" s="25"/>
       <c r="K371" s="15"/>
-      <c r="L371" s="28"/>
+      <c r="L371" s="27"/>
     </row>
     <row r="372" spans="1:12">
       <c r="A372" s="11"/>
       <c r="B372" s="15"/>
       <c r="C372" s="13"/>
-      <c r="D372" s="32"/>
-      <c r="E372" s="34"/>
-      <c r="F372" s="34"/>
+      <c r="D372" s="31"/>
+      <c r="E372" s="33"/>
+      <c r="F372" s="33"/>
       <c r="G372" s="16"/>
       <c r="H372"/>
-      <c r="I372" s="26"/>
+      <c r="I372" s="25"/>
       <c r="K372" s="15"/>
-      <c r="L372" s="28"/>
+      <c r="L372" s="27"/>
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="11"/>
       <c r="B373" s="15"/>
       <c r="C373" s="13"/>
-      <c r="D373" s="32"/>
-      <c r="E373" s="34"/>
-      <c r="F373" s="34"/>
+      <c r="D373" s="31"/>
+      <c r="E373" s="33"/>
+      <c r="F373" s="33"/>
       <c r="G373" s="16"/>
       <c r="H373"/>
-      <c r="I373" s="26"/>
+      <c r="I373" s="25"/>
       <c r="K373" s="15"/>
-      <c r="L373" s="28"/>
+      <c r="L373" s="27"/>
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="11"/>
       <c r="B374" s="15"/>
       <c r="C374" s="13"/>
-      <c r="D374" s="32"/>
-      <c r="E374" s="34"/>
-      <c r="F374" s="34"/>
+      <c r="D374" s="31"/>
+      <c r="E374" s="33"/>
+      <c r="F374" s="33"/>
       <c r="G374" s="16"/>
       <c r="H374"/>
-      <c r="I374" s="26"/>
+      <c r="I374" s="25"/>
       <c r="K374" s="15"/>
-      <c r="L374" s="28"/>
+      <c r="L374" s="27"/>
     </row>
     <row r="375" spans="1:12">
       <c r="A375" s="11"/>
       <c r="B375" s="15"/>
       <c r="C375" s="13"/>
-      <c r="D375" s="32"/>
-      <c r="E375" s="34"/>
-      <c r="F375" s="34"/>
+      <c r="D375" s="31"/>
+      <c r="E375" s="33"/>
+      <c r="F375" s="33"/>
       <c r="G375" s="16"/>
       <c r="H375"/>
-      <c r="I375" s="26"/>
+      <c r="I375" s="25"/>
       <c r="K375" s="15"/>
-      <c r="L375" s="28"/>
+      <c r="L375" s="27"/>
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="11"/>
       <c r="B376" s="15"/>
       <c r="C376" s="13"/>
-      <c r="D376" s="32"/>
-      <c r="E376" s="34"/>
-      <c r="F376" s="34"/>
+      <c r="D376" s="31"/>
+      <c r="E376" s="33"/>
+      <c r="F376" s="33"/>
       <c r="G376" s="16"/>
       <c r="H376"/>
-      <c r="I376" s="26"/>
+      <c r="I376" s="25"/>
       <c r="K376" s="15"/>
-      <c r="L376" s="28"/>
+      <c r="L376" s="27"/>
     </row>
     <row r="377" spans="1:12">
       <c r="A377" s="11"/>
       <c r="B377" s="15"/>
       <c r="C377" s="13"/>
-      <c r="D377" s="32"/>
-      <c r="E377" s="34"/>
-      <c r="F377" s="34"/>
+      <c r="D377" s="31"/>
+      <c r="E377" s="33"/>
+      <c r="F377" s="33"/>
       <c r="G377" s="16"/>
       <c r="H377"/>
-      <c r="I377" s="26"/>
+      <c r="I377" s="25"/>
       <c r="K377" s="15"/>
-      <c r="L377" s="28"/>
+      <c r="L377" s="27"/>
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="11"/>
       <c r="B378" s="15"/>
       <c r="C378" s="13"/>
-      <c r="D378" s="32"/>
-      <c r="E378" s="34"/>
-      <c r="F378" s="34"/>
+      <c r="D378" s="31"/>
+      <c r="E378" s="33"/>
+      <c r="F378" s="33"/>
       <c r="G378" s="16"/>
       <c r="H378"/>
-      <c r="I378" s="26"/>
+      <c r="I378" s="25"/>
       <c r="K378" s="15"/>
-      <c r="L378" s="28"/>
+      <c r="L378" s="27"/>
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="11"/>
       <c r="B379" s="15"/>
       <c r="C379" s="13"/>
-      <c r="D379" s="32"/>
-      <c r="E379" s="34"/>
-      <c r="F379" s="34"/>
+      <c r="D379" s="31"/>
+      <c r="E379" s="33"/>
+      <c r="F379" s="33"/>
       <c r="G379" s="16"/>
       <c r="H379"/>
-      <c r="I379" s="26"/>
+      <c r="I379" s="25"/>
       <c r="K379" s="15"/>
-      <c r="L379" s="28"/>
+      <c r="L379" s="27"/>
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="11"/>
       <c r="B380" s="15"/>
       <c r="C380" s="13"/>
-      <c r="D380" s="32"/>
-      <c r="E380" s="34"/>
-      <c r="F380" s="34"/>
+      <c r="D380" s="31"/>
+      <c r="E380" s="33"/>
+      <c r="F380" s="33"/>
       <c r="G380" s="16"/>
       <c r="H380"/>
-      <c r="I380" s="26"/>
+      <c r="I380" s="25"/>
       <c r="K380" s="15"/>
-      <c r="L380" s="28"/>
+      <c r="L380" s="27"/>
     </row>
     <row r="381" spans="1:12">
       <c r="A381" s="11"/>
       <c r="B381" s="15"/>
       <c r="C381" s="13"/>
-      <c r="D381" s="32"/>
-      <c r="E381" s="34"/>
-      <c r="F381" s="34"/>
+      <c r="D381" s="31"/>
+      <c r="E381" s="33"/>
+      <c r="F381" s="33"/>
       <c r="G381" s="16"/>
       <c r="H381"/>
-      <c r="I381" s="26"/>
+      <c r="I381" s="25"/>
       <c r="K381" s="15"/>
-      <c r="L381" s="28"/>
+      <c r="L381" s="27"/>
     </row>
     <row r="382" spans="1:12">
       <c r="A382" s="11"/>
       <c r="B382" s="15"/>
       <c r="C382" s="13"/>
-      <c r="D382" s="32"/>
-      <c r="E382" s="34"/>
-      <c r="F382" s="34"/>
+      <c r="D382" s="31"/>
+      <c r="E382" s="33"/>
+      <c r="F382" s="33"/>
       <c r="G382" s="16"/>
       <c r="H382"/>
-      <c r="I382" s="26"/>
+      <c r="I382" s="25"/>
       <c r="K382" s="15"/>
-      <c r="L382" s="28"/>
+      <c r="L382" s="27"/>
     </row>
     <row r="383" spans="1:12">
       <c r="A383" s="11"/>
       <c r="B383" s="15"/>
       <c r="C383" s="13"/>
-      <c r="D383" s="32"/>
-      <c r="E383" s="34"/>
-      <c r="F383" s="34"/>
+      <c r="D383" s="31"/>
+      <c r="E383" s="33"/>
+      <c r="F383" s="33"/>
       <c r="G383" s="16"/>
       <c r="H383"/>
-      <c r="I383" s="26"/>
+      <c r="I383" s="25"/>
       <c r="K383" s="15"/>
-      <c r="L383" s="28"/>
+      <c r="L383" s="27"/>
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="11"/>
       <c r="B384" s="15"/>
       <c r="C384" s="13"/>
-      <c r="D384" s="32"/>
-      <c r="E384" s="34"/>
-      <c r="F384" s="34"/>
+      <c r="D384" s="31"/>
+      <c r="E384" s="33"/>
+      <c r="F384" s="33"/>
       <c r="G384" s="16"/>
       <c r="H384"/>
-      <c r="I384" s="26"/>
+      <c r="I384" s="25"/>
       <c r="K384" s="15"/>
-      <c r="L384" s="28"/>
+      <c r="L384" s="27"/>
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="11"/>
       <c r="B385" s="15"/>
       <c r="C385" s="13"/>
-      <c r="D385" s="32"/>
-      <c r="E385" s="34"/>
-      <c r="F385" s="34"/>
+      <c r="D385" s="31"/>
+      <c r="E385" s="33"/>
+      <c r="F385" s="33"/>
       <c r="G385" s="16"/>
       <c r="H385"/>
-      <c r="I385" s="26"/>
+      <c r="I385" s="25"/>
       <c r="K385" s="15"/>
-      <c r="L385" s="28"/>
+      <c r="L385" s="27"/>
     </row>
     <row r="386" spans="1:12">
       <c r="A386" s="11"/>
       <c r="B386" s="15"/>
       <c r="C386" s="13"/>
-      <c r="D386" s="32"/>
-      <c r="E386" s="34"/>
-      <c r="F386" s="34"/>
+      <c r="D386" s="31"/>
+      <c r="E386" s="33"/>
+      <c r="F386" s="33"/>
       <c r="G386" s="16"/>
       <c r="H386"/>
-      <c r="I386" s="26"/>
+      <c r="I386" s="25"/>
       <c r="K386" s="15"/>
-      <c r="L386" s="28"/>
+      <c r="L386" s="27"/>
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="11"/>
       <c r="B387" s="15"/>
       <c r="C387" s="13"/>
-      <c r="D387" s="32"/>
-      <c r="E387" s="34"/>
-      <c r="F387" s="34"/>
+      <c r="D387" s="31"/>
+      <c r="E387" s="33"/>
+      <c r="F387" s="33"/>
       <c r="G387" s="16"/>
       <c r="H387"/>
-      <c r="I387" s="26"/>
+      <c r="I387" s="25"/>
       <c r="K387" s="15"/>
-      <c r="L387" s="28"/>
+      <c r="L387" s="27"/>
     </row>
     <row r="388" spans="1:12">
       <c r="A388" s="11"/>
       <c r="B388" s="15"/>
       <c r="C388" s="13"/>
-      <c r="D388" s="32"/>
-      <c r="E388" s="34"/>
-      <c r="F388" s="34"/>
+      <c r="D388" s="31"/>
+      <c r="E388" s="33"/>
+      <c r="F388" s="33"/>
       <c r="G388" s="16"/>
       <c r="H388"/>
-      <c r="I388" s="26"/>
+      <c r="I388" s="25"/>
       <c r="K388" s="15"/>
-      <c r="L388" s="28"/>
+      <c r="L388" s="27"/>
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="11"/>
       <c r="B389" s="15"/>
       <c r="C389" s="13"/>
-      <c r="D389" s="32"/>
-      <c r="E389" s="34"/>
-      <c r="F389" s="34"/>
+      <c r="D389" s="31"/>
+      <c r="E389" s="33"/>
+      <c r="F389" s="33"/>
       <c r="G389" s="16"/>
       <c r="H389"/>
-      <c r="I389" s="26"/>
+      <c r="I389" s="25"/>
       <c r="K389" s="15"/>
-      <c r="L389" s="28"/>
+      <c r="L389" s="27"/>
     </row>
     <row r="390" spans="1:12">
       <c r="A390" s="11"/>
       <c r="B390" s="15"/>
       <c r="C390" s="13"/>
-      <c r="D390" s="32"/>
-      <c r="E390" s="34"/>
-      <c r="F390" s="34"/>
+      <c r="D390" s="31"/>
+      <c r="E390" s="33"/>
+      <c r="F390" s="33"/>
       <c r="G390" s="16"/>
       <c r="H390"/>
-      <c r="I390" s="26"/>
+      <c r="I390" s="25"/>
       <c r="K390" s="15"/>
-      <c r="L390" s="28"/>
+      <c r="L390" s="27"/>
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="11"/>
       <c r="B391" s="15"/>
       <c r="C391" s="13"/>
-      <c r="D391" s="32"/>
-      <c r="E391" s="34"/>
-      <c r="F391" s="34"/>
+      <c r="D391" s="31"/>
+      <c r="E391" s="33"/>
+      <c r="F391" s="33"/>
       <c r="G391" s="16"/>
       <c r="H391"/>
-      <c r="I391" s="26"/>
+      <c r="I391" s="25"/>
       <c r="K391" s="15"/>
-      <c r="L391" s="28"/>
+      <c r="L391" s="27"/>
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="11"/>
       <c r="B392" s="15"/>
       <c r="C392" s="13"/>
-      <c r="D392" s="32"/>
-      <c r="E392" s="34"/>
-      <c r="F392" s="34"/>
+      <c r="D392" s="31"/>
+      <c r="E392" s="33"/>
+      <c r="F392" s="33"/>
       <c r="G392" s="16"/>
       <c r="H392"/>
-      <c r="I392" s="26"/>
+      <c r="I392" s="25"/>
       <c r="K392" s="15"/>
-      <c r="L392" s="28"/>
+      <c r="L392" s="27"/>
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="11"/>
       <c r="B393" s="15"/>
       <c r="C393" s="13"/>
-      <c r="D393" s="32"/>
-      <c r="E393" s="34"/>
-      <c r="F393" s="34"/>
+      <c r="D393" s="31"/>
+      <c r="E393" s="33"/>
+      <c r="F393" s="33"/>
       <c r="G393" s="16"/>
       <c r="H393"/>
-      <c r="I393" s="26"/>
+      <c r="I393" s="25"/>
       <c r="K393" s="15"/>
-      <c r="L393" s="28"/>
+      <c r="L393" s="27"/>
     </row>
     <row r="394" spans="1:12">
       <c r="A394" s="11"/>
       <c r="B394" s="15"/>
       <c r="C394" s="13"/>
-      <c r="D394" s="32"/>
-      <c r="E394" s="34"/>
-      <c r="F394" s="34"/>
+      <c r="D394" s="31"/>
+      <c r="E394" s="33"/>
+      <c r="F394" s="33"/>
       <c r="G394" s="16"/>
       <c r="H394"/>
-      <c r="I394" s="26"/>
+      <c r="I394" s="25"/>
       <c r="K394" s="15"/>
-      <c r="L394" s="28"/>
+      <c r="L394" s="27"/>
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="11"/>
       <c r="B395" s="15"/>
       <c r="C395" s="13"/>
-      <c r="D395" s="32"/>
-      <c r="E395" s="34"/>
-      <c r="F395" s="34"/>
+      <c r="D395" s="31"/>
+      <c r="E395" s="33"/>
+      <c r="F395" s="33"/>
       <c r="G395" s="16"/>
       <c r="H395"/>
-      <c r="I395" s="26"/>
+      <c r="I395" s="25"/>
       <c r="K395" s="15"/>
-      <c r="L395" s="28"/>
+      <c r="L395" s="27"/>
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="11"/>
       <c r="B396" s="15"/>
       <c r="C396" s="13"/>
-      <c r="D396" s="32"/>
-      <c r="E396" s="34"/>
-      <c r="F396" s="34"/>
+      <c r="D396" s="31"/>
+      <c r="E396" s="33"/>
+      <c r="F396" s="33"/>
       <c r="G396" s="16"/>
       <c r="H396"/>
-      <c r="I396" s="26"/>
+      <c r="I396" s="25"/>
       <c r="K396" s="15"/>
-      <c r="L396" s="28"/>
+      <c r="L396" s="27"/>
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="11"/>
       <c r="B397" s="15"/>
       <c r="C397" s="13"/>
-      <c r="D397" s="32"/>
-      <c r="E397" s="34"/>
-      <c r="F397" s="34"/>
+      <c r="D397" s="31"/>
+      <c r="E397" s="33"/>
+      <c r="F397" s="33"/>
       <c r="G397" s="16"/>
       <c r="H397"/>
-      <c r="I397" s="26"/>
+      <c r="I397" s="25"/>
       <c r="K397" s="15"/>
-      <c r="L397" s="28"/>
+      <c r="L397" s="27"/>
     </row>
     <row r="398" spans="1:12">
       <c r="A398" s="11"/>
       <c r="B398" s="15"/>
       <c r="C398" s="13"/>
-      <c r="D398" s="32"/>
-      <c r="E398" s="34"/>
-      <c r="F398" s="34"/>
+      <c r="D398" s="31"/>
+      <c r="E398" s="33"/>
+      <c r="F398" s="33"/>
       <c r="G398" s="16"/>
       <c r="H398"/>
-      <c r="I398" s="26"/>
+      <c r="I398" s="25"/>
       <c r="K398" s="15"/>
-      <c r="L398" s="28"/>
+      <c r="L398" s="27"/>
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="11"/>
       <c r="B399" s="15"/>
       <c r="C399" s="13"/>
-      <c r="D399" s="32"/>
-      <c r="E399" s="34"/>
-      <c r="F399" s="34"/>
+      <c r="D399" s="31"/>
+      <c r="E399" s="33"/>
+      <c r="F399" s="33"/>
       <c r="G399" s="16"/>
       <c r="H399"/>
-      <c r="I399" s="26"/>
+      <c r="I399" s="25"/>
       <c r="K399" s="15"/>
-      <c r="L399" s="28"/>
+      <c r="L399" s="27"/>
     </row>
     <row r="400" spans="1:12">
       <c r="A400" s="11"/>
       <c r="B400" s="15"/>
       <c r="C400" s="13"/>
-      <c r="D400" s="32"/>
-      <c r="E400" s="34"/>
-      <c r="F400" s="34"/>
+      <c r="D400" s="31"/>
+      <c r="E400" s="33"/>
+      <c r="F400" s="33"/>
       <c r="G400" s="16"/>
       <c r="H400"/>
-      <c r="I400" s="26"/>
+      <c r="I400" s="25"/>
       <c r="K400" s="15"/>
-      <c r="L400" s="28"/>
+      <c r="L400" s="27"/>
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="11"/>
       <c r="B401" s="15"/>
       <c r="C401" s="13"/>
-      <c r="D401" s="32"/>
-      <c r="E401" s="34"/>
-      <c r="F401" s="34"/>
+      <c r="D401" s="31"/>
+      <c r="E401" s="33"/>
+      <c r="F401" s="33"/>
       <c r="G401" s="16"/>
       <c r="H401"/>
-      <c r="I401" s="26"/>
+      <c r="I401" s="25"/>
       <c r="K401" s="15"/>
-      <c r="L401" s="28"/>
+      <c r="L401" s="27"/>
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="11"/>
       <c r="B402" s="15"/>
       <c r="C402" s="13"/>
-      <c r="D402" s="32"/>
-      <c r="E402" s="34"/>
-      <c r="F402" s="34"/>
+      <c r="D402" s="31"/>
+      <c r="E402" s="33"/>
+      <c r="F402" s="33"/>
       <c r="G402" s="16"/>
       <c r="H402"/>
-      <c r="I402" s="26"/>
+      <c r="I402" s="25"/>
       <c r="K402" s="15"/>
-      <c r="L402" s="28"/>
+      <c r="L402" s="27"/>
     </row>
     <row r="403" spans="1:12">
       <c r="A403" s="11"/>
       <c r="B403" s="15"/>
       <c r="C403" s="13"/>
-      <c r="D403" s="32"/>
-      <c r="E403" s="34"/>
-      <c r="F403" s="34"/>
+      <c r="D403" s="31"/>
+      <c r="E403" s="33"/>
+      <c r="F403" s="33"/>
       <c r="G403" s="16"/>
       <c r="H403"/>
-      <c r="I403" s="26"/>
+      <c r="I403" s="25"/>
       <c r="K403" s="15"/>
-      <c r="L403" s="28"/>
+      <c r="L403" s="27"/>
     </row>
     <row r="404" spans="1:12">
       <c r="A404" s="11"/>
       <c r="B404" s="15"/>
       <c r="C404" s="13"/>
-      <c r="D404" s="32"/>
-      <c r="E404" s="34"/>
-      <c r="F404" s="34"/>
+      <c r="D404" s="31"/>
+      <c r="E404" s="33"/>
+      <c r="F404" s="33"/>
       <c r="G404" s="16"/>
       <c r="H404"/>
-      <c r="I404" s="26"/>
+      <c r="I404" s="25"/>
       <c r="K404" s="15"/>
-      <c r="L404" s="28"/>
+      <c r="L404" s="27"/>
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="11"/>
       <c r="B405" s="15"/>
       <c r="C405" s="13"/>
-      <c r="D405" s="32"/>
-      <c r="E405" s="34"/>
-      <c r="F405" s="34"/>
+      <c r="D405" s="31"/>
+      <c r="E405" s="33"/>
+      <c r="F405" s="33"/>
       <c r="G405" s="16"/>
       <c r="H405"/>
-      <c r="I405" s="26"/>
+      <c r="I405" s="25"/>
       <c r="K405" s="15"/>
-      <c r="L405" s="28"/>
+      <c r="L405" s="27"/>
     </row>
     <row r="406" spans="1:12">
       <c r="A406" s="11"/>
       <c r="B406" s="15"/>
       <c r="C406" s="13"/>
-      <c r="D406" s="32"/>
-      <c r="E406" s="34"/>
-      <c r="F406" s="34"/>
+      <c r="D406" s="31"/>
+      <c r="E406" s="33"/>
+      <c r="F406" s="33"/>
       <c r="G406" s="16"/>
       <c r="H406"/>
-      <c r="I406" s="26"/>
+      <c r="I406" s="25"/>
       <c r="K406" s="15"/>
-      <c r="L406" s="28"/>
+      <c r="L406" s="27"/>
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="11"/>
       <c r="B407" s="15"/>
       <c r="C407" s="13"/>
-      <c r="D407" s="32"/>
-      <c r="E407" s="34"/>
-      <c r="F407" s="34"/>
+      <c r="D407" s="31"/>
+      <c r="E407" s="33"/>
+      <c r="F407" s="33"/>
       <c r="G407" s="16"/>
       <c r="H407"/>
-      <c r="I407" s="26"/>
+      <c r="I407" s="25"/>
       <c r="K407" s="15"/>
-      <c r="L407" s="28"/>
+      <c r="L407" s="27"/>
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="11"/>
       <c r="B408" s="15"/>
       <c r="C408" s="13"/>
-      <c r="D408" s="32"/>
-      <c r="E408" s="34"/>
-      <c r="F408" s="34"/>
+      <c r="D408" s="31"/>
+      <c r="E408" s="33"/>
+      <c r="F408" s="33"/>
       <c r="G408" s="16"/>
       <c r="H408"/>
-      <c r="I408" s="26"/>
+      <c r="I408" s="25"/>
       <c r="K408" s="15"/>
-      <c r="L408" s="28"/>
+      <c r="L408" s="27"/>
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="11"/>
       <c r="B409" s="15"/>
       <c r="C409" s="13"/>
-      <c r="D409" s="32"/>
-      <c r="E409" s="34"/>
-      <c r="F409" s="34"/>
+      <c r="D409" s="31"/>
+      <c r="E409" s="33"/>
+      <c r="F409" s="33"/>
       <c r="G409" s="16"/>
       <c r="H409"/>
-      <c r="I409" s="26"/>
+      <c r="I409" s="25"/>
       <c r="K409" s="15"/>
-      <c r="L409" s="28"/>
+      <c r="L409" s="27"/>
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="11"/>
       <c r="B410" s="15"/>
       <c r="C410" s="13"/>
-      <c r="D410" s="32"/>
-      <c r="E410" s="34"/>
-      <c r="F410" s="34"/>
+      <c r="D410" s="31"/>
+      <c r="E410" s="33"/>
+      <c r="F410" s="33"/>
       <c r="G410" s="16"/>
       <c r="H410"/>
-      <c r="I410" s="26"/>
+      <c r="I410" s="25"/>
       <c r="K410" s="15"/>
-      <c r="L410" s="28"/>
+      <c r="L410" s="27"/>
     </row>
     <row r="411" spans="1:12">
       <c r="A411" s="11"/>
       <c r="B411" s="15"/>
       <c r="C411" s="13"/>
-      <c r="D411" s="32"/>
-      <c r="E411" s="34"/>
-      <c r="F411" s="34"/>
+      <c r="D411" s="31"/>
+      <c r="E411" s="33"/>
+      <c r="F411" s="33"/>
       <c r="G411" s="16"/>
       <c r="H411"/>
-      <c r="I411" s="26"/>
+      <c r="I411" s="25"/>
       <c r="K411" s="15"/>
-      <c r="L411" s="28"/>
+      <c r="L411" s="27"/>
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="11"/>
       <c r="B412" s="15"/>
       <c r="C412" s="13"/>
-      <c r="D412" s="32"/>
-      <c r="E412" s="34"/>
-      <c r="F412" s="34"/>
+      <c r="D412" s="31"/>
+      <c r="E412" s="33"/>
+      <c r="F412" s="33"/>
       <c r="G412" s="16"/>
       <c r="H412"/>
-      <c r="I412" s="26"/>
+      <c r="I412" s="25"/>
       <c r="K412" s="15"/>
-      <c r="L412" s="28"/>
+      <c r="L412" s="27"/>
     </row>
     <row r="413" spans="1:12">
       <c r="A413" s="11"/>
       <c r="B413" s="15"/>
       <c r="C413" s="13"/>
-      <c r="D413" s="32"/>
-      <c r="E413" s="34"/>
-      <c r="F413" s="34"/>
+      <c r="D413" s="31"/>
+      <c r="E413" s="33"/>
+      <c r="F413" s="33"/>
       <c r="G413" s="16"/>
       <c r="H413"/>
-      <c r="I413" s="26"/>
+      <c r="I413" s="25"/>
       <c r="K413" s="15"/>
-      <c r="L413" s="28"/>
+      <c r="L413" s="27"/>
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="11"/>
       <c r="B414" s="15"/>
       <c r="C414" s="13"/>
-      <c r="D414" s="32"/>
-      <c r="E414" s="34"/>
-      <c r="F414" s="34"/>
+      <c r="D414" s="31"/>
+      <c r="E414" s="33"/>
+      <c r="F414" s="33"/>
       <c r="G414" s="16"/>
       <c r="H414"/>
-      <c r="I414" s="26"/>
+      <c r="I414" s="25"/>
       <c r="K414" s="15"/>
-      <c r="L414" s="28"/>
+      <c r="L414" s="27"/>
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="11"/>
       <c r="B415" s="15"/>
       <c r="C415" s="13"/>
-      <c r="D415" s="32"/>
-      <c r="E415" s="34"/>
-      <c r="F415" s="34"/>
+      <c r="D415" s="31"/>
+      <c r="E415" s="33"/>
+      <c r="F415" s="33"/>
       <c r="G415" s="16"/>
       <c r="H415"/>
-      <c r="I415" s="26"/>
+      <c r="I415" s="25"/>
       <c r="K415" s="15"/>
-      <c r="L415" s="28"/>
+      <c r="L415" s="27"/>
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="11"/>
       <c r="B416" s="15"/>
       <c r="C416" s="13"/>
-      <c r="D416" s="32"/>
-      <c r="E416" s="34"/>
-      <c r="F416" s="34"/>
+      <c r="D416" s="31"/>
+      <c r="E416" s="33"/>
+      <c r="F416" s="33"/>
       <c r="G416" s="16"/>
       <c r="H416"/>
-      <c r="I416" s="26"/>
+      <c r="I416" s="25"/>
       <c r="K416" s="15"/>
-      <c r="L416" s="28"/>
+      <c r="L416" s="27"/>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" s="11"/>

--- a/ACCOUNT_RECEIPT/tests/DatasheetKDMC 12.xlsx
+++ b/ACCOUNT_RECEIPT/tests/DatasheetKDMC 12.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19290" windowHeight="4485"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Done" sheetId="1" r:id="rId1"/>
